--- a/신고신저가_20260720.xlsx
+++ b/신고신저가_20260720.xlsx
@@ -77,10 +77,10 @@
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
@@ -449,7 +449,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -607,7 +607,14 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>💬 금요일(7/17)은 미국-아시아 온도차가 뚜렷 — 미국은 신고가 137개(정유 정제마진 강세, TRV 어닝 서프라이즈 +8%)인 반면, 아시아는 AI·반도체 고밸류 되돌림으로 일본 기계·비철 급락(신저 7개), 중국A 신저가 41개, 항셍테크 -4.4% 리스크오프. 이벤트: NFLX 3Q 가이던스 실망 -7%, 세븐&amp;아이는 폴란드 자브카 출자 검토 보도로 신고가, 중국 중약 섹터는 15·5규획 발표에 강세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -708,7 +715,7 @@
       <c r="F2" t="n">
         <v>55</v>
       </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="G2" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -743,7 +750,7 @@
       <c r="F3" t="n">
         <v>11</v>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -778,7 +785,7 @@
       <c r="F4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -813,7 +820,7 @@
       <c r="F5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="G5" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -848,7 +855,7 @@
       <c r="F6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="G6" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -883,7 +890,7 @@
       <c r="F7" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -918,7 +925,7 @@
       <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="G8" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -953,7 +960,7 @@
       <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="G9" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -988,7 +995,7 @@
       <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G10" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1023,7 +1030,7 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="G11" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1058,7 +1065,7 @@
       <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="G12" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1093,7 +1100,7 @@
       <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="G13" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1128,7 +1135,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1268,7 +1275,7 @@
       <c r="F18" t="n">
         <v>-2</v>
       </c>
-      <c r="G18" s="3" t="inlineStr">
+      <c r="G18" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1303,7 +1310,7 @@
       <c r="F19" t="n">
         <v>-2</v>
       </c>
-      <c r="G19" s="3" t="inlineStr">
+      <c r="G19" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1338,7 +1345,7 @@
       <c r="F20" t="n">
         <v>-13</v>
       </c>
-      <c r="G20" s="3" t="inlineStr">
+      <c r="G20" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1373,7 +1380,7 @@
       <c r="F21" t="n">
         <v>-26</v>
       </c>
-      <c r="G21" s="3" t="inlineStr">
+      <c r="G21" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1408,7 +1415,7 @@
       <c r="F22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="2" t="inlineStr">
+      <c r="G22" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1443,7 +1450,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="G23" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1478,7 +1485,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="G24" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1513,7 +1520,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="G25" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1968,7 +1975,7 @@
       <c r="F38" t="n">
         <v>-2</v>
       </c>
-      <c r="G38" s="3" t="inlineStr">
+      <c r="G38" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2003,7 +2010,7 @@
       <c r="F39" t="n">
         <v>-4</v>
       </c>
-      <c r="G39" s="3" t="inlineStr">
+      <c r="G39" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2038,7 +2045,7 @@
       <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="2" t="inlineStr">
+      <c r="G40" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2528,7 +2535,7 @@
       <c r="F54" t="n">
         <v>-2</v>
       </c>
-      <c r="G54" s="3" t="inlineStr">
+      <c r="G54" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2563,7 +2570,7 @@
       <c r="F55" t="n">
         <v>-2</v>
       </c>
-      <c r="G55" s="3" t="inlineStr">
+      <c r="G55" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2598,7 +2605,7 @@
       <c r="F56" t="n">
         <v>-5</v>
       </c>
-      <c r="G56" s="3" t="inlineStr">
+      <c r="G56" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2633,7 +2640,7 @@
       <c r="F57" t="n">
         <v>-7</v>
       </c>
-      <c r="G57" s="3" t="inlineStr">
+      <c r="G57" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2668,7 +2675,7 @@
       <c r="F58" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="3" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2981,7 +2988,7 @@
       <c r="F67" t="n">
         <v>-1</v>
       </c>
-      <c r="G67" s="3" t="inlineStr">
+      <c r="G67" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3014,7 +3021,7 @@
       <c r="F68" t="n">
         <v>-1</v>
       </c>
-      <c r="G68" s="3" t="inlineStr">
+      <c r="G68" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3049,7 +3056,7 @@
       <c r="F69" t="n">
         <v>-1</v>
       </c>
-      <c r="G69" s="3" t="inlineStr">
+      <c r="G69" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3084,7 +3091,7 @@
       <c r="F70" t="n">
         <v>-2</v>
       </c>
-      <c r="G70" s="3" t="inlineStr">
+      <c r="G70" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3119,7 +3126,7 @@
       <c r="F71" t="n">
         <v>-2</v>
       </c>
-      <c r="G71" s="3" t="inlineStr">
+      <c r="G71" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3154,7 +3161,7 @@
       <c r="F72" t="n">
         <v>-3</v>
       </c>
-      <c r="G72" s="3" t="inlineStr">
+      <c r="G72" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3189,7 +3196,7 @@
       <c r="F73" t="n">
         <v>-4</v>
       </c>
-      <c r="G73" s="3" t="inlineStr">
+      <c r="G73" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3224,7 +3231,7 @@
       <c r="F74" t="n">
         <v>-13</v>
       </c>
-      <c r="G74" s="3" t="inlineStr">
+      <c r="G74" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3259,7 +3266,7 @@
       <c r="F75" t="n">
         <v>-13</v>
       </c>
-      <c r="G75" s="3" t="inlineStr">
+      <c r="G75" s="4" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3439,55 +3446,55 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D2" s="4" t="n">
+      <c r="D2" s="5" t="n">
         <v>1.2</v>
       </c>
-      <c r="E2" s="4" t="n">
+      <c r="E2" s="5" t="n">
         <v>4.7</v>
       </c>
-      <c r="F2" s="4" t="n">
+      <c r="F2" s="5" t="n">
         <v>4.9</v>
       </c>
-      <c r="G2" s="4" t="n">
+      <c r="G2" s="5" t="n">
         <v>2.7</v>
       </c>
-      <c r="H2" s="4" t="n">
+      <c r="H2" s="5" t="n">
         <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="4" t="n">
+      <c r="J2" s="5" t="n">
         <v>7.9</v>
       </c>
       <c r="K2" t="n">
         <v>8</v>
       </c>
-      <c r="L2" s="4" t="n">
+      <c r="L2" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
       </c>
-      <c r="N2" s="4" t="n">
+      <c r="N2" s="5" t="n">
         <v>-0.6</v>
       </c>
       <c r="O2" t="n">
         <v>9</v>
       </c>
-      <c r="P2" s="4" t="n">
+      <c r="P2" s="5" t="n">
         <v>64.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" s="4" t="n">
+      <c r="R2" s="5" t="n">
         <v>53.3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="4" t="n">
+      <c r="T2" s="5" t="n">
         <v>-32.7</v>
       </c>
       <c r="U2" t="n">
@@ -3510,55 +3517,55 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>4.6</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>14.3</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="5" t="n">
         <v>2.6</v>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="5" t="n">
         <v>5.1</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="5" t="n">
         <v>12.4</v>
       </c>
       <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="P3" s="4" t="n">
+      <c r="P3" s="5" t="n">
         <v>-26.2</v>
       </c>
       <c r="Q3" t="n">
         <v>8</v>
       </c>
-      <c r="R3" s="4" t="n">
+      <c r="R3" s="5" t="n">
         <v>46.1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="T3" s="4" t="n">
+      <c r="T3" s="5" t="n">
         <v>-2.2</v>
       </c>
       <c r="U3" t="n">
@@ -3581,55 +3588,55 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>5.6</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>16.3</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="5" t="n">
         <v>19.3</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="5" t="n">
         <v>17.3</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="5" t="n">
         <v>18.1</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
-      <c r="P4" s="4" t="n">
+      <c r="P4" s="5" t="n">
         <v>-5.6</v>
       </c>
       <c r="Q4" t="n">
         <v>5</v>
       </c>
-      <c r="R4" s="4" t="n">
+      <c r="R4" s="5" t="n">
         <v>21.1</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
       </c>
-      <c r="T4" s="4" t="n">
+      <c r="T4" s="5" t="n">
         <v>10.9</v>
       </c>
       <c r="U4" t="n">
@@ -3652,55 +3659,55 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>5.8</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>10.4</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>14.5</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="5" t="n">
         <v>2.5</v>
       </c>
       <c r="M5" t="n">
         <v>10</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="O5" t="n">
         <v>8</v>
       </c>
-      <c r="P5" s="4" t="n">
+      <c r="P5" s="5" t="n">
         <v>-2.1</v>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
-      <c r="R5" s="4" t="n">
+      <c r="R5" s="5" t="n">
         <v>26</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
       </c>
-      <c r="T5" s="4" t="n">
+      <c r="T5" s="5" t="n">
         <v>13.3</v>
       </c>
       <c r="U5" t="n">
@@ -3723,55 +3730,55 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>-3.8</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <v>-2</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>12.3</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="5" t="n">
         <v>9.9</v>
       </c>
       <c r="K6" t="n">
         <v>7</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="5" t="n">
         <v>0.1</v>
       </c>
       <c r="M6" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="5" t="n">
         <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="P6" s="4" t="n">
+      <c r="P6" s="5" t="n">
         <v>-12.3</v>
       </c>
       <c r="Q6" t="n">
         <v>7</v>
       </c>
-      <c r="R6" s="4" t="n">
+      <c r="R6" s="5" t="n">
         <v>27.4</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
-      <c r="T6" s="4" t="n">
+      <c r="T6" s="5" t="n">
         <v>20.5</v>
       </c>
       <c r="U6" t="n">
@@ -3794,55 +3801,55 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>5.3</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>11.1</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="5" t="n">
         <v>1.5</v>
       </c>
       <c r="K7" t="n">
         <v>11</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="5" t="n">
         <v>12.2</v>
       </c>
       <c r="M7" t="n">
         <v>7</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="5" t="n">
         <v>-0.8</v>
       </c>
       <c r="O7" t="n">
         <v>10</v>
       </c>
-      <c r="P7" s="4" t="n">
+      <c r="P7" s="5" t="n">
         <v>-0.8</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="R7" s="4" t="n">
+      <c r="R7" s="5" t="n">
         <v>17.2</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
-      <c r="T7" s="4" t="n">
+      <c r="T7" s="5" t="n">
         <v>10.1</v>
       </c>
       <c r="U7" t="n">
@@ -3865,55 +3872,55 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="5" t="n">
         <v>-1.9</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>7.2</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="5" t="n">
         <v>16</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="5" t="n">
         <v>23.3</v>
       </c>
       <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="5" t="n">
         <v>-7.2</v>
       </c>
       <c r="O8" t="n">
         <v>11</v>
       </c>
-      <c r="P8" s="4" t="n">
+      <c r="P8" s="5" t="n">
         <v>1.4</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="R8" s="4" t="n">
+      <c r="R8" s="5" t="n">
         <v>17.7</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
       </c>
-      <c r="T8" s="4" t="n">
+      <c r="T8" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="U8" t="n">
@@ -3936,55 +3943,55 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <v>3.9</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="5" t="n">
         <v>8.5</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>3.6</v>
       </c>
       <c r="I9" t="n">
         <v>9</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="5" t="n">
         <v>14.9</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="5" t="n">
         <v>30.6</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="5" t="n">
         <v>12</v>
       </c>
       <c r="O9" t="n">
         <v>7</v>
       </c>
-      <c r="P9" s="4" t="n">
+      <c r="P9" s="5" t="n">
         <v>-10.6</v>
       </c>
       <c r="Q9" t="n">
         <v>6</v>
       </c>
-      <c r="R9" s="4" t="n">
+      <c r="R9" s="5" t="n">
         <v>34.8</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T9" s="4" t="n">
+      <c r="T9" s="5" t="n">
         <v>-1.7</v>
       </c>
       <c r="U9" t="n">
@@ -4007,55 +4014,55 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="5" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>-5.5</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>-5.7</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="5" t="n">
         <v>15.6</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="5" t="n">
         <v>22.3</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="5" t="n">
         <v>24.6</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="5" t="n">
         <v>21.6</v>
       </c>
       <c r="M10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="5" t="n">
         <v>56</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="P10" s="4" t="n">
+      <c r="P10" s="5" t="n">
         <v>-27.7</v>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
-      <c r="R10" s="4" t="n">
+      <c r="R10" s="5" t="n">
         <v>34.7</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="T10" s="4" t="n">
+      <c r="T10" s="5" t="n">
         <v>43.6</v>
       </c>
       <c r="U10" t="n">
@@ -4078,55 +4085,55 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="5" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="5" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="5" t="n">
         <v>-2.9</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="5" t="n">
         <v>7.4</v>
       </c>
       <c r="K11" t="n">
         <v>9</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="5" t="n">
         <v>26.5</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="5" t="n">
         <v>39.6</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="P11" s="4" t="n">
+      <c r="P11" s="5" t="n">
         <v>-36.3</v>
       </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
-      <c r="R11" s="4" t="n">
+      <c r="R11" s="5" t="n">
         <v>27.9</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="T11" s="4" t="n">
+      <c r="T11" s="5" t="n">
         <v>29.6</v>
       </c>
       <c r="U11" t="n">
@@ -4149,55 +4156,55 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="5" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="5" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="5" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="5" t="n">
         <v>-5.5</v>
       </c>
       <c r="I12" t="n">
         <v>11</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="5" t="n">
         <v>23.1</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="5" t="n">
         <v>34.7</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="5" t="n">
         <v>52.8</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="P12" s="4" t="n">
+      <c r="P12" s="5" t="n">
         <v>-37.6</v>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
-      <c r="R12" s="4" t="n">
+      <c r="R12" s="5" t="n">
         <v>16</v>
       </c>
       <c r="S12" t="n">
         <v>11</v>
       </c>
-      <c r="T12" s="4" t="n">
+      <c r="T12" s="5" t="n">
         <v>26.9</v>
       </c>
       <c r="U12" t="n">
@@ -4220,55 +4227,55 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>1.1</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>3.1</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="5" t="n">
         <v>-6.5</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="I13" t="n">
         <v>14</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="5" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>16</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="5" t="n">
         <v>10.8</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N13" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="O13" t="n">
         <v>17</v>
       </c>
-      <c r="P13" s="4" t="n">
+      <c r="P13" s="5" t="n">
         <v>16.4</v>
       </c>
       <c r="Q13" t="n">
         <v>4</v>
       </c>
-      <c r="R13" s="4" t="n">
+      <c r="R13" s="5" t="n">
         <v>-8.4</v>
       </c>
       <c r="S13" t="n">
         <v>17</v>
       </c>
-      <c r="T13" s="4" t="n">
+      <c r="T13" s="5" t="n">
         <v>4.6</v>
       </c>
       <c r="U13" t="n">
@@ -4291,55 +4298,55 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="5" t="n">
         <v>7.1</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="5" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="5" t="n">
         <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>13</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="5" t="n">
         <v>19.9</v>
       </c>
       <c r="K14" t="n">
         <v>11</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="5" t="n">
         <v>-0</v>
       </c>
       <c r="M14" t="n">
         <v>17</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="5" t="n">
         <v>19</v>
       </c>
       <c r="O14" t="n">
         <v>14</v>
       </c>
-      <c r="P14" s="4" t="n">
+      <c r="P14" s="5" t="n">
         <v>13.1</v>
       </c>
       <c r="Q14" t="n">
         <v>8</v>
       </c>
-      <c r="R14" s="4" t="n">
+      <c r="R14" s="5" t="n">
         <v>4.7</v>
       </c>
       <c r="S14" t="n">
         <v>12</v>
       </c>
-      <c r="T14" s="4" t="n">
+      <c r="T14" s="5" t="n">
         <v>-17.1</v>
       </c>
       <c r="U14" t="n">
@@ -4362,55 +4369,55 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="5" t="n">
         <v>5.7</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="5" t="n">
         <v>16.2</v>
       </c>
       <c r="I15" t="n">
         <v>6</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="5" t="n">
         <v>11.8</v>
       </c>
       <c r="K15" t="n">
         <v>15</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="5" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="5" t="n">
         <v>22.3</v>
       </c>
       <c r="O15" t="n">
         <v>13</v>
       </c>
-      <c r="P15" s="4" t="n">
+      <c r="P15" s="5" t="n">
         <v>6.4</v>
       </c>
       <c r="Q15" t="n">
         <v>10</v>
       </c>
-      <c r="R15" s="4" t="n">
+      <c r="R15" s="5" t="n">
         <v>5.6</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
       </c>
-      <c r="T15" s="4" t="n">
+      <c r="T15" s="5" t="n">
         <v>-3.4</v>
       </c>
       <c r="U15" t="n">
@@ -4433,55 +4440,55 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="5" t="n">
         <v>1.8</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>3.6</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>4.3</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="5" t="n">
         <v>16.8</v>
       </c>
       <c r="K16" t="n">
         <v>12</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="5" t="n">
         <v>23.4</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="5" t="n">
         <v>16.4</v>
       </c>
       <c r="O16" t="n">
         <v>16</v>
       </c>
-      <c r="P16" s="4" t="n">
+      <c r="P16" s="5" t="n">
         <v>10.2</v>
       </c>
       <c r="Q16" t="n">
         <v>9</v>
       </c>
-      <c r="R16" s="4" t="n">
+      <c r="R16" s="5" t="n">
         <v>-4.4</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
       </c>
-      <c r="T16" s="4" t="n">
+      <c r="T16" s="5" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="U16" t="n">
@@ -4504,55 +4511,55 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="5" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="5" t="n">
         <v>1.6</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="5" t="n">
         <v>0.2</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>-8</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="5" t="n">
         <v>10.8</v>
       </c>
       <c r="I17" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="5" t="n">
         <v>41.5</v>
       </c>
       <c r="K17" t="n">
         <v>5</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="5" t="n">
         <v>20.1</v>
       </c>
       <c r="M17" t="n">
         <v>9</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="5" t="n">
         <v>42</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="P17" s="4" t="n">
+      <c r="P17" s="5" t="n">
         <v>21.3</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="R17" s="4" t="n">
+      <c r="R17" s="5" t="n">
         <v>29.2</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T17" s="4" t="n">
+      <c r="T17" s="5" t="n">
         <v>1.9</v>
       </c>
       <c r="U17" t="n">
@@ -4575,55 +4582,55 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="5" t="n">
         <v>-0</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="5" t="n">
         <v>-1.9</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="5" t="n">
         <v>7.3</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>23.8</v>
       </c>
       <c r="I18" t="n">
         <v>5</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="5" t="n">
         <v>8.6</v>
       </c>
       <c r="K18" t="n">
         <v>17</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="5" t="n">
         <v>3.9</v>
       </c>
       <c r="M18" t="n">
         <v>16</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="5" t="n">
         <v>23.1</v>
       </c>
       <c r="O18" t="n">
         <v>12</v>
       </c>
-      <c r="P18" s="4" t="n">
+      <c r="P18" s="5" t="n">
         <v>-9.4</v>
       </c>
       <c r="Q18" t="n">
         <v>14</v>
       </c>
-      <c r="R18" s="4" t="n">
+      <c r="R18" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="S18" t="n">
         <v>14</v>
       </c>
-      <c r="T18" s="4" t="n">
+      <c r="T18" s="5" t="n">
         <v>8.6</v>
       </c>
       <c r="U18" t="n">
@@ -4646,55 +4653,55 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="5" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="5" t="n">
         <v>0.7</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="5" t="n">
         <v>2.4</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="5" t="n">
         <v>-10.9</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="5" t="n">
         <v>-1.2</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="5" t="n">
         <v>41.6</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="5" t="n">
         <v>13.9</v>
       </c>
       <c r="M19" t="n">
         <v>12</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="5" t="n">
         <v>23.6</v>
       </c>
       <c r="O19" t="n">
         <v>11</v>
       </c>
-      <c r="P19" s="4" t="n">
+      <c r="P19" s="5" t="n">
         <v>4.4</v>
       </c>
       <c r="Q19" t="n">
         <v>11</v>
       </c>
-      <c r="R19" s="4" t="n">
+      <c r="R19" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
-      <c r="T19" s="4" t="n">
+      <c r="T19" s="5" t="n">
         <v>-13.3</v>
       </c>
       <c r="U19" t="n">
@@ -4717,55 +4724,55 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="5" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="5" t="n">
         <v>3.4</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="5" t="n">
         <v>2.6</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="5" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="5" t="n">
         <v>-6.1</v>
       </c>
       <c r="I20" t="n">
         <v>17</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="5" t="n">
         <v>13.5</v>
       </c>
       <c r="K20" t="n">
         <v>14</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="5" t="n">
         <v>16.4</v>
       </c>
       <c r="M20" t="n">
         <v>11</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="5" t="n">
         <v>40.5</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="P20" s="4" t="n">
+      <c r="P20" s="5" t="n">
         <v>-10.7</v>
       </c>
       <c r="Q20" t="n">
         <v>16</v>
       </c>
-      <c r="R20" s="4" t="n">
+      <c r="R20" s="5" t="n">
         <v>27.8</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="T20" s="4" t="n">
+      <c r="T20" s="5" t="n">
         <v>0.7</v>
       </c>
       <c r="U20" t="n">
@@ -4788,55 +4795,55 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="5" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="5" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="5" t="n">
         <v>-14.8</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>9</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="5" t="n">
         <v>41.4</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="5" t="n">
         <v>29.9</v>
       </c>
       <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="5" t="n">
         <v>37.2</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
       </c>
-      <c r="P21" s="4" t="n">
+      <c r="P21" s="5" t="n">
         <v>23.6</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R21" s="4" t="n">
+      <c r="R21" s="5" t="n">
         <v>39.3</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T21" s="4" t="n">
+      <c r="T21" s="5" t="n">
         <v>-29</v>
       </c>
       <c r="U21" t="n">
@@ -4859,55 +4866,55 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="5" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="5" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="5" t="n">
         <v>11.6</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="5" t="n">
         <v>4.5</v>
       </c>
       <c r="I22" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" s="5" t="n">
         <v>13.9</v>
       </c>
       <c r="K22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="5" t="n">
         <v>21</v>
       </c>
       <c r="M22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="5" t="n">
         <v>17.9</v>
       </c>
       <c r="O22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="4" t="n">
+      <c r="P22" s="5" t="n">
         <v>-5.9</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="4" t="n">
+      <c r="R22" s="5" t="n">
         <v>3.5</v>
       </c>
       <c r="S22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="4" t="n">
+      <c r="T22" s="5" t="n">
         <v>21.9</v>
       </c>
       <c r="U22" t="n">
@@ -4930,55 +4937,55 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="5" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="5" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="5" t="n">
         <v>10.7</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="5" t="n">
         <v>24.1</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="5" t="n">
         <v>21.4</v>
       </c>
       <c r="K23" t="n">
         <v>10</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="5" t="n">
         <v>49</v>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="5" t="n">
         <v>27.2</v>
       </c>
       <c r="O23" t="n">
         <v>10</v>
       </c>
-      <c r="P23" s="4" t="n">
+      <c r="P23" s="5" t="n">
         <v>13.7</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
       </c>
-      <c r="R23" s="4" t="n">
+      <c r="R23" s="5" t="n">
         <v>22.6</v>
       </c>
       <c r="S23" t="n">
         <v>6</v>
       </c>
-      <c r="T23" s="4" t="n">
+      <c r="T23" s="5" t="n">
         <v>-3.6</v>
       </c>
       <c r="U23" t="n">
@@ -5001,55 +5008,55 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="5" t="n">
         <v>-2.6</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="5" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="5" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="5" t="n">
         <v>-11.1</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="5" t="n">
         <v>-1.1</v>
       </c>
       <c r="I24" t="n">
         <v>15</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="5" t="n">
         <v>37.4</v>
       </c>
       <c r="K24" t="n">
         <v>7</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="5" t="n">
         <v>6.3</v>
       </c>
       <c r="M24" t="n">
         <v>15</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="5" t="n">
         <v>35</v>
       </c>
       <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" s="4" t="n">
+      <c r="P24" s="5" t="n">
         <v>13.2</v>
       </c>
       <c r="Q24" t="n">
         <v>7</v>
       </c>
-      <c r="R24" s="4" t="n">
+      <c r="R24" s="5" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="S24" t="n">
         <v>16</v>
       </c>
-      <c r="T24" s="4" t="n">
+      <c r="T24" s="5" t="n">
         <v>-10.7</v>
       </c>
       <c r="U24" t="n">
@@ -5072,55 +5079,55 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D25" s="4" t="n">
+      <c r="D25" s="5" t="n">
         <v>-3.3</v>
       </c>
-      <c r="E25" s="4" t="n">
+      <c r="E25" s="5" t="n">
         <v>-5</v>
       </c>
-      <c r="F25" s="4" t="n">
+      <c r="F25" s="5" t="n">
         <v>-7</v>
       </c>
-      <c r="G25" s="4" t="n">
+      <c r="G25" s="5" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H25" s="4" t="n">
+      <c r="H25" s="5" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="4" t="n">
+      <c r="J25" s="5" t="n">
         <v>42</v>
       </c>
       <c r="K25" t="n">
         <v>3</v>
       </c>
-      <c r="L25" s="4" t="n">
+      <c r="L25" s="5" t="n">
         <v>21.6</v>
       </c>
       <c r="M25" t="n">
         <v>6</v>
       </c>
-      <c r="N25" s="4" t="n">
+      <c r="N25" s="5" t="n">
         <v>32</v>
       </c>
       <c r="O25" t="n">
         <v>9</v>
       </c>
-      <c r="P25" s="4" t="n">
+      <c r="P25" s="5" t="n">
         <v>-2.4</v>
       </c>
       <c r="Q25" t="n">
         <v>12</v>
       </c>
-      <c r="R25" s="4" t="n">
+      <c r="R25" s="5" t="n">
         <v>12.6</v>
       </c>
       <c r="S25" t="n">
         <v>8</v>
       </c>
-      <c r="T25" s="4" t="n">
+      <c r="T25" s="5" t="n">
         <v>-6.1</v>
       </c>
       <c r="U25" t="n">
@@ -5143,55 +5150,55 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D26" s="4" t="n">
+      <c r="D26" s="5" t="n">
         <v>-3.7</v>
       </c>
-      <c r="E26" s="4" t="n">
+      <c r="E26" s="5" t="n">
         <v>-7.9</v>
       </c>
-      <c r="F26" s="4" t="n">
+      <c r="F26" s="5" t="n">
         <v>-11.7</v>
       </c>
-      <c r="G26" s="4" t="n">
+      <c r="G26" s="5" t="n">
         <v>12.9</v>
       </c>
-      <c r="H26" s="4" t="n">
+      <c r="H26" s="5" t="n">
         <v>28</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
       </c>
-      <c r="J26" s="4" t="n">
+      <c r="J26" s="5" t="n">
         <v>27.5</v>
       </c>
       <c r="K26" t="n">
         <v>9</v>
       </c>
-      <c r="L26" s="4" t="n">
+      <c r="L26" s="5" t="n">
         <v>17.9</v>
       </c>
       <c r="M26" t="n">
         <v>10</v>
       </c>
-      <c r="N26" s="4" t="n">
+      <c r="N26" s="5" t="n">
         <v>33.7</v>
       </c>
       <c r="O26" t="n">
         <v>7</v>
       </c>
-      <c r="P26" s="4" t="n">
+      <c r="P26" s="5" t="n">
         <v>-23</v>
       </c>
       <c r="Q26" t="n">
         <v>17</v>
       </c>
-      <c r="R26" s="4" t="n">
+      <c r="R26" s="5" t="n">
         <v>25</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
       </c>
-      <c r="T26" s="4" t="n">
+      <c r="T26" s="5" t="n">
         <v>26.2</v>
       </c>
       <c r="U26" t="n">
@@ -5214,55 +5221,55 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="4" t="n">
+      <c r="D27" s="5" t="n">
         <v>-4.7</v>
       </c>
-      <c r="E27" s="4" t="n">
+      <c r="E27" s="5" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F27" s="4" t="n">
+      <c r="F27" s="5" t="n">
         <v>0.4</v>
       </c>
-      <c r="G27" s="4" t="n">
+      <c r="G27" s="5" t="n">
         <v>15.9</v>
       </c>
-      <c r="H27" s="4" t="n">
+      <c r="H27" s="5" t="n">
         <v>39.9</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="4" t="n">
+      <c r="J27" s="5" t="n">
         <v>44.8</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="4" t="n">
+      <c r="L27" s="5" t="n">
         <v>50.4</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="4" t="n">
+      <c r="N27" s="5" t="n">
         <v>33.2</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="4" t="n">
+      <c r="P27" s="5" t="n">
         <v>38.3</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="4" t="n">
+      <c r="R27" s="5" t="n">
         <v>26.7</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="4" t="n">
+      <c r="T27" s="5" t="n">
         <v>-16.3</v>
       </c>
       <c r="U27" t="n">
@@ -5285,55 +5292,55 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D28" s="4" t="n">
+      <c r="D28" s="5" t="n">
         <v>-4.9</v>
       </c>
-      <c r="E28" s="4" t="n">
+      <c r="E28" s="5" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="F28" s="4" t="n">
+      <c r="F28" s="5" t="n">
         <v>-16</v>
       </c>
-      <c r="G28" s="4" t="n">
+      <c r="G28" s="5" t="n">
         <v>-16.9</v>
       </c>
-      <c r="H28" s="4" t="n">
+      <c r="H28" s="5" t="n">
         <v>32.2</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="4" t="n">
+      <c r="J28" s="5" t="n">
         <v>68.8</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" s="4" t="n">
+      <c r="L28" s="5" t="n">
         <v>20.6</v>
       </c>
       <c r="M28" t="n">
         <v>8</v>
       </c>
-      <c r="N28" s="4" t="n">
+      <c r="N28" s="5" t="n">
         <v>35</v>
       </c>
       <c r="O28" t="n">
         <v>4</v>
       </c>
-      <c r="P28" s="4" t="n">
+      <c r="P28" s="5" t="n">
         <v>16.1</v>
       </c>
       <c r="Q28" t="n">
         <v>5</v>
       </c>
-      <c r="R28" s="4" t="n">
+      <c r="R28" s="5" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
       </c>
-      <c r="T28" s="4" t="n">
+      <c r="T28" s="5" t="n">
         <v>-8.6</v>
       </c>
       <c r="U28" t="n">
@@ -5356,55 +5363,55 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D29" s="4" t="n">
+      <c r="D29" s="5" t="n">
         <v>-5.9</v>
       </c>
-      <c r="E29" s="4" t="n">
+      <c r="E29" s="5" t="n">
         <v>-7.6</v>
       </c>
-      <c r="F29" s="4" t="n">
+      <c r="F29" s="5" t="n">
         <v>-10.6</v>
       </c>
-      <c r="G29" s="4" t="n">
+      <c r="G29" s="5" t="n">
         <v>-7.8</v>
       </c>
-      <c r="H29" s="4" t="n">
+      <c r="H29" s="5" t="n">
         <v>13.7</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
       </c>
-      <c r="J29" s="4" t="n">
+      <c r="J29" s="5" t="n">
         <v>31.1</v>
       </c>
       <c r="K29" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="4" t="n">
+      <c r="L29" s="5" t="n">
         <v>22.3</v>
       </c>
       <c r="M29" t="n">
         <v>5</v>
       </c>
-      <c r="N29" s="4" t="n">
+      <c r="N29" s="5" t="n">
         <v>33.9</v>
       </c>
       <c r="O29" t="n">
         <v>6</v>
       </c>
-      <c r="P29" s="4" t="n">
+      <c r="P29" s="5" t="n">
         <v>-9.9</v>
       </c>
       <c r="Q29" t="n">
         <v>15</v>
       </c>
-      <c r="R29" s="4" t="n">
+      <c r="R29" s="5" t="n">
         <v>7.5</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
       </c>
-      <c r="T29" s="4" t="n">
+      <c r="T29" s="5" t="n">
         <v>17.7</v>
       </c>
       <c r="U29" t="n">
@@ -5427,55 +5434,55 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="4" t="n">
+      <c r="D30" s="5" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E30" s="4" t="n">
+      <c r="E30" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="F30" s="4" t="n">
+      <c r="F30" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G30" s="4" t="n">
+      <c r="G30" s="5" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H30" s="4" t="n">
+      <c r="H30" s="5" t="n">
         <v>-2.5</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="4" t="n">
+      <c r="J30" s="5" t="n">
         <v>32.8</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="4" t="n">
+      <c r="L30" s="5" t="n">
         <v>24.8</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="4" t="n">
+      <c r="N30" s="5" t="n">
         <v>-11.9</v>
       </c>
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="4" t="n">
+      <c r="P30" s="5" t="n">
         <v>-14.4</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="4" t="n">
+      <c r="R30" s="5" t="n">
         <v>-13.5</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="4" t="n">
+      <c r="T30" s="5" t="n">
         <v>-1.2</v>
       </c>
       <c r="U30" t="n">
@@ -5498,55 +5505,55 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="4" t="n">
+      <c r="D31" s="5" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E31" s="4" t="n">
+      <c r="E31" s="5" t="n">
         <v>1.3</v>
       </c>
-      <c r="F31" s="4" t="n">
+      <c r="F31" s="5" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G31" s="4" t="n">
+      <c r="G31" s="5" t="n">
         <v>-5.5</v>
       </c>
-      <c r="H31" s="4" t="n">
+      <c r="H31" s="5" t="n">
         <v>-7.6</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="4" t="n">
+      <c r="J31" s="5" t="n">
         <v>26.2</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="4" t="n">
+      <c r="L31" s="5" t="n">
         <v>32.1</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="4" t="n">
+      <c r="N31" s="5" t="n">
         <v>-12.8</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="4" t="n">
+      <c r="P31" s="5" t="n">
         <v>-17.8</v>
       </c>
       <c r="Q31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="4" t="n">
+      <c r="R31" s="5" t="n">
         <v>-23.6</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="4" t="n">
+      <c r="T31" s="5" t="n">
         <v>-2</v>
       </c>
       <c r="U31" t="n">
@@ -5569,55 +5576,55 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="4" t="n">
+      <c r="D32" s="5" t="n">
         <v>-4.5</v>
       </c>
-      <c r="E32" s="4" t="n">
+      <c r="E32" s="5" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F32" s="4" t="n">
+      <c r="F32" s="5" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G32" s="4" t="n">
+      <c r="G32" s="5" t="n">
         <v>-5.8</v>
       </c>
-      <c r="H32" s="4" t="n">
+      <c r="H32" s="5" t="n">
         <v>-15.9</v>
       </c>
       <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="4" t="n">
+      <c r="J32" s="5" t="n">
         <v>22.7</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="4" t="n">
+      <c r="L32" s="5" t="n">
         <v>18.9</v>
       </c>
       <c r="M32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="4" t="n">
+      <c r="N32" s="5" t="n">
         <v>-9.300000000000001</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="4" t="n">
+      <c r="P32" s="5" t="n">
         <v>-27.4</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="4" t="n">
+      <c r="R32" s="5" t="n">
         <v>-32.9</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="4" t="inlineStr"/>
+      <c r="T32" s="5" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5636,55 +5643,55 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D33" s="4" t="n">
+      <c r="D33" s="5" t="n">
         <v>0.9</v>
       </c>
-      <c r="E33" s="4" t="n">
+      <c r="E33" s="5" t="n">
         <v>2.9</v>
       </c>
-      <c r="F33" s="4" t="n">
+      <c r="F33" s="5" t="n">
         <v>0.5</v>
       </c>
-      <c r="G33" s="4" t="n">
+      <c r="G33" s="5" t="n">
         <v>-1.6</v>
       </c>
-      <c r="H33" s="4" t="n">
+      <c r="H33" s="5" t="n">
         <v>-4.1</v>
       </c>
       <c r="I33" t="n">
         <v>5</v>
       </c>
-      <c r="J33" s="4" t="n">
+      <c r="J33" s="5" t="n">
         <v>10.8</v>
       </c>
       <c r="K33" t="n">
         <v>8</v>
       </c>
-      <c r="L33" s="4" t="n">
+      <c r="L33" s="5" t="n">
         <v>42.6</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="4" t="n">
+      <c r="N33" s="5" t="n">
         <v>-3.3</v>
       </c>
       <c r="O33" t="n">
         <v>5</v>
       </c>
-      <c r="P33" s="4" t="n">
+      <c r="P33" s="5" t="n">
         <v>-4.8</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" s="4" t="n">
+      <c r="R33" s="5" t="n">
         <v>-1.2</v>
       </c>
       <c r="S33" t="n">
         <v>7</v>
       </c>
-      <c r="T33" s="4" t="n">
+      <c r="T33" s="5" t="n">
         <v>1.2</v>
       </c>
       <c r="U33" t="n">
@@ -5707,55 +5714,55 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D34" s="4" t="n">
+      <c r="D34" s="5" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E34" s="4" t="n">
+      <c r="E34" s="5" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F34" s="4" t="n">
+      <c r="F34" s="5" t="n">
         <v>1.5</v>
       </c>
-      <c r="G34" s="4" t="n">
+      <c r="G34" s="5" t="n">
         <v>2.2</v>
       </c>
-      <c r="H34" s="4" t="n">
+      <c r="H34" s="5" t="n">
         <v>-9.4</v>
       </c>
       <c r="I34" t="n">
         <v>6</v>
       </c>
-      <c r="J34" s="4" t="n">
+      <c r="J34" s="5" t="n">
         <v>3.5</v>
       </c>
       <c r="K34" t="n">
         <v>10</v>
       </c>
-      <c r="L34" s="4" t="n">
+      <c r="L34" s="5" t="n">
         <v>29.7</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
       </c>
-      <c r="N34" s="4" t="n">
+      <c r="N34" s="5" t="n">
         <v>3.8</v>
       </c>
       <c r="O34" t="n">
         <v>2</v>
       </c>
-      <c r="P34" s="4" t="n">
+      <c r="P34" s="5" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q34" t="n">
         <v>8</v>
       </c>
-      <c r="R34" s="4" t="n">
+      <c r="R34" s="5" t="n">
         <v>-3.8</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
       </c>
-      <c r="T34" s="4" t="n">
+      <c r="T34" s="5" t="n">
         <v>17.5</v>
       </c>
       <c r="U34" t="n">
@@ -5778,55 +5785,55 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D35" s="4" t="n">
+      <c r="D35" s="5" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E35" s="4" t="n">
+      <c r="E35" s="5" t="n">
         <v>4</v>
       </c>
-      <c r="F35" s="4" t="n">
+      <c r="F35" s="5" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="4" t="n">
+      <c r="G35" s="5" t="n">
         <v>-16.1</v>
       </c>
-      <c r="H35" s="4" t="n">
+      <c r="H35" s="5" t="n">
         <v>-22.9</v>
       </c>
       <c r="I35" t="n">
         <v>13</v>
       </c>
-      <c r="J35" s="4" t="n">
+      <c r="J35" s="5" t="n">
         <v>-13</v>
       </c>
       <c r="K35" t="n">
         <v>13</v>
       </c>
-      <c r="L35" s="4" t="n">
+      <c r="L35" s="5" t="n">
         <v>-11</v>
       </c>
       <c r="M35" t="n">
         <v>11</v>
       </c>
-      <c r="N35" s="4" t="n">
+      <c r="N35" s="5" t="n">
         <v>-18.6</v>
       </c>
       <c r="O35" t="n">
         <v>10</v>
       </c>
-      <c r="P35" s="4" t="n">
+      <c r="P35" s="5" t="n">
         <v>-11.9</v>
       </c>
       <c r="Q35" t="n">
         <v>3</v>
       </c>
-      <c r="R35" s="4" t="n">
+      <c r="R35" s="5" t="n">
         <v>-3</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
       </c>
-      <c r="T35" s="4" t="n">
+      <c r="T35" s="5" t="n">
         <v>302.8</v>
       </c>
       <c r="U35" t="n">
@@ -5849,55 +5856,55 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D36" s="4" t="n">
+      <c r="D36" s="5" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E36" s="4" t="n">
+      <c r="E36" s="5" t="n">
         <v>3.3</v>
       </c>
-      <c r="F36" s="4" t="n">
+      <c r="F36" s="5" t="n">
         <v>2.8</v>
       </c>
-      <c r="G36" s="4" t="n">
+      <c r="G36" s="5" t="n">
         <v>-13.2</v>
       </c>
-      <c r="H36" s="4" t="n">
+      <c r="H36" s="5" t="n">
         <v>-17.7</v>
       </c>
       <c r="I36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" s="4" t="n">
+      <c r="J36" s="5" t="n">
         <v>-2.9</v>
       </c>
       <c r="K36" t="n">
         <v>12</v>
       </c>
-      <c r="L36" s="4" t="n">
+      <c r="L36" s="5" t="n">
         <v>-4.2</v>
       </c>
       <c r="M36" t="n">
         <v>10</v>
       </c>
-      <c r="N36" s="4" t="n">
+      <c r="N36" s="5" t="n">
         <v>-18.3</v>
       </c>
       <c r="O36" t="n">
         <v>9</v>
       </c>
-      <c r="P36" s="4" t="n">
+      <c r="P36" s="5" t="n">
         <v>-13.4</v>
       </c>
       <c r="Q36" t="n">
         <v>4</v>
       </c>
-      <c r="R36" s="4" t="n">
+      <c r="R36" s="5" t="n">
         <v>-7.5</v>
       </c>
       <c r="S36" t="n">
         <v>12</v>
       </c>
-      <c r="T36" s="4" t="n">
+      <c r="T36" s="5" t="n">
         <v>72.7</v>
       </c>
       <c r="U36" t="n">
@@ -5920,55 +5927,55 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D37" s="4" t="n">
+      <c r="D37" s="5" t="n">
         <v>-3</v>
       </c>
-      <c r="E37" s="4" t="n">
+      <c r="E37" s="5" t="n">
         <v>-7.1</v>
       </c>
-      <c r="F37" s="4" t="n">
+      <c r="F37" s="5" t="n">
         <v>-20.1</v>
       </c>
-      <c r="G37" s="4" t="n">
+      <c r="G37" s="5" t="n">
         <v>-21</v>
       </c>
-      <c r="H37" s="4" t="n">
+      <c r="H37" s="5" t="n">
         <v>-17</v>
       </c>
       <c r="I37" t="n">
         <v>8</v>
       </c>
-      <c r="J37" s="4" t="n">
+      <c r="J37" s="5" t="n">
         <v>56.6</v>
       </c>
       <c r="K37" t="n">
         <v>3</v>
       </c>
-      <c r="L37" s="4" t="n">
+      <c r="L37" s="5" t="n">
         <v>0.3</v>
       </c>
       <c r="M37" t="n">
         <v>8</v>
       </c>
-      <c r="N37" s="4" t="n">
+      <c r="N37" s="5" t="n">
         <v>-29</v>
       </c>
       <c r="O37" t="n">
         <v>12</v>
       </c>
-      <c r="P37" s="4" t="n">
+      <c r="P37" s="5" t="n">
         <v>-28.9</v>
       </c>
       <c r="Q37" t="n">
         <v>10</v>
       </c>
-      <c r="R37" s="4" t="n">
+      <c r="R37" s="5" t="n">
         <v>41.9</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
       </c>
-      <c r="T37" s="4" t="inlineStr"/>
+      <c r="T37" s="5" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -5987,55 +5994,55 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="4" t="n">
+      <c r="D38" s="5" t="n">
         <v>-3.5</v>
       </c>
-      <c r="E38" s="4" t="n">
+      <c r="E38" s="5" t="n">
         <v>-11.1</v>
       </c>
-      <c r="F38" s="4" t="n">
+      <c r="F38" s="5" t="n">
         <v>-22.4</v>
       </c>
-      <c r="G38" s="4" t="n">
+      <c r="G38" s="5" t="n">
         <v>-24.7</v>
       </c>
-      <c r="H38" s="4" t="n">
+      <c r="H38" s="5" t="n">
         <v>-17.2</v>
       </c>
       <c r="I38" t="n">
         <v>9</v>
       </c>
-      <c r="J38" s="4" t="n">
+      <c r="J38" s="5" t="n">
         <v>27.1</v>
       </c>
       <c r="K38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="4" t="n">
+      <c r="L38" s="5" t="n">
         <v>-14.9</v>
       </c>
       <c r="M38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="4" t="n">
+      <c r="N38" s="5" t="n">
         <v>-35.2</v>
       </c>
       <c r="O38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="4" t="n">
+      <c r="P38" s="5" t="n">
         <v>-19.7</v>
       </c>
       <c r="Q38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="4" t="n">
+      <c r="R38" s="5" t="n">
         <v>50.7</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="4" t="inlineStr"/>
+      <c r="T38" s="5" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -6054,55 +6061,55 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D39" s="4" t="n">
+      <c r="D39" s="5" t="n">
         <v>-3.7</v>
       </c>
-      <c r="E39" s="4" t="n">
+      <c r="E39" s="5" t="n">
         <v>0.3</v>
       </c>
-      <c r="F39" s="4" t="n">
+      <c r="F39" s="5" t="n">
         <v>12.7</v>
       </c>
-      <c r="G39" s="4" t="n">
+      <c r="G39" s="5" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H39" s="4" t="n">
+      <c r="H39" s="5" t="n">
         <v>-3.7</v>
       </c>
       <c r="I39" t="n">
         <v>4</v>
       </c>
-      <c r="J39" s="4" t="n">
+      <c r="J39" s="5" t="n">
         <v>4.7</v>
       </c>
       <c r="K39" t="n">
         <v>9</v>
       </c>
-      <c r="L39" s="4" t="n">
+      <c r="L39" s="5" t="n">
         <v>-12.2</v>
       </c>
       <c r="M39" t="n">
         <v>12</v>
       </c>
-      <c r="N39" s="4" t="n">
+      <c r="N39" s="5" t="n">
         <v>-14</v>
       </c>
       <c r="O39" t="n">
         <v>8</v>
       </c>
-      <c r="P39" s="4" t="n">
+      <c r="P39" s="5" t="n">
         <v>-24.5</v>
       </c>
       <c r="Q39" t="n">
         <v>7</v>
       </c>
-      <c r="R39" s="4" t="n">
+      <c r="R39" s="5" t="n">
         <v>-15.7</v>
       </c>
       <c r="S39" t="n">
         <v>13</v>
       </c>
-      <c r="T39" s="4" t="n">
+      <c r="T39" s="5" t="n">
         <v>58.4</v>
       </c>
       <c r="U39" t="n">
@@ -6125,55 +6132,55 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D40" s="4" t="n">
+      <c r="D40" s="5" t="n">
         <v>-4.4</v>
       </c>
-      <c r="E40" s="4" t="n">
+      <c r="E40" s="5" t="n">
         <v>-4.9</v>
       </c>
-      <c r="F40" s="4" t="n">
+      <c r="F40" s="5" t="n">
         <v>-8</v>
       </c>
-      <c r="G40" s="4" t="n">
+      <c r="G40" s="5" t="n">
         <v>-16</v>
       </c>
-      <c r="H40" s="4" t="n">
+      <c r="H40" s="5" t="n">
         <v>-22.8</v>
       </c>
       <c r="I40" t="n">
         <v>12</v>
       </c>
-      <c r="J40" s="4" t="n">
+      <c r="J40" s="5" t="n">
         <v>2.5</v>
       </c>
       <c r="K40" t="n">
         <v>11</v>
       </c>
-      <c r="L40" s="4" t="n">
+      <c r="L40" s="5" t="n">
         <v>-0.5</v>
       </c>
       <c r="M40" t="n">
         <v>9</v>
       </c>
-      <c r="N40" s="4" t="n">
+      <c r="N40" s="5" t="n">
         <v>-27</v>
       </c>
       <c r="O40" t="n">
         <v>11</v>
       </c>
-      <c r="P40" s="4" t="n">
+      <c r="P40" s="5" t="n">
         <v>-10.4</v>
       </c>
       <c r="Q40" t="n">
         <v>2</v>
       </c>
-      <c r="R40" s="4" t="n">
+      <c r="R40" s="5" t="n">
         <v>-6.4</v>
       </c>
       <c r="S40" t="n">
         <v>11</v>
       </c>
-      <c r="T40" s="4" t="n">
+      <c r="T40" s="5" t="n">
         <v>-6.6</v>
       </c>
       <c r="U40" t="n">
@@ -6196,55 +6203,55 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D41" s="4" t="n">
+      <c r="D41" s="5" t="n">
         <v>-5.2</v>
       </c>
-      <c r="E41" s="4" t="n">
+      <c r="E41" s="5" t="n">
         <v>-17.1</v>
       </c>
-      <c r="F41" s="4" t="n">
+      <c r="F41" s="5" t="n">
         <v>-17.6</v>
       </c>
-      <c r="G41" s="4" t="n">
+      <c r="G41" s="5" t="n">
         <v>-22.3</v>
       </c>
-      <c r="H41" s="4" t="n">
+      <c r="H41" s="5" t="n">
         <v>-22.7</v>
       </c>
       <c r="I41" t="n">
         <v>11</v>
       </c>
-      <c r="J41" s="4" t="n">
+      <c r="J41" s="5" t="n">
         <v>31.8</v>
       </c>
       <c r="K41" t="n">
         <v>6</v>
       </c>
-      <c r="L41" s="4" t="n">
+      <c r="L41" s="5" t="n">
         <v>8.5</v>
       </c>
       <c r="M41" t="n">
         <v>6</v>
       </c>
-      <c r="N41" s="4" t="n">
+      <c r="N41" s="5" t="n">
         <v>-10.8</v>
       </c>
       <c r="O41" t="n">
         <v>6</v>
       </c>
-      <c r="P41" s="4" t="n">
+      <c r="P41" s="5" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q41" t="n">
         <v>8</v>
       </c>
-      <c r="R41" s="4" t="n">
+      <c r="R41" s="5" t="n">
         <v>13.1</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
       </c>
-      <c r="T41" s="4" t="n">
+      <c r="T41" s="5" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="U41" t="n">
@@ -6267,55 +6274,55 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D42" s="4" t="n">
+      <c r="D42" s="5" t="n">
         <v>-5.2</v>
       </c>
-      <c r="E42" s="4" t="n">
+      <c r="E42" s="5" t="n">
         <v>-6.8</v>
       </c>
-      <c r="F42" s="4" t="n">
+      <c r="F42" s="5" t="n">
         <v>-20</v>
       </c>
-      <c r="G42" s="4" t="n">
+      <c r="G42" s="5" t="n">
         <v>-22.2</v>
       </c>
-      <c r="H42" s="4" t="n">
+      <c r="H42" s="5" t="n">
         <v>-15.1</v>
       </c>
       <c r="I42" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="4" t="n">
+      <c r="J42" s="5" t="n">
         <v>101.1</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" s="4" t="n">
+      <c r="L42" s="5" t="n">
         <v>4.1</v>
       </c>
       <c r="M42" t="n">
         <v>7</v>
       </c>
-      <c r="N42" s="4" t="n">
+      <c r="N42" s="5" t="n">
         <v>-11.4</v>
       </c>
       <c r="O42" t="n">
         <v>7</v>
       </c>
-      <c r="P42" s="4" t="n">
+      <c r="P42" s="5" t="n">
         <v>-21.6</v>
       </c>
       <c r="Q42" t="n">
         <v>6</v>
       </c>
-      <c r="R42" s="4" t="n">
+      <c r="R42" s="5" t="n">
         <v>33.2</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
       </c>
-      <c r="T42" s="4" t="n">
+      <c r="T42" s="5" t="n">
         <v>41.8</v>
       </c>
       <c r="U42" t="n">
@@ -6338,55 +6345,55 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D43" s="4" t="n">
+      <c r="D43" s="5" t="n">
         <v>-7.7</v>
       </c>
-      <c r="E43" s="4" t="n">
+      <c r="E43" s="5" t="n">
         <v>-21.8</v>
       </c>
-      <c r="F43" s="4" t="n">
+      <c r="F43" s="5" t="n">
         <v>-10.4</v>
       </c>
-      <c r="G43" s="4" t="n">
+      <c r="G43" s="5" t="n">
         <v>33.9</v>
       </c>
-      <c r="H43" s="4" t="n">
+      <c r="H43" s="5" t="n">
         <v>46.2</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="4" t="n">
+      <c r="J43" s="5" t="n">
         <v>45</v>
       </c>
       <c r="K43" t="n">
         <v>5</v>
       </c>
-      <c r="L43" s="4" t="n">
+      <c r="L43" s="5" t="n">
         <v>25.6</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
-      <c r="N43" s="4" t="n">
+      <c r="N43" s="5" t="n">
         <v>-2.4</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
-      <c r="P43" s="4" t="n">
+      <c r="P43" s="5" t="n">
         <v>-36.6</v>
       </c>
       <c r="Q43" t="n">
         <v>12</v>
       </c>
-      <c r="R43" s="4" t="n">
+      <c r="R43" s="5" t="n">
         <v>23.8</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
       </c>
-      <c r="T43" s="4" t="n">
+      <c r="T43" s="5" t="n">
         <v>46.2</v>
       </c>
       <c r="U43" t="n">
@@ -6409,55 +6416,55 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D44" s="4" t="n">
+      <c r="D44" s="5" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="E44" s="4" t="n">
+      <c r="E44" s="5" t="n">
         <v>-16.8</v>
       </c>
-      <c r="F44" s="4" t="n">
+      <c r="F44" s="5" t="n">
         <v>-14.4</v>
       </c>
-      <c r="G44" s="4" t="n">
+      <c r="G44" s="5" t="n">
         <v>18.5</v>
       </c>
-      <c r="H44" s="4" t="n">
+      <c r="H44" s="5" t="n">
         <v>29.1</v>
       </c>
       <c r="I44" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="4" t="n">
+      <c r="J44" s="5" t="n">
         <v>52.1</v>
       </c>
       <c r="K44" t="n">
         <v>4</v>
       </c>
-      <c r="L44" s="4" t="n">
+      <c r="L44" s="5" t="n">
         <v>12</v>
       </c>
       <c r="M44" t="n">
         <v>5</v>
       </c>
-      <c r="N44" s="4" t="n">
+      <c r="N44" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
       </c>
-      <c r="P44" s="4" t="n">
+      <c r="P44" s="5" t="n">
         <v>-34</v>
       </c>
       <c r="Q44" t="n">
         <v>11</v>
       </c>
-      <c r="R44" s="4" t="n">
+      <c r="R44" s="5" t="n">
         <v>-2.8</v>
       </c>
       <c r="S44" t="n">
         <v>8</v>
       </c>
-      <c r="T44" s="4" t="n">
+      <c r="T44" s="5" t="n">
         <v>44</v>
       </c>
       <c r="U44" t="n">
@@ -6480,55 +6487,55 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D45" s="4" t="n">
+      <c r="D45" s="5" t="n">
         <v>-10</v>
       </c>
-      <c r="E45" s="4" t="n">
+      <c r="E45" s="5" t="n">
         <v>-13.8</v>
       </c>
-      <c r="F45" s="4" t="n">
+      <c r="F45" s="5" t="n">
         <v>-20.9</v>
       </c>
-      <c r="G45" s="4" t="n">
+      <c r="G45" s="5" t="n">
         <v>17.6</v>
       </c>
-      <c r="H45" s="4" t="n">
+      <c r="H45" s="5" t="n">
         <v>38.9</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="4" t="n">
+      <c r="J45" s="5" t="n">
         <v>99.7</v>
       </c>
       <c r="K45" t="n">
         <v>2</v>
       </c>
-      <c r="L45" s="4" t="n">
+      <c r="L45" s="5" t="n">
         <v>24.2</v>
       </c>
       <c r="M45" t="n">
         <v>4</v>
       </c>
-      <c r="N45" s="4" t="n">
+      <c r="N45" s="5" t="n">
         <v>16.3</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="P45" s="4" t="n">
+      <c r="P45" s="5" t="n">
         <v>-37.8</v>
       </c>
       <c r="Q45" t="n">
         <v>13</v>
       </c>
-      <c r="R45" s="4" t="n">
+      <c r="R45" s="5" t="n">
         <v>6.8</v>
       </c>
       <c r="S45" t="n">
         <v>6</v>
       </c>
-      <c r="T45" s="4" t="n">
+      <c r="T45" s="5" t="n">
         <v>19.3</v>
       </c>
       <c r="U45" t="n">
@@ -6771,12 +6778,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6819,15 +6826,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>3Q 매출 가이던스 컨센 하회+참여도 공시 축소에 -7%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6866,15 +6877,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>2Q 실적 미스+호주 제련소 사고로 알루미나 가이던스 하향</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6919,15 +6934,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>개별 촉매 없이 바이오 섹터 매도세 속 52주 신저가</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -6968,15 +6987,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>AI데이터센터·비트코인 채굴주 동반 급락, 6일 연속 하락</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7017,15 +7040,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>$1.65B Superior 인수 후 레버리지 우려·차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7069,12 +7096,12 @@
       <c r="M7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7118,12 +7145,12 @@
       <c r="M8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7167,12 +7194,12 @@
       <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7216,12 +7243,12 @@
       <c r="M10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7265,12 +7292,12 @@
       <c r="M11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7314,12 +7341,12 @@
       <c r="M12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7363,12 +7390,12 @@
       <c r="M13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7412,12 +7439,12 @@
       <c r="M14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7461,12 +7488,12 @@
       <c r="M15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7510,12 +7537,12 @@
       <c r="M16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7559,12 +7586,12 @@
       <c r="M17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7608,12 +7635,12 @@
       <c r="M18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7657,12 +7684,12 @@
       <c r="M19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7706,12 +7733,12 @@
       <c r="M20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7753,12 +7780,12 @@
       <c r="M21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7802,12 +7829,12 @@
       <c r="M22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7851,12 +7878,12 @@
       <c r="M23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7900,12 +7927,12 @@
       <c r="M24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7949,12 +7976,12 @@
       <c r="M25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -7998,12 +8025,12 @@
       <c r="M26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8047,12 +8074,12 @@
       <c r="M27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8096,12 +8123,12 @@
       <c r="M28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8145,12 +8172,12 @@
       <c r="M29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8192,12 +8219,12 @@
       <c r="M30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8241,12 +8268,12 @@
       <c r="M31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B32" s="5" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8290,12 +8317,12 @@
       <c r="M32" s="6" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B33" s="5" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8339,12 +8366,12 @@
       <c r="M33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B34" s="5" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8388,12 +8415,12 @@
       <c r="M34" s="6" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B35" s="5" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8437,12 +8464,12 @@
       <c r="M35" s="6" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B36" s="5" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8486,12 +8513,12 @@
       <c r="M36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B37" s="5" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8535,12 +8562,12 @@
       <c r="M37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B38" s="5" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8584,12 +8611,12 @@
       <c r="M38" s="6" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B39" s="5" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8631,12 +8658,12 @@
       <c r="M39" s="6" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B40" s="5" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8680,12 +8707,12 @@
       <c r="M40" s="6" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B41" s="5" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8727,12 +8754,12 @@
       <c r="M41" s="6" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B42" s="5" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8776,12 +8803,12 @@
       <c r="M42" s="6" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8825,12 +8852,12 @@
       <c r="M43" s="6" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8874,12 +8901,12 @@
       <c r="M44" s="6" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
+      <c r="A45" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B45" s="5" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8923,12 +8950,12 @@
       <c r="M45" s="6" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="3" t="inlineStr">
+      <c r="A46" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B46" s="5" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -8972,12 +8999,12 @@
       <c r="M46" s="6" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="3" t="inlineStr">
+      <c r="A47" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B47" s="5" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9025,12 +9052,12 @@
       <c r="M47" s="6" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="A48" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B48" s="5" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9074,12 +9101,12 @@
       <c r="M48" s="6" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
+      <c r="A49" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B49" s="5" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9123,12 +9150,12 @@
       <c r="M49" s="6" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="3" t="inlineStr">
+      <c r="A50" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B50" s="5" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9170,7 +9197,7 @@
       <c r="M50" s="6" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr">
+      <c r="A51" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9225,7 +9252,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="3" t="inlineStr">
+      <c r="A52" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9278,7 +9305,7 @@
       <c r="M52" s="6" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
+      <c r="A53" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9329,7 +9356,7 @@
       <c r="M53" s="6" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
+      <c r="A54" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9382,7 +9409,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="3" t="inlineStr">
+      <c r="A55" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9431,7 +9458,7 @@
       <c r="M55" s="6" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="3" t="inlineStr">
+      <c r="A56" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9482,7 +9509,7 @@
       <c r="M56" s="6" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="3" t="inlineStr">
+      <c r="A57" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9533,7 +9560,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="3" t="inlineStr">
+      <c r="A58" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9582,7 +9609,7 @@
       <c r="M58" s="6" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="3" t="inlineStr">
+      <c r="A59" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9631,7 +9658,7 @@
       <c r="M59" s="6" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="3" t="inlineStr">
+      <c r="A60" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9684,7 +9711,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="3" t="inlineStr">
+      <c r="A61" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9735,7 +9762,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
+      <c r="A62" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9784,7 +9811,7 @@
       <c r="M62" s="6" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="3" t="inlineStr">
+      <c r="A63" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9831,12 +9858,12 @@
       <c r="M63" s="6" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B64" s="5" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9881,15 +9908,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M64" s="6" t="inlineStr"/>
+      <c r="M64" s="6" t="inlineStr">
+        <is>
+          <t>2Q EPS $10.04(예상 $5.34) 대폭 서프라이즈, 재해손실 감소 +8%</t>
+        </is>
+      </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+      <c r="A65" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B65" s="5" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9934,15 +9965,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M65" s="6" t="inlineStr"/>
+      <c r="M65" s="6" t="inlineStr">
+        <is>
+          <t>General Mills·월마트 재생농업 제휴 발표+BMO 목표가 상향</t>
+        </is>
+      </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+      <c r="A66" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B66" s="5" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -9987,15 +10022,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M66" s="6" t="inlineStr"/>
+      <c r="M66" s="6" t="inlineStr">
+        <is>
+          <t>정제마진 강세 지속, 애널리스트 목표가 상향 랠리</t>
+        </is>
+      </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+      <c r="A67" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B67" s="5" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10040,15 +10079,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr"/>
+      <c r="M67" s="6" t="inlineStr">
+        <is>
+          <t>정제 업황 호조, Raymond James TP $235 상향·정유 동반 강세</t>
+        </is>
+      </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+      <c r="A68" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B68" s="5" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10093,15 +10136,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M68" s="6" t="inlineStr"/>
+      <c r="M68" s="6" t="inlineStr">
+        <is>
+          <t>정유·에너지 섹터 강세 동반(개별 뉴스 미확인)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+      <c r="A69" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B69" s="5" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10145,12 +10192,12 @@
       <c r="M69" s="6" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+      <c r="A70" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B70" s="5" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10198,12 +10245,12 @@
       <c r="M70" s="6" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+      <c r="A71" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B71" s="5" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10247,12 +10294,12 @@
       <c r="M71" s="6" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+      <c r="A72" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B72" s="5" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10300,12 +10347,12 @@
       <c r="M72" s="6" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+      <c r="A73" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B73" s="5" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10347,12 +10394,12 @@
       <c r="M73" s="6" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+      <c r="A74" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B74" s="5" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10398,12 +10445,12 @@
       <c r="M74" s="6" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+      <c r="A75" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B75" s="5" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10451,12 +10498,12 @@
       <c r="M75" s="6" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+      <c r="A76" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B76" s="5" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10502,12 +10549,12 @@
       <c r="M76" s="6" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+      <c r="A77" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B77" s="5" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10555,12 +10602,12 @@
       <c r="M77" s="6" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+      <c r="A78" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B78" s="5" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10608,12 +10655,12 @@
       <c r="M78" s="6" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+      <c r="A79" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B79" s="5" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10661,12 +10708,12 @@
       <c r="M79" s="6" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+      <c r="A80" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B80" s="5" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10714,12 +10761,12 @@
       <c r="M80" s="6" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+      <c r="A81" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B81" s="5" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10767,12 +10814,12 @@
       <c r="M81" s="6" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+      <c r="A82" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B82" s="5" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10820,12 +10867,12 @@
       <c r="M82" s="6" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+      <c r="A83" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B83" s="5" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10873,12 +10920,12 @@
       <c r="M83" s="6" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+      <c r="A84" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B84" s="5" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10926,12 +10973,12 @@
       <c r="M84" s="6" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+      <c r="A85" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B85" s="5" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -10979,12 +11026,12 @@
       <c r="M85" s="6" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+      <c r="A86" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B86" s="5" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11030,12 +11077,12 @@
       <c r="M86" s="6" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+      <c r="A87" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B87" s="5" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11083,12 +11130,12 @@
       <c r="M87" s="6" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+      <c r="A88" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B88" s="5" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11136,12 +11183,12 @@
       <c r="M88" s="6" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+      <c r="A89" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B89" s="5" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11189,12 +11236,12 @@
       <c r="M89" s="6" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+      <c r="A90" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B90" s="5" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11242,12 +11289,12 @@
       <c r="M90" s="6" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+      <c r="A91" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B91" s="5" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11295,12 +11342,12 @@
       <c r="M91" s="6" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+      <c r="A92" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B92" s="5" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11348,12 +11395,12 @@
       <c r="M92" s="6" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+      <c r="A93" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B93" s="5" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11397,12 +11444,12 @@
       <c r="M93" s="6" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+      <c r="A94" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B94" s="5" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11450,12 +11497,12 @@
       <c r="M94" s="6" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+      <c r="A95" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B95" s="5" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11503,12 +11550,12 @@
       <c r="M95" s="6" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+      <c r="A96" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B96" s="5" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11556,12 +11603,12 @@
       <c r="M96" s="6" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+      <c r="A97" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B97" s="5" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11609,12 +11656,12 @@
       <c r="M97" s="6" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+      <c r="A98" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B98" s="5" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11662,12 +11709,12 @@
       <c r="M98" s="6" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+      <c r="A99" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B99" s="5" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11715,12 +11762,12 @@
       <c r="M99" s="6" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+      <c r="A100" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B100" s="5" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11768,12 +11815,12 @@
       <c r="M100" s="6" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+      <c r="A101" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B101" s="5" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11821,12 +11868,12 @@
       <c r="M101" s="6" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+      <c r="A102" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B102" s="5" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11870,12 +11917,12 @@
       <c r="M102" s="6" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B103" s="5" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11923,12 +11970,12 @@
       <c r="M103" s="6" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+      <c r="A104" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B104" s="5" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -11972,12 +12019,12 @@
       <c r="M104" s="6" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+      <c r="A105" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B105" s="5" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12025,12 +12072,12 @@
       <c r="M105" s="6" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+      <c r="A106" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B106" s="5" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12074,12 +12121,12 @@
       <c r="M106" s="6" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+      <c r="A107" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B107" s="5" t="inlineStr">
+      <c r="B107" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12123,12 +12170,12 @@
       <c r="M107" s="6" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+      <c r="A108" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B108" s="5" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12174,12 +12221,12 @@
       <c r="M108" s="6" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+      <c r="A109" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B109" s="5" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12225,12 +12272,12 @@
       <c r="M109" s="6" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+      <c r="A110" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B110" s="5" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12274,12 +12321,12 @@
       <c r="M110" s="6" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+      <c r="A111" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B111" s="5" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12327,12 +12374,12 @@
       <c r="M111" s="6" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+      <c r="A112" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B112" s="5" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12380,12 +12427,12 @@
       <c r="M112" s="6" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+      <c r="A113" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B113" s="5" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12429,12 +12476,12 @@
       <c r="M113" s="6" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+      <c r="A114" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B114" s="5" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12478,12 +12525,12 @@
       <c r="M114" s="6" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+      <c r="A115" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B115" s="5" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12527,12 +12574,12 @@
       <c r="M115" s="6" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+      <c r="A116" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B116" s="5" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12576,12 +12623,12 @@
       <c r="M116" s="6" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+      <c r="A117" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B117" s="5" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12629,12 +12676,12 @@
       <c r="M117" s="6" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+      <c r="A118" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B118" s="5" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12676,12 +12723,12 @@
       <c r="M118" s="6" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+      <c r="A119" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B119" s="5" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12725,12 +12772,12 @@
       <c r="M119" s="6" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+      <c r="A120" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B120" s="5" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12778,12 +12825,12 @@
       <c r="M120" s="6" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+      <c r="A121" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B121" s="5" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12831,12 +12878,12 @@
       <c r="M121" s="6" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+      <c r="A122" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B122" s="5" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12884,12 +12931,12 @@
       <c r="M122" s="6" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+      <c r="A123" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B123" s="5" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12933,12 +12980,12 @@
       <c r="M123" s="6" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+      <c r="A124" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B124" s="5" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -12986,12 +13033,12 @@
       <c r="M124" s="6" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+      <c r="A125" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B125" s="5" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13035,12 +13082,12 @@
       <c r="M125" s="6" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+      <c r="A126" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B126" s="5" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13084,12 +13131,12 @@
       <c r="M126" s="6" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+      <c r="A127" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B127" s="5" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13133,12 +13180,12 @@
       <c r="M127" s="6" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+      <c r="A128" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B128" s="5" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13182,12 +13229,12 @@
       <c r="M128" s="6" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+      <c r="A129" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B129" s="5" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13235,12 +13282,12 @@
       <c r="M129" s="6" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+      <c r="A130" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B130" s="5" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13288,12 +13335,12 @@
       <c r="M130" s="6" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+      <c r="A131" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B131" s="5" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13341,12 +13388,12 @@
       <c r="M131" s="6" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+      <c r="A132" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B132" s="5" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13390,12 +13437,12 @@
       <c r="M132" s="6" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+      <c r="A133" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B133" s="5" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13439,12 +13486,12 @@
       <c r="M133" s="6" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+      <c r="A134" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B134" s="5" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13488,12 +13535,12 @@
       <c r="M134" s="6" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+      <c r="A135" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B135" s="5" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13537,12 +13584,12 @@
       <c r="M135" s="6" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+      <c r="A136" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B136" s="5" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13586,12 +13633,12 @@
       <c r="M136" s="6" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+      <c r="A137" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B137" s="5" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13635,12 +13682,12 @@
       <c r="M137" s="6" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+      <c r="A138" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B138" s="5" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13684,12 +13731,12 @@
       <c r="M138" s="6" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+      <c r="A139" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B139" s="5" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13733,12 +13780,12 @@
       <c r="M139" s="6" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+      <c r="A140" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B140" s="5" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13782,12 +13829,12 @@
       <c r="M140" s="6" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+      <c r="A141" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B141" s="5" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13831,12 +13878,12 @@
       <c r="M141" s="6" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+      <c r="A142" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B142" s="5" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13884,12 +13931,12 @@
       <c r="M142" s="6" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+      <c r="A143" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B143" s="5" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13935,12 +13982,12 @@
       <c r="M143" s="6" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+      <c r="A144" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B144" s="5" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -13988,12 +14035,12 @@
       <c r="M144" s="6" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+      <c r="A145" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B145" s="5" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14037,12 +14084,12 @@
       <c r="M145" s="6" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+      <c r="A146" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B146" s="5" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14086,12 +14133,12 @@
       <c r="M146" s="6" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+      <c r="A147" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B147" s="5" t="inlineStr">
+      <c r="B147" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14139,12 +14186,12 @@
       <c r="M147" s="6" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+      <c r="A148" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B148" s="5" t="inlineStr">
+      <c r="B148" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14188,12 +14235,12 @@
       <c r="M148" s="6" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+      <c r="A149" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B149" s="5" t="inlineStr">
+      <c r="B149" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14237,12 +14284,12 @@
       <c r="M149" s="6" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="2" t="inlineStr">
+      <c r="A150" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B150" s="5" t="inlineStr">
+      <c r="B150" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14286,12 +14333,12 @@
       <c r="M150" s="6" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="2" t="inlineStr">
+      <c r="A151" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B151" s="5" t="inlineStr">
+      <c r="B151" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14339,12 +14386,12 @@
       <c r="M151" s="6" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="2" t="inlineStr">
+      <c r="A152" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B152" s="5" t="inlineStr">
+      <c r="B152" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14392,12 +14439,12 @@
       <c r="M152" s="6" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="2" t="inlineStr">
+      <c r="A153" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B153" s="5" t="inlineStr">
+      <c r="B153" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14439,12 +14486,12 @@
       <c r="M153" s="6" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="2" t="inlineStr">
+      <c r="A154" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B154" s="5" t="inlineStr">
+      <c r="B154" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14488,12 +14535,12 @@
       <c r="M154" s="6" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="2" t="inlineStr">
+      <c r="A155" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B155" s="5" t="inlineStr">
+      <c r="B155" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14537,12 +14584,12 @@
       <c r="M155" s="6" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="2" t="inlineStr">
+      <c r="A156" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B156" s="5" t="inlineStr">
+      <c r="B156" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14586,12 +14633,12 @@
       <c r="M156" s="6" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="2" t="inlineStr">
+      <c r="A157" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B157" s="5" t="inlineStr">
+      <c r="B157" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14639,12 +14686,12 @@
       <c r="M157" s="6" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="2" t="inlineStr">
+      <c r="A158" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B158" s="5" t="inlineStr">
+      <c r="B158" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14688,12 +14735,12 @@
       <c r="M158" s="6" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="2" t="inlineStr">
+      <c r="A159" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B159" s="5" t="inlineStr">
+      <c r="B159" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14739,12 +14786,12 @@
       <c r="M159" s="6" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="2" t="inlineStr">
+      <c r="A160" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B160" s="5" t="inlineStr">
+      <c r="B160" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14788,12 +14835,12 @@
       <c r="M160" s="6" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="2" t="inlineStr">
+      <c r="A161" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B161" s="5" t="inlineStr">
+      <c r="B161" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14841,12 +14888,12 @@
       <c r="M161" s="6" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="2" t="inlineStr">
+      <c r="A162" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B162" s="5" t="inlineStr">
+      <c r="B162" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -14888,7 +14935,7 @@
       <c r="M162" s="6" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="2" t="inlineStr">
+      <c r="A163" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14941,7 +14988,7 @@
       <c r="M163" s="6" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="2" t="inlineStr">
+      <c r="A164" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14994,7 +15041,7 @@
       <c r="M164" s="6" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="2" t="inlineStr">
+      <c r="A165" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15047,7 +15094,7 @@
       <c r="M165" s="6" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="2" t="inlineStr">
+      <c r="A166" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15100,7 +15147,7 @@
       <c r="M166" s="6" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="2" t="inlineStr">
+      <c r="A167" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15153,7 +15200,7 @@
       <c r="M167" s="6" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="2" t="inlineStr">
+      <c r="A168" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15206,7 +15253,7 @@
       <c r="M168" s="6" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="2" t="inlineStr">
+      <c r="A169" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15259,7 +15306,7 @@
       <c r="M169" s="6" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="2" t="inlineStr">
+      <c r="A170" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15312,7 +15359,7 @@
       <c r="M170" s="6" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="2" t="inlineStr">
+      <c r="A171" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15361,7 +15408,7 @@
       <c r="M171" s="6" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="2" t="inlineStr">
+      <c r="A172" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15410,7 +15457,7 @@
       <c r="M172" s="6" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="2" t="inlineStr">
+      <c r="A173" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15463,7 +15510,7 @@
       <c r="M173" s="6" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="2" t="inlineStr">
+      <c r="A174" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15516,7 +15563,7 @@
       <c r="M174" s="6" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="2" t="inlineStr">
+      <c r="A175" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15569,7 +15616,7 @@
       <c r="M175" s="6" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="2" t="inlineStr">
+      <c r="A176" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15626,7 +15673,7 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="2" t="inlineStr">
+      <c r="A177" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15679,7 +15726,7 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="2" t="inlineStr">
+      <c r="A178" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15732,7 +15779,7 @@
       <c r="M178" s="6" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="2" t="inlineStr">
+      <c r="A179" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15781,7 +15828,7 @@
       <c r="M179" s="6" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="2" t="inlineStr">
+      <c r="A180" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15834,7 +15881,7 @@
       <c r="M180" s="6" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="2" t="inlineStr">
+      <c r="A181" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15887,7 +15934,7 @@
       <c r="M181" s="6" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="2" t="inlineStr">
+      <c r="A182" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15936,7 +15983,7 @@
       <c r="M182" s="6" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="2" t="inlineStr">
+      <c r="A183" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15983,7 +16030,7 @@
       <c r="M183" s="6" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="2" t="inlineStr">
+      <c r="A184" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16032,7 +16079,7 @@
       <c r="M184" s="6" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="2" t="inlineStr">
+      <c r="A185" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16081,7 +16128,7 @@
       <c r="M185" s="6" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="2" t="inlineStr">
+      <c r="A186" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16130,7 +16177,7 @@
       <c r="M186" s="6" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="2" t="inlineStr">
+      <c r="A187" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16179,7 +16226,7 @@
       <c r="M187" s="6" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="2" t="inlineStr">
+      <c r="A188" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16232,7 +16279,7 @@
       <c r="M188" s="6" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="2" t="inlineStr">
+      <c r="A189" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16279,7 +16326,7 @@
       <c r="M189" s="6" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="2" t="inlineStr">
+      <c r="A190" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16332,7 +16379,7 @@
       <c r="M190" s="6" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="2" t="inlineStr">
+      <c r="A191" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16381,7 +16428,7 @@
       <c r="M191" s="6" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="2" t="inlineStr">
+      <c r="A192" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16430,7 +16477,7 @@
       <c r="M192" s="6" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="2" t="inlineStr">
+      <c r="A193" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16479,7 +16526,7 @@
       <c r="M193" s="6" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="2" t="inlineStr">
+      <c r="A194" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16532,7 +16579,7 @@
       <c r="M194" s="6" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="2" t="inlineStr">
+      <c r="A195" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16585,7 +16632,7 @@
       <c r="M195" s="6" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="2" t="inlineStr">
+      <c r="A196" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16634,7 +16681,7 @@
       <c r="M196" s="6" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="2" t="inlineStr">
+      <c r="A197" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16687,7 +16734,7 @@
       <c r="M197" s="6" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="2" t="inlineStr">
+      <c r="A198" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16736,7 +16783,7 @@
       <c r="M198" s="6" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="2" t="inlineStr">
+      <c r="A199" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16789,7 +16836,7 @@
       <c r="M199" s="6" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="2" t="inlineStr">
+      <c r="A200" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16935,12 +16982,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -16981,15 +17028,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>비철 섹터 급락 — 구리·아연 가격 하락 우려로 -7%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17030,15 +17081,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>금 가격 하락·FY27 감익 전망 경계, 비철 매도 동반</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17079,15 +17134,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>구리·비철 급락 연동+AI전선 수요 기대 되돌림</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17128,15 +17187,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>AI전선 테마 과열 경계 속 외국인 매도 가속 -6%</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17177,15 +17240,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>반도체 관련 조정 동반 급락(수주 사상최고나 선반영 해소)</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17229,12 +17296,12 @@
       <c r="M7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17278,12 +17345,12 @@
       <c r="M8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17324,15 +17391,19 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
+      <c r="M9" s="6" t="inlineStr">
+        <is>
+          <t>폴란드 편의점 1위 자브카 대규모 출자 검토 보도(7/16), 유럽 확장 기대</t>
+        </is>
+      </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17373,15 +17444,19 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
+      <c r="M10" s="6" t="inlineStr">
+        <is>
+          <t>FY3/26 사상 최고익 경신 전망, 토이하비 호조 상승추세 지속</t>
+        </is>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="A11" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17426,15 +17501,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="6" t="inlineStr">
+        <is>
+          <t>기계·비철 급락장서 고배당 디펜시브로 상대 자금 유입</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="A12" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17475,15 +17554,19 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr"/>
+      <c r="M12" s="6" t="inlineStr">
+        <is>
+          <t>디펜시브 소비재로 급락장서 상대적 견조, 60일 신고가</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="A13" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17524,7 +17607,11 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr"/>
+      <c r="M13" s="6" t="inlineStr">
+        <is>
+          <t>미국 주택사업 확대 기대·고배당(당일 보합, 장중 신고가 터치)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M13"/>
@@ -17624,12 +17711,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17666,15 +17753,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>10% 할인 신주배정 발표 희석 우려+반도체 급락 -15%</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17715,15 +17806,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>노무라 경쟁심화 경고·광섬유 가격 둔화 우려, 고점 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17766,15 +17861,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>IPO 공모가 하회 지속, 항셍테크 -4.4% 급락 속 매도 압력</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17817,15 +17916,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>PCB·전자부품 섹터 급락(A주 동종 다수 하한가) 동반 하락</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17868,15 +17971,19 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>7/10 상장 직후 고점 대비 신규상장주 조정+섹터 약세</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17920,12 +18027,12 @@
       <c r="M7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -17967,12 +18074,12 @@
       <c r="M8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18016,12 +18123,12 @@
       <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18065,12 +18172,12 @@
       <c r="M10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18114,12 +18221,12 @@
       <c r="M11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18167,12 +18274,12 @@
       <c r="M12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18220,12 +18327,12 @@
       <c r="M13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18273,12 +18380,12 @@
       <c r="M14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18322,7 +18429,7 @@
       <c r="M15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18375,7 +18482,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18432,7 +18539,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18485,7 +18592,7 @@
       <c r="M18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18639,12 +18746,12 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="inlineStr">
+      <c r="A2" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B2" s="5" t="inlineStr">
+      <c r="B2" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18685,15 +18792,19 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr"/>
+      <c r="M2" s="6" t="inlineStr">
+        <is>
+          <t>반기 순익 +3200% 예고에도 대주주 감자 계획·고밸류 차익실현</t>
+        </is>
+      </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="inlineStr">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B3" s="5" t="inlineStr">
+      <c r="B3" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18734,15 +18845,19 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr"/>
+      <c r="M3" s="6" t="inlineStr">
+        <is>
+          <t>반기 가이던스(+25~45%)가 기관 예상(68%) 하회, PE 106배 해소</t>
+        </is>
+      </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="inlineStr">
+      <c r="A4" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18781,15 +18896,19 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr"/>
+      <c r="M4" s="6" t="inlineStr">
+        <is>
+          <t>로봇 섹터 차익실현+1Q 순익 -48%, 시장 전반 약세</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="inlineStr">
+      <c r="A5" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18830,15 +18949,19 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr"/>
+      <c r="M5" s="6" t="inlineStr">
+        <is>
+          <t>위성통신·AI 테마 과열 후 PE 87배 고평가 해소 연속 하락</t>
+        </is>
+      </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="inlineStr">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18879,15 +19002,19 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr"/>
+      <c r="M6" s="6" t="inlineStr">
+        <is>
+          <t>1Q 순익 -30.7%·환차손 확대, 주력자금 순매도</t>
+        </is>
+      </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="inlineStr">
+      <c r="A7" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18931,12 +19058,12 @@
       <c r="M7" s="6" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="inlineStr">
+      <c r="A8" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B8" s="5" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -18980,12 +19107,12 @@
       <c r="M8" s="6" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B9" s="5" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19027,12 +19154,12 @@
       <c r="M9" s="6" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B10" s="5" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19076,12 +19203,12 @@
       <c r="M10" s="6" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B11" s="5" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19125,12 +19252,12 @@
       <c r="M11" s="6" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B12" s="5" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19172,12 +19299,12 @@
       <c r="M12" s="6" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B13" s="5" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19223,12 +19350,12 @@
       <c r="M13" s="6" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="inlineStr">
+      <c r="A14" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B14" s="5" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19272,12 +19399,12 @@
       <c r="M14" s="6" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="inlineStr">
+      <c r="A15" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B15" s="5" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19321,12 +19448,12 @@
       <c r="M15" s="6" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="inlineStr">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B16" s="5" t="inlineStr">
+      <c r="B16" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19374,12 +19501,12 @@
       <c r="M16" s="6" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="3" t="inlineStr">
+      <c r="A17" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B17" s="5" t="inlineStr">
+      <c r="B17" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19423,12 +19550,12 @@
       <c r="M17" s="6" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B18" s="5" t="inlineStr">
+      <c r="B18" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19472,12 +19599,12 @@
       <c r="M18" s="6" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B19" s="5" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19521,12 +19648,12 @@
       <c r="M19" s="6" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B20" s="5" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19570,12 +19697,12 @@
       <c r="M20" s="6" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="A21" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B21" s="5" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19619,12 +19746,12 @@
       <c r="M21" s="6" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="3" t="inlineStr">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B22" s="5" t="inlineStr">
+      <c r="B22" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19664,12 +19791,12 @@
       <c r="M22" s="6" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="3" t="inlineStr">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B23" s="5" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19713,12 +19840,12 @@
       <c r="M23" s="6" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="3" t="inlineStr">
+      <c r="A24" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B24" s="5" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19764,12 +19891,12 @@
       <c r="M24" s="6" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B25" s="5" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19813,12 +19940,12 @@
       <c r="M25" s="6" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="3" t="inlineStr">
+      <c r="A26" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B26" s="5" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19866,12 +19993,12 @@
       <c r="M26" s="6" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B27" s="5" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19919,12 +20046,12 @@
       <c r="M27" s="6" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="3" t="inlineStr">
+      <c r="A28" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B28" s="5" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -19968,12 +20095,12 @@
       <c r="M28" s="6" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="3" t="inlineStr">
+      <c r="A29" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B29" s="5" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20021,12 +20148,12 @@
       <c r="M29" s="6" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="3" t="inlineStr">
+      <c r="A30" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B30" s="5" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20070,12 +20197,12 @@
       <c r="M30" s="6" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="3" t="inlineStr">
+      <c r="A31" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
       </c>
-      <c r="B31" s="5" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20119,7 +20246,7 @@
       <c r="M31" s="6" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="A32" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20174,7 +20301,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="3" t="inlineStr">
+      <c r="A33" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20223,7 +20350,7 @@
       <c r="M33" s="6" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="3" t="inlineStr">
+      <c r="A34" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20276,7 +20403,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="3" t="inlineStr">
+      <c r="A35" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20331,7 +20458,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
+      <c r="A36" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20380,7 +20507,7 @@
       <c r="M36" s="6" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="3" t="inlineStr">
+      <c r="A37" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20429,7 +20556,7 @@
       <c r="M37" s="6" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="3" t="inlineStr">
+      <c r="A38" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20482,7 +20609,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="3" t="inlineStr">
+      <c r="A39" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20535,7 +20662,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="3" t="inlineStr">
+      <c r="A40" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20586,7 +20713,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="A41" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20639,7 +20766,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr">
+      <c r="A42" s="4" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20694,12 +20821,12 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B43" s="5" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20740,15 +20867,19 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="6" t="inlineStr"/>
+      <c r="M43" s="6" t="inlineStr">
+        <is>
+          <t>국무원 중의약 15·5규획 발표로 중약 섹터 급등, 연속 강세</t>
+        </is>
+      </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+      <c r="A44" s="3" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
       </c>
-      <c r="B44" s="5" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
         <is>
           <t>NEW</t>
         </is>
@@ -20789,7 +20920,11 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="6" t="inlineStr"/>
+      <c r="M44" s="6" t="inlineStr">
+        <is>
+          <t>야룽장 유역 강수 증가로 수력 발전량 상승 기대</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:M44"/>

--- a/신고신저가_20260720.xlsx
+++ b/신고신저가_20260720.xlsx
@@ -31,7 +31,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0&quot;%&quot;"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,6 +42,7 @@
     <font>
       <b val="1"/>
     </font>
+    <font/>
     <font>
       <color rgb="00C00000"/>
     </font>
@@ -74,12 +75,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -449,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -609,12 +611,33 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 금요일(7/17)은 미국-아시아 온도차가 뚜렷 — 미국은 신고가 137개(정유 정제마진 강세, TRV 어닝 서프라이즈 +8%)인 반면, 아시아는 AI·반도체 고밸류 되돌림으로 일본 기계·비철 급락(신저 7개), 중국A 신저가 41개, 항셍테크 -4.4% 리스크오프. 이벤트: NFLX 3Q 가이던스 실망 -7%, 세븐&amp;아이는 폴란드 자브카 출자 검토 보도로 신고가, 중국 중약 섹터는 15·5규획 발표에 강세.</t>
+          <t>💬 [B·해석형] AI 하드웨어 밸류 되돌림이 아시아 전역으로 확산된 하루 — 일본 AI전선(스미토모전공 -6.2%)·중국 광모듈(天孚通信 -13%, PE 106배)·PCB(다수 하한가)·메모리까지 같은 체인이 같은 이유(고밸류+기대치 하회)로 무너진 반면, 미국은 TRV 어닝서프라이즈 +8%·정제마진 강세로 신고가 137개 — 조정이 아직 실적 팩터가 받치는 미국으로 전이되지 않은 국면. 일본 은행 -4.7%는 YTD +40% 고점권 차익실현 성격. 예외는 중국 중약 — 15·5규획 발표에 역행 강세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>[C·구조형] [결론] AI 하드웨어 고밸류 되돌림, 아시아부터 — 미국은 실적주가 방어. [강세] 미국 정유(정제마진)·보험(TRV +8%), 일본 디펜시브(의약·운수·식품), 중국 중약(15·5규획). [약세] AI 체인 일제 조정: 일본 전선·기계(철강비철 ETF 1M -16%), 중국 광모듈 天孚 -13%(기관 기대 하회·PE 106배), PCB 하한가 다수, 항셍테크 -4.4%. 일본 은행 -4.7%는 YTD +40% 후 차익실현.</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>[D·시장별] 미국: 신고 137 — 보험(TRV +8%)·정유(정제마진) 주도, NFLX만 가이던스 실망 -7% / 일본: 기계·비철 급락(철강비철 1M -16%)·AI전선 되돌림, 의약·운수 디펜시브로 피난 / 홍콩: 테크 -4.4%, IPO 신주(루시쉐어 등) 매도 압력 / 중국A: 신저 41개 — 광모듈·PCB·메모리 고밸류 해소, 중약만 15·5규획에 역행 강세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>[A·요약형] 금요일(7/17)은 미국-아시아 온도차 뚜렷 — 미국 신고가 137개(정유·보험 강세) vs 아시아는 AI·반도체 고밸류 되돌림(일본 기계·비철 급락, 중국A 신저 41개, 항셍테크 -4.4%). 이벤트: NFLX 가이던스 실망 -7%, 세븐&amp;아이 자브카 출자 검토 보도 신고가, 중약 15·5규획 강세.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>
@@ -715,7 +738,7 @@
       <c r="F2" t="n">
         <v>55</v>
       </c>
-      <c r="G2" s="3" t="inlineStr">
+      <c r="G2" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -750,7 +773,7 @@
       <c r="F3" t="n">
         <v>11</v>
       </c>
-      <c r="G3" s="3" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -785,7 +808,7 @@
       <c r="F4" t="n">
         <v>9</v>
       </c>
-      <c r="G4" s="3" t="inlineStr">
+      <c r="G4" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -820,7 +843,7 @@
       <c r="F5" t="n">
         <v>8</v>
       </c>
-      <c r="G5" s="3" t="inlineStr">
+      <c r="G5" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -855,7 +878,7 @@
       <c r="F6" t="n">
         <v>8</v>
       </c>
-      <c r="G6" s="3" t="inlineStr">
+      <c r="G6" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -890,7 +913,7 @@
       <c r="F7" t="n">
         <v>7</v>
       </c>
-      <c r="G7" s="3" t="inlineStr">
+      <c r="G7" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -925,7 +948,7 @@
       <c r="F8" t="n">
         <v>5</v>
       </c>
-      <c r="G8" s="3" t="inlineStr">
+      <c r="G8" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -960,7 +983,7 @@
       <c r="F9" t="n">
         <v>4</v>
       </c>
-      <c r="G9" s="3" t="inlineStr">
+      <c r="G9" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -995,7 +1018,7 @@
       <c r="F10" t="n">
         <v>4</v>
       </c>
-      <c r="G10" s="3" t="inlineStr">
+      <c r="G10" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1030,7 +1053,7 @@
       <c r="F11" t="n">
         <v>2</v>
       </c>
-      <c r="G11" s="3" t="inlineStr">
+      <c r="G11" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1065,7 +1088,7 @@
       <c r="F12" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="3" t="inlineStr">
+      <c r="G12" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1100,7 +1123,7 @@
       <c r="F13" t="n">
         <v>2</v>
       </c>
-      <c r="G13" s="3" t="inlineStr">
+      <c r="G13" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1135,7 +1158,7 @@
       <c r="F14" t="n">
         <v>1</v>
       </c>
-      <c r="G14" s="3" t="inlineStr">
+      <c r="G14" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1275,7 +1298,7 @@
       <c r="F18" t="n">
         <v>-2</v>
       </c>
-      <c r="G18" s="4" t="inlineStr">
+      <c r="G18" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1310,7 +1333,7 @@
       <c r="F19" t="n">
         <v>-2</v>
       </c>
-      <c r="G19" s="4" t="inlineStr">
+      <c r="G19" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1345,7 +1368,7 @@
       <c r="F20" t="n">
         <v>-13</v>
       </c>
-      <c r="G20" s="4" t="inlineStr">
+      <c r="G20" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1380,7 +1403,7 @@
       <c r="F21" t="n">
         <v>-26</v>
       </c>
-      <c r="G21" s="4" t="inlineStr">
+      <c r="G21" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -1415,7 +1438,7 @@
       <c r="F22" t="n">
         <v>1</v>
       </c>
-      <c r="G22" s="3" t="inlineStr">
+      <c r="G22" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1450,7 +1473,7 @@
       <c r="F23" t="n">
         <v>1</v>
       </c>
-      <c r="G23" s="3" t="inlineStr">
+      <c r="G23" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1485,7 +1508,7 @@
       <c r="F24" t="n">
         <v>1</v>
       </c>
-      <c r="G24" s="3" t="inlineStr">
+      <c r="G24" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1520,7 +1543,7 @@
       <c r="F25" t="n">
         <v>1</v>
       </c>
-      <c r="G25" s="3" t="inlineStr">
+      <c r="G25" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -1975,7 +1998,7 @@
       <c r="F38" t="n">
         <v>-2</v>
       </c>
-      <c r="G38" s="4" t="inlineStr">
+      <c r="G38" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2010,7 +2033,7 @@
       <c r="F39" t="n">
         <v>-4</v>
       </c>
-      <c r="G39" s="4" t="inlineStr">
+      <c r="G39" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2045,7 +2068,7 @@
       <c r="F40" t="n">
         <v>2</v>
       </c>
-      <c r="G40" s="3" t="inlineStr">
+      <c r="G40" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2535,7 +2558,7 @@
       <c r="F54" t="n">
         <v>-2</v>
       </c>
-      <c r="G54" s="4" t="inlineStr">
+      <c r="G54" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2570,7 +2593,7 @@
       <c r="F55" t="n">
         <v>-2</v>
       </c>
-      <c r="G55" s="4" t="inlineStr">
+      <c r="G55" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2605,7 +2628,7 @@
       <c r="F56" t="n">
         <v>-5</v>
       </c>
-      <c r="G56" s="4" t="inlineStr">
+      <c r="G56" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2640,7 +2663,7 @@
       <c r="F57" t="n">
         <v>-7</v>
       </c>
-      <c r="G57" s="4" t="inlineStr">
+      <c r="G57" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -2675,7 +2698,7 @@
       <c r="F58" t="n">
         <v>1</v>
       </c>
-      <c r="G58" s="3" t="inlineStr">
+      <c r="G58" s="4" t="inlineStr">
         <is>
           <t>강세</t>
         </is>
@@ -2988,7 +3011,7 @@
       <c r="F67" t="n">
         <v>-1</v>
       </c>
-      <c r="G67" s="4" t="inlineStr">
+      <c r="G67" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3021,7 +3044,7 @@
       <c r="F68" t="n">
         <v>-1</v>
       </c>
-      <c r="G68" s="4" t="inlineStr">
+      <c r="G68" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3056,7 +3079,7 @@
       <c r="F69" t="n">
         <v>-1</v>
       </c>
-      <c r="G69" s="4" t="inlineStr">
+      <c r="G69" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3091,7 +3114,7 @@
       <c r="F70" t="n">
         <v>-2</v>
       </c>
-      <c r="G70" s="4" t="inlineStr">
+      <c r="G70" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3126,7 +3149,7 @@
       <c r="F71" t="n">
         <v>-2</v>
       </c>
-      <c r="G71" s="4" t="inlineStr">
+      <c r="G71" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3161,7 +3184,7 @@
       <c r="F72" t="n">
         <v>-3</v>
       </c>
-      <c r="G72" s="4" t="inlineStr">
+      <c r="G72" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3196,7 +3219,7 @@
       <c r="F73" t="n">
         <v>-4</v>
       </c>
-      <c r="G73" s="4" t="inlineStr">
+      <c r="G73" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3231,7 +3254,7 @@
       <c r="F74" t="n">
         <v>-13</v>
       </c>
-      <c r="G74" s="4" t="inlineStr">
+      <c r="G74" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3266,7 +3289,7 @@
       <c r="F75" t="n">
         <v>-13</v>
       </c>
-      <c r="G75" s="4" t="inlineStr">
+      <c r="G75" s="5" t="inlineStr">
         <is>
           <t>약세</t>
         </is>
@@ -3446,55 +3469,55 @@
           <t>에너지</t>
         </is>
       </c>
-      <c r="D2" s="5" t="n">
+      <c r="D2" s="6" t="n">
         <v>1.2</v>
       </c>
-      <c r="E2" s="5" t="n">
+      <c r="E2" s="6" t="n">
         <v>4.7</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="6" t="n">
         <v>4.9</v>
       </c>
-      <c r="G2" s="5" t="n">
+      <c r="G2" s="6" t="n">
         <v>2.7</v>
       </c>
-      <c r="H2" s="5" t="n">
+      <c r="H2" s="6" t="n">
         <v>30.8</v>
       </c>
       <c r="I2" t="n">
         <v>1</v>
       </c>
-      <c r="J2" s="5" t="n">
+      <c r="J2" s="6" t="n">
         <v>7.9</v>
       </c>
       <c r="K2" t="n">
         <v>8</v>
       </c>
-      <c r="L2" s="5" t="n">
+      <c r="L2" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="M2" t="n">
         <v>8</v>
       </c>
-      <c r="N2" s="5" t="n">
+      <c r="N2" s="6" t="n">
         <v>-0.6</v>
       </c>
       <c r="O2" t="n">
         <v>9</v>
       </c>
-      <c r="P2" s="5" t="n">
+      <c r="P2" s="6" t="n">
         <v>64.3</v>
       </c>
       <c r="Q2" t="n">
         <v>1</v>
       </c>
-      <c r="R2" s="5" t="n">
+      <c r="R2" s="6" t="n">
         <v>53.3</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
       </c>
-      <c r="T2" s="5" t="n">
+      <c r="T2" s="6" t="n">
         <v>-32.7</v>
       </c>
       <c r="U2" t="n">
@@ -3517,55 +3540,55 @@
           <t>리츠</t>
         </is>
       </c>
-      <c r="D3" s="5" t="n">
+      <c r="D3" s="6" t="n">
         <v>-0.1</v>
       </c>
-      <c r="E3" s="5" t="n">
+      <c r="E3" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="G3" s="5" t="n">
+      <c r="G3" s="6" t="n">
         <v>4.6</v>
       </c>
-      <c r="H3" s="5" t="n">
+      <c r="H3" s="6" t="n">
         <v>14.3</v>
       </c>
       <c r="I3" t="n">
         <v>4</v>
       </c>
-      <c r="J3" s="5" t="n">
+      <c r="J3" s="6" t="n">
         <v>2.6</v>
       </c>
       <c r="K3" t="n">
         <v>10</v>
       </c>
-      <c r="L3" s="5" t="n">
+      <c r="L3" s="6" t="n">
         <v>5.1</v>
       </c>
       <c r="M3" t="n">
         <v>9</v>
       </c>
-      <c r="N3" s="5" t="n">
+      <c r="N3" s="6" t="n">
         <v>12.4</v>
       </c>
       <c r="O3" t="n">
         <v>6</v>
       </c>
-      <c r="P3" s="5" t="n">
+      <c r="P3" s="6" t="n">
         <v>-26.2</v>
       </c>
       <c r="Q3" t="n">
         <v>8</v>
       </c>
-      <c r="R3" s="5" t="n">
+      <c r="R3" s="6" t="n">
         <v>46.1</v>
       </c>
       <c r="S3" t="n">
         <v>2</v>
       </c>
-      <c r="T3" s="5" t="n">
+      <c r="T3" s="6" t="n">
         <v>-2.2</v>
       </c>
       <c r="U3" t="n">
@@ -3588,55 +3611,55 @@
           <t>산업재</t>
         </is>
       </c>
-      <c r="D4" s="5" t="n">
+      <c r="D4" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E4" s="5" t="n">
+      <c r="E4" s="6" t="n">
         <v>-1.4</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G4" s="5" t="n">
+      <c r="G4" s="6" t="n">
         <v>5.6</v>
       </c>
-      <c r="H4" s="5" t="n">
+      <c r="H4" s="6" t="n">
         <v>16.3</v>
       </c>
       <c r="I4" t="n">
         <v>3</v>
       </c>
-      <c r="J4" s="5" t="n">
+      <c r="J4" s="6" t="n">
         <v>19.3</v>
       </c>
       <c r="K4" t="n">
         <v>3</v>
       </c>
-      <c r="L4" s="5" t="n">
+      <c r="L4" s="6" t="n">
         <v>17.3</v>
       </c>
       <c r="M4" t="n">
         <v>6</v>
       </c>
-      <c r="N4" s="5" t="n">
+      <c r="N4" s="6" t="n">
         <v>18.1</v>
       </c>
       <c r="O4" t="n">
         <v>4</v>
       </c>
-      <c r="P4" s="5" t="n">
+      <c r="P4" s="6" t="n">
         <v>-5.6</v>
       </c>
       <c r="Q4" t="n">
         <v>5</v>
       </c>
-      <c r="R4" s="5" t="n">
+      <c r="R4" s="6" t="n">
         <v>21.1</v>
       </c>
       <c r="S4" t="n">
         <v>8</v>
       </c>
-      <c r="T4" s="5" t="n">
+      <c r="T4" s="6" t="n">
         <v>10.9</v>
       </c>
       <c r="U4" t="n">
@@ -3659,55 +3682,55 @@
           <t>헬스케어</t>
         </is>
       </c>
-      <c r="D5" s="5" t="n">
+      <c r="D5" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="E5" s="5" t="n">
+      <c r="E5" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="6" t="n">
         <v>5.8</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="G5" s="6" t="n">
         <v>10.4</v>
       </c>
-      <c r="H5" s="5" t="n">
+      <c r="H5" s="6" t="n">
         <v>5</v>
       </c>
       <c r="I5" t="n">
         <v>8</v>
       </c>
-      <c r="J5" s="5" t="n">
+      <c r="J5" s="6" t="n">
         <v>14.5</v>
       </c>
       <c r="K5" t="n">
         <v>6</v>
       </c>
-      <c r="L5" s="5" t="n">
+      <c r="L5" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="M5" t="n">
         <v>10</v>
       </c>
-      <c r="N5" s="5" t="n">
+      <c r="N5" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="O5" t="n">
         <v>8</v>
       </c>
-      <c r="P5" s="5" t="n">
+      <c r="P5" s="6" t="n">
         <v>-2.1</v>
       </c>
       <c r="Q5" t="n">
         <v>4</v>
       </c>
-      <c r="R5" s="5" t="n">
+      <c r="R5" s="6" t="n">
         <v>26</v>
       </c>
       <c r="S5" t="n">
         <v>7</v>
       </c>
-      <c r="T5" s="5" t="n">
+      <c r="T5" s="6" t="n">
         <v>13.3</v>
       </c>
       <c r="U5" t="n">
@@ -3730,55 +3753,55 @@
           <t>소재</t>
         </is>
       </c>
-      <c r="D6" s="5" t="n">
+      <c r="D6" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E6" s="5" t="n">
+      <c r="E6" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="6" t="n">
         <v>-3.8</v>
       </c>
-      <c r="G6" s="5" t="n">
+      <c r="G6" s="6" t="n">
         <v>-2</v>
       </c>
-      <c r="H6" s="5" t="n">
+      <c r="H6" s="6" t="n">
         <v>12.3</v>
       </c>
       <c r="I6" t="n">
         <v>5</v>
       </c>
-      <c r="J6" s="5" t="n">
+      <c r="J6" s="6" t="n">
         <v>9.9</v>
       </c>
       <c r="K6" t="n">
         <v>7</v>
       </c>
-      <c r="L6" s="5" t="n">
+      <c r="L6" s="6" t="n">
         <v>0.1</v>
       </c>
       <c r="M6" t="n">
         <v>11</v>
       </c>
-      <c r="N6" s="5" t="n">
+      <c r="N6" s="6" t="n">
         <v>12.5</v>
       </c>
       <c r="O6" t="n">
         <v>5</v>
       </c>
-      <c r="P6" s="5" t="n">
+      <c r="P6" s="6" t="n">
         <v>-12.3</v>
       </c>
       <c r="Q6" t="n">
         <v>7</v>
       </c>
-      <c r="R6" s="5" t="n">
+      <c r="R6" s="6" t="n">
         <v>27.4</v>
       </c>
       <c r="S6" t="n">
         <v>6</v>
       </c>
-      <c r="T6" s="5" t="n">
+      <c r="T6" s="6" t="n">
         <v>20.5</v>
       </c>
       <c r="U6" t="n">
@@ -3801,55 +3824,55 @@
           <t>필수소비재</t>
         </is>
       </c>
-      <c r="D7" s="5" t="n">
+      <c r="D7" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E7" s="5" t="n">
+      <c r="E7" s="6" t="n">
         <v>1.3</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="G7" s="5" t="n">
+      <c r="G7" s="6" t="n">
         <v>5.3</v>
       </c>
-      <c r="H7" s="5" t="n">
+      <c r="H7" s="6" t="n">
         <v>11.1</v>
       </c>
       <c r="I7" t="n">
         <v>6</v>
       </c>
-      <c r="J7" s="5" t="n">
+      <c r="J7" s="6" t="n">
         <v>1.5</v>
       </c>
       <c r="K7" t="n">
         <v>11</v>
       </c>
-      <c r="L7" s="5" t="n">
+      <c r="L7" s="6" t="n">
         <v>12.2</v>
       </c>
       <c r="M7" t="n">
         <v>7</v>
       </c>
-      <c r="N7" s="5" t="n">
+      <c r="N7" s="6" t="n">
         <v>-0.8</v>
       </c>
       <c r="O7" t="n">
         <v>10</v>
       </c>
-      <c r="P7" s="5" t="n">
+      <c r="P7" s="6" t="n">
         <v>-0.8</v>
       </c>
       <c r="Q7" t="n">
         <v>3</v>
       </c>
-      <c r="R7" s="5" t="n">
+      <c r="R7" s="6" t="n">
         <v>17.2</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
       </c>
-      <c r="T7" s="5" t="n">
+      <c r="T7" s="6" t="n">
         <v>10.1</v>
       </c>
       <c r="U7" t="n">
@@ -3872,55 +3895,55 @@
           <t>유틸리티</t>
         </is>
       </c>
-      <c r="D8" s="5" t="n">
+      <c r="D8" s="6" t="n">
         <v>-0.7</v>
       </c>
-      <c r="E8" s="5" t="n">
+      <c r="E8" s="6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="G8" s="5" t="n">
+      <c r="G8" s="6" t="n">
         <v>-1.9</v>
       </c>
-      <c r="H8" s="5" t="n">
+      <c r="H8" s="6" t="n">
         <v>7.2</v>
       </c>
       <c r="I8" t="n">
         <v>7</v>
       </c>
-      <c r="J8" s="5" t="n">
+      <c r="J8" s="6" t="n">
         <v>16</v>
       </c>
       <c r="K8" t="n">
         <v>4</v>
       </c>
-      <c r="L8" s="5" t="n">
+      <c r="L8" s="6" t="n">
         <v>23.3</v>
       </c>
       <c r="M8" t="n">
         <v>4</v>
       </c>
-      <c r="N8" s="5" t="n">
+      <c r="N8" s="6" t="n">
         <v>-7.2</v>
       </c>
       <c r="O8" t="n">
         <v>11</v>
       </c>
-      <c r="P8" s="5" t="n">
+      <c r="P8" s="6" t="n">
         <v>1.4</v>
       </c>
       <c r="Q8" t="n">
         <v>2</v>
       </c>
-      <c r="R8" s="5" t="n">
+      <c r="R8" s="6" t="n">
         <v>17.7</v>
       </c>
       <c r="S8" t="n">
         <v>9</v>
       </c>
-      <c r="T8" s="5" t="n">
+      <c r="T8" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="U8" t="n">
@@ -3943,55 +3966,55 @@
           <t>금융</t>
         </is>
       </c>
-      <c r="D9" s="5" t="n">
+      <c r="D9" s="6" t="n">
         <v>-0.9</v>
       </c>
-      <c r="E9" s="5" t="n">
+      <c r="E9" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="6" t="n">
         <v>3.9</v>
       </c>
-      <c r="G9" s="5" t="n">
+      <c r="G9" s="6" t="n">
         <v>8.5</v>
       </c>
-      <c r="H9" s="5" t="n">
+      <c r="H9" s="6" t="n">
         <v>3.6</v>
       </c>
       <c r="I9" t="n">
         <v>9</v>
       </c>
-      <c r="J9" s="5" t="n">
+      <c r="J9" s="6" t="n">
         <v>14.9</v>
       </c>
       <c r="K9" t="n">
         <v>5</v>
       </c>
-      <c r="L9" s="5" t="n">
+      <c r="L9" s="6" t="n">
         <v>30.6</v>
       </c>
       <c r="M9" t="n">
         <v>2</v>
       </c>
-      <c r="N9" s="5" t="n">
+      <c r="N9" s="6" t="n">
         <v>12</v>
       </c>
       <c r="O9" t="n">
         <v>7</v>
       </c>
-      <c r="P9" s="5" t="n">
+      <c r="P9" s="6" t="n">
         <v>-10.6</v>
       </c>
       <c r="Q9" t="n">
         <v>6</v>
       </c>
-      <c r="R9" s="5" t="n">
+      <c r="R9" s="6" t="n">
         <v>34.8</v>
       </c>
       <c r="S9" t="n">
         <v>3</v>
       </c>
-      <c r="T9" s="5" t="n">
+      <c r="T9" s="6" t="n">
         <v>-1.7</v>
       </c>
       <c r="U9" t="n">
@@ -4014,55 +4037,55 @@
           <t>테크</t>
         </is>
       </c>
-      <c r="D10" s="5" t="n">
+      <c r="D10" s="6" t="n">
         <v>-1.1</v>
       </c>
-      <c r="E10" s="5" t="n">
+      <c r="E10" s="6" t="n">
         <v>-5.5</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="6" t="n">
         <v>-5.7</v>
       </c>
-      <c r="G10" s="5" t="n">
+      <c r="G10" s="6" t="n">
         <v>15.6</v>
       </c>
-      <c r="H10" s="5" t="n">
+      <c r="H10" s="6" t="n">
         <v>22.3</v>
       </c>
       <c r="I10" t="n">
         <v>2</v>
       </c>
-      <c r="J10" s="5" t="n">
+      <c r="J10" s="6" t="n">
         <v>24.6</v>
       </c>
       <c r="K10" t="n">
         <v>1</v>
       </c>
-      <c r="L10" s="5" t="n">
+      <c r="L10" s="6" t="n">
         <v>21.6</v>
       </c>
       <c r="M10" t="n">
         <v>5</v>
       </c>
-      <c r="N10" s="5" t="n">
+      <c r="N10" s="6" t="n">
         <v>56</v>
       </c>
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="P10" s="5" t="n">
+      <c r="P10" s="6" t="n">
         <v>-27.7</v>
       </c>
       <c r="Q10" t="n">
         <v>9</v>
       </c>
-      <c r="R10" s="5" t="n">
+      <c r="R10" s="6" t="n">
         <v>34.7</v>
       </c>
       <c r="S10" t="n">
         <v>4</v>
       </c>
-      <c r="T10" s="5" t="n">
+      <c r="T10" s="6" t="n">
         <v>43.6</v>
       </c>
       <c r="U10" t="n">
@@ -4085,55 +4108,55 @@
           <t>경기소비재</t>
         </is>
       </c>
-      <c r="D11" s="5" t="n">
+      <c r="D11" s="6" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E11" s="5" t="n">
+      <c r="E11" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="6" t="n">
         <v>-2.4</v>
       </c>
-      <c r="G11" s="5" t="n">
+      <c r="G11" s="6" t="n">
         <v>-1.7</v>
       </c>
-      <c r="H11" s="5" t="n">
+      <c r="H11" s="6" t="n">
         <v>-2.9</v>
       </c>
       <c r="I11" t="n">
         <v>10</v>
       </c>
-      <c r="J11" s="5" t="n">
+      <c r="J11" s="6" t="n">
         <v>7.4</v>
       </c>
       <c r="K11" t="n">
         <v>9</v>
       </c>
-      <c r="L11" s="5" t="n">
+      <c r="L11" s="6" t="n">
         <v>26.5</v>
       </c>
       <c r="M11" t="n">
         <v>3</v>
       </c>
-      <c r="N11" s="5" t="n">
+      <c r="N11" s="6" t="n">
         <v>39.6</v>
       </c>
       <c r="O11" t="n">
         <v>3</v>
       </c>
-      <c r="P11" s="5" t="n">
+      <c r="P11" s="6" t="n">
         <v>-36.3</v>
       </c>
       <c r="Q11" t="n">
         <v>10</v>
       </c>
-      <c r="R11" s="5" t="n">
+      <c r="R11" s="6" t="n">
         <v>27.9</v>
       </c>
       <c r="S11" t="n">
         <v>5</v>
       </c>
-      <c r="T11" s="5" t="n">
+      <c r="T11" s="6" t="n">
         <v>29.6</v>
       </c>
       <c r="U11" t="n">
@@ -4156,55 +4179,55 @@
           <t>커뮤니케이션</t>
         </is>
       </c>
-      <c r="D12" s="5" t="n">
+      <c r="D12" s="6" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E12" s="5" t="n">
+      <c r="E12" s="6" t="n">
         <v>-0.9</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="6" t="n">
         <v>-1.2</v>
       </c>
-      <c r="G12" s="5" t="n">
+      <c r="G12" s="6" t="n">
         <v>-6.6</v>
       </c>
-      <c r="H12" s="5" t="n">
+      <c r="H12" s="6" t="n">
         <v>-5.5</v>
       </c>
       <c r="I12" t="n">
         <v>11</v>
       </c>
-      <c r="J12" s="5" t="n">
+      <c r="J12" s="6" t="n">
         <v>23.1</v>
       </c>
       <c r="K12" t="n">
         <v>2</v>
       </c>
-      <c r="L12" s="5" t="n">
+      <c r="L12" s="6" t="n">
         <v>34.7</v>
       </c>
       <c r="M12" t="n">
         <v>1</v>
       </c>
-      <c r="N12" s="5" t="n">
+      <c r="N12" s="6" t="n">
         <v>52.8</v>
       </c>
       <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="P12" s="5" t="n">
+      <c r="P12" s="6" t="n">
         <v>-37.6</v>
       </c>
       <c r="Q12" t="n">
         <v>11</v>
       </c>
-      <c r="R12" s="5" t="n">
+      <c r="R12" s="6" t="n">
         <v>16</v>
       </c>
       <c r="S12" t="n">
         <v>11</v>
       </c>
-      <c r="T12" s="5" t="n">
+      <c r="T12" s="6" t="n">
         <v>26.9</v>
       </c>
       <c r="U12" t="n">
@@ -4227,55 +4250,55 @@
           <t>의약품</t>
         </is>
       </c>
-      <c r="D13" s="5" t="n">
+      <c r="D13" s="6" t="n">
         <v>1.1</v>
       </c>
-      <c r="E13" s="5" t="n">
+      <c r="E13" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="6" t="n">
         <v>3.1</v>
       </c>
-      <c r="G13" s="5" t="n">
+      <c r="G13" s="6" t="n">
         <v>-6.5</v>
       </c>
-      <c r="H13" s="5" t="n">
+      <c r="H13" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="I13" t="n">
         <v>14</v>
       </c>
-      <c r="J13" s="5" t="n">
+      <c r="J13" s="6" t="n">
         <v>9.699999999999999</v>
       </c>
       <c r="K13" t="n">
         <v>16</v>
       </c>
-      <c r="L13" s="5" t="n">
+      <c r="L13" s="6" t="n">
         <v>10.8</v>
       </c>
       <c r="M13" t="n">
         <v>13</v>
       </c>
-      <c r="N13" s="5" t="n">
+      <c r="N13" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="O13" t="n">
         <v>17</v>
       </c>
-      <c r="P13" s="5" t="n">
+      <c r="P13" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="Q13" t="n">
         <v>4</v>
       </c>
-      <c r="R13" s="5" t="n">
+      <c r="R13" s="6" t="n">
         <v>-8.4</v>
       </c>
       <c r="S13" t="n">
         <v>17</v>
       </c>
-      <c r="T13" s="5" t="n">
+      <c r="T13" s="6" t="n">
         <v>4.6</v>
       </c>
       <c r="U13" t="n">
@@ -4298,55 +4321,55 @@
           <t>운수·물류</t>
         </is>
       </c>
-      <c r="D14" s="5" t="n">
+      <c r="D14" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="E14" s="5" t="n">
+      <c r="E14" s="6" t="n">
         <v>3.4</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="6" t="n">
         <v>7.1</v>
       </c>
-      <c r="G14" s="5" t="n">
+      <c r="G14" s="6" t="n">
         <v>-1.1</v>
       </c>
-      <c r="H14" s="5" t="n">
+      <c r="H14" s="6" t="n">
         <v>3</v>
       </c>
       <c r="I14" t="n">
         <v>13</v>
       </c>
-      <c r="J14" s="5" t="n">
+      <c r="J14" s="6" t="n">
         <v>19.9</v>
       </c>
       <c r="K14" t="n">
         <v>11</v>
       </c>
-      <c r="L14" s="5" t="n">
+      <c r="L14" s="6" t="n">
         <v>-0</v>
       </c>
       <c r="M14" t="n">
         <v>17</v>
       </c>
-      <c r="N14" s="5" t="n">
+      <c r="N14" s="6" t="n">
         <v>19</v>
       </c>
       <c r="O14" t="n">
         <v>14</v>
       </c>
-      <c r="P14" s="5" t="n">
+      <c r="P14" s="6" t="n">
         <v>13.1</v>
       </c>
       <c r="Q14" t="n">
         <v>8</v>
       </c>
-      <c r="R14" s="5" t="n">
+      <c r="R14" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="S14" t="n">
         <v>12</v>
       </c>
-      <c r="T14" s="5" t="n">
+      <c r="T14" s="6" t="n">
         <v>-17.1</v>
       </c>
       <c r="U14" t="n">
@@ -4369,55 +4392,55 @@
           <t>식품</t>
         </is>
       </c>
-      <c r="D15" s="5" t="n">
+      <c r="D15" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="E15" s="5" t="n">
+      <c r="E15" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="6" t="n">
         <v>3.3</v>
       </c>
-      <c r="G15" s="5" t="n">
+      <c r="G15" s="6" t="n">
         <v>5.7</v>
       </c>
-      <c r="H15" s="5" t="n">
+      <c r="H15" s="6" t="n">
         <v>16.2</v>
       </c>
       <c r="I15" t="n">
         <v>6</v>
       </c>
-      <c r="J15" s="5" t="n">
+      <c r="J15" s="6" t="n">
         <v>11.8</v>
       </c>
       <c r="K15" t="n">
         <v>15</v>
       </c>
-      <c r="L15" s="5" t="n">
+      <c r="L15" s="6" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="M15" t="n">
         <v>14</v>
       </c>
-      <c r="N15" s="5" t="n">
+      <c r="N15" s="6" t="n">
         <v>22.3</v>
       </c>
       <c r="O15" t="n">
         <v>13</v>
       </c>
-      <c r="P15" s="5" t="n">
+      <c r="P15" s="6" t="n">
         <v>6.4</v>
       </c>
       <c r="Q15" t="n">
         <v>10</v>
       </c>
-      <c r="R15" s="5" t="n">
+      <c r="R15" s="6" t="n">
         <v>5.6</v>
       </c>
       <c r="S15" t="n">
         <v>11</v>
       </c>
-      <c r="T15" s="5" t="n">
+      <c r="T15" s="6" t="n">
         <v>-3.4</v>
       </c>
       <c r="U15" t="n">
@@ -4440,55 +4463,55 @@
           <t>소매</t>
         </is>
       </c>
-      <c r="D16" s="5" t="n">
+      <c r="D16" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="E16" s="5" t="n">
+      <c r="E16" s="6" t="n">
         <v>1.8</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="6" t="n">
         <v>3.6</v>
       </c>
-      <c r="G16" s="5" t="n">
+      <c r="G16" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="H16" s="5" t="n">
+      <c r="H16" s="6" t="n">
         <v>4.3</v>
       </c>
       <c r="I16" t="n">
         <v>12</v>
       </c>
-      <c r="J16" s="5" t="n">
+      <c r="J16" s="6" t="n">
         <v>16.8</v>
       </c>
       <c r="K16" t="n">
         <v>12</v>
       </c>
-      <c r="L16" s="5" t="n">
+      <c r="L16" s="6" t="n">
         <v>23.4</v>
       </c>
       <c r="M16" t="n">
         <v>4</v>
       </c>
-      <c r="N16" s="5" t="n">
+      <c r="N16" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="O16" t="n">
         <v>16</v>
       </c>
-      <c r="P16" s="5" t="n">
+      <c r="P16" s="6" t="n">
         <v>10.2</v>
       </c>
       <c r="Q16" t="n">
         <v>9</v>
       </c>
-      <c r="R16" s="5" t="n">
+      <c r="R16" s="6" t="n">
         <v>-4.4</v>
       </c>
       <c r="S16" t="n">
         <v>15</v>
       </c>
-      <c r="T16" s="5" t="n">
+      <c r="T16" s="6" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="U16" t="n">
@@ -4511,55 +4534,55 @@
           <t>상사·도매</t>
         </is>
       </c>
-      <c r="D17" s="5" t="n">
+      <c r="D17" s="6" t="n">
         <v>-0.6</v>
       </c>
-      <c r="E17" s="5" t="n">
+      <c r="E17" s="6" t="n">
         <v>1.6</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="6" t="n">
         <v>0.2</v>
       </c>
-      <c r="G17" s="5" t="n">
+      <c r="G17" s="6" t="n">
         <v>-8</v>
       </c>
-      <c r="H17" s="5" t="n">
+      <c r="H17" s="6" t="n">
         <v>10.8</v>
       </c>
       <c r="I17" t="n">
         <v>8</v>
       </c>
-      <c r="J17" s="5" t="n">
+      <c r="J17" s="6" t="n">
         <v>41.5</v>
       </c>
       <c r="K17" t="n">
         <v>5</v>
       </c>
-      <c r="L17" s="5" t="n">
+      <c r="L17" s="6" t="n">
         <v>20.1</v>
       </c>
       <c r="M17" t="n">
         <v>9</v>
       </c>
-      <c r="N17" s="5" t="n">
+      <c r="N17" s="6" t="n">
         <v>42</v>
       </c>
       <c r="O17" t="n">
         <v>1</v>
       </c>
-      <c r="P17" s="5" t="n">
+      <c r="P17" s="6" t="n">
         <v>21.3</v>
       </c>
       <c r="Q17" t="n">
         <v>3</v>
       </c>
-      <c r="R17" s="5" t="n">
+      <c r="R17" s="6" t="n">
         <v>29.2</v>
       </c>
       <c r="S17" t="n">
         <v>2</v>
       </c>
-      <c r="T17" s="5" t="n">
+      <c r="T17" s="6" t="n">
         <v>1.9</v>
       </c>
       <c r="U17" t="n">
@@ -4582,55 +4605,55 @@
           <t>소재·화학</t>
         </is>
       </c>
-      <c r="D18" s="5" t="n">
+      <c r="D18" s="6" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E18" s="5" t="n">
+      <c r="E18" s="6" t="n">
         <v>-0</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="6" t="n">
         <v>-1.9</v>
       </c>
-      <c r="G18" s="5" t="n">
+      <c r="G18" s="6" t="n">
         <v>7.3</v>
       </c>
-      <c r="H18" s="5" t="n">
+      <c r="H18" s="6" t="n">
         <v>23.8</v>
       </c>
       <c r="I18" t="n">
         <v>5</v>
       </c>
-      <c r="J18" s="5" t="n">
+      <c r="J18" s="6" t="n">
         <v>8.6</v>
       </c>
       <c r="K18" t="n">
         <v>17</v>
       </c>
-      <c r="L18" s="5" t="n">
+      <c r="L18" s="6" t="n">
         <v>3.9</v>
       </c>
       <c r="M18" t="n">
         <v>16</v>
       </c>
-      <c r="N18" s="5" t="n">
+      <c r="N18" s="6" t="n">
         <v>23.1</v>
       </c>
       <c r="O18" t="n">
         <v>12</v>
       </c>
-      <c r="P18" s="5" t="n">
+      <c r="P18" s="6" t="n">
         <v>-9.4</v>
       </c>
       <c r="Q18" t="n">
         <v>14</v>
       </c>
-      <c r="R18" s="5" t="n">
+      <c r="R18" s="6" t="n">
         <v>2.1</v>
       </c>
       <c r="S18" t="n">
         <v>14</v>
       </c>
-      <c r="T18" s="5" t="n">
+      <c r="T18" s="6" t="n">
         <v>8.6</v>
       </c>
       <c r="U18" t="n">
@@ -4653,55 +4676,55 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D19" s="5" t="n">
+      <c r="D19" s="6" t="n">
         <v>-0.8</v>
       </c>
-      <c r="E19" s="5" t="n">
+      <c r="E19" s="6" t="n">
         <v>0.7</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="6" t="n">
         <v>2.4</v>
       </c>
-      <c r="G19" s="5" t="n">
+      <c r="G19" s="6" t="n">
         <v>-10.9</v>
       </c>
-      <c r="H19" s="5" t="n">
+      <c r="H19" s="6" t="n">
         <v>-1.2</v>
       </c>
       <c r="I19" t="n">
         <v>16</v>
       </c>
-      <c r="J19" s="5" t="n">
+      <c r="J19" s="6" t="n">
         <v>41.6</v>
       </c>
       <c r="K19" t="n">
         <v>4</v>
       </c>
-      <c r="L19" s="5" t="n">
+      <c r="L19" s="6" t="n">
         <v>13.9</v>
       </c>
       <c r="M19" t="n">
         <v>12</v>
       </c>
-      <c r="N19" s="5" t="n">
+      <c r="N19" s="6" t="n">
         <v>23.6</v>
       </c>
       <c r="O19" t="n">
         <v>11</v>
       </c>
-      <c r="P19" s="5" t="n">
+      <c r="P19" s="6" t="n">
         <v>4.4</v>
       </c>
       <c r="Q19" t="n">
         <v>11</v>
       </c>
-      <c r="R19" s="5" t="n">
+      <c r="R19" s="6" t="n">
         <v>6.8</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
       </c>
-      <c r="T19" s="5" t="n">
+      <c r="T19" s="6" t="n">
         <v>-13.3</v>
       </c>
       <c r="U19" t="n">
@@ -4724,55 +4747,55 @@
           <t>자동차·운송기기</t>
         </is>
       </c>
-      <c r="D20" s="5" t="n">
+      <c r="D20" s="6" t="n">
         <v>-1.2</v>
       </c>
-      <c r="E20" s="5" t="n">
+      <c r="E20" s="6" t="n">
         <v>3.4</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="6" t="n">
         <v>2.6</v>
       </c>
-      <c r="G20" s="5" t="n">
+      <c r="G20" s="6" t="n">
         <v>-5.2</v>
       </c>
-      <c r="H20" s="5" t="n">
+      <c r="H20" s="6" t="n">
         <v>-6.1</v>
       </c>
       <c r="I20" t="n">
         <v>17</v>
       </c>
-      <c r="J20" s="5" t="n">
+      <c r="J20" s="6" t="n">
         <v>13.5</v>
       </c>
       <c r="K20" t="n">
         <v>14</v>
       </c>
-      <c r="L20" s="5" t="n">
+      <c r="L20" s="6" t="n">
         <v>16.4</v>
       </c>
       <c r="M20" t="n">
         <v>11</v>
       </c>
-      <c r="N20" s="5" t="n">
+      <c r="N20" s="6" t="n">
         <v>40.5</v>
       </c>
       <c r="O20" t="n">
         <v>2</v>
       </c>
-      <c r="P20" s="5" t="n">
+      <c r="P20" s="6" t="n">
         <v>-10.7</v>
       </c>
       <c r="Q20" t="n">
         <v>16</v>
       </c>
-      <c r="R20" s="5" t="n">
+      <c r="R20" s="6" t="n">
         <v>27.8</v>
       </c>
       <c r="S20" t="n">
         <v>3</v>
       </c>
-      <c r="T20" s="5" t="n">
+      <c r="T20" s="6" t="n">
         <v>0.7</v>
       </c>
       <c r="U20" t="n">
@@ -4795,55 +4818,55 @@
           <t>에너지자원</t>
         </is>
       </c>
-      <c r="D21" s="5" t="n">
+      <c r="D21" s="6" t="n">
         <v>-1.5</v>
       </c>
-      <c r="E21" s="5" t="n">
+      <c r="E21" s="6" t="n">
         <v>-0.5</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="G21" s="5" t="n">
+      <c r="G21" s="6" t="n">
         <v>-14.8</v>
       </c>
-      <c r="H21" s="5" t="n">
+      <c r="H21" s="6" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I21" t="n">
         <v>9</v>
       </c>
-      <c r="J21" s="5" t="n">
+      <c r="J21" s="6" t="n">
         <v>41.4</v>
       </c>
       <c r="K21" t="n">
         <v>6</v>
       </c>
-      <c r="L21" s="5" t="n">
+      <c r="L21" s="6" t="n">
         <v>29.9</v>
       </c>
       <c r="M21" t="n">
         <v>3</v>
       </c>
-      <c r="N21" s="5" t="n">
+      <c r="N21" s="6" t="n">
         <v>37.2</v>
       </c>
       <c r="O21" t="n">
         <v>3</v>
       </c>
-      <c r="P21" s="5" t="n">
+      <c r="P21" s="6" t="n">
         <v>23.6</v>
       </c>
       <c r="Q21" t="n">
         <v>2</v>
       </c>
-      <c r="R21" s="5" t="n">
+      <c r="R21" s="6" t="n">
         <v>39.3</v>
       </c>
       <c r="S21" t="n">
         <v>1</v>
       </c>
-      <c r="T21" s="5" t="n">
+      <c r="T21" s="6" t="n">
         <v>-29</v>
       </c>
       <c r="U21" t="n">
@@ -4866,55 +4889,55 @@
           <t>정보통신·서비스</t>
         </is>
       </c>
-      <c r="D22" s="5" t="n">
+      <c r="D22" s="6" t="n">
         <v>-1.6</v>
       </c>
-      <c r="E22" s="5" t="n">
+      <c r="E22" s="6" t="n">
         <v>-1.3</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="G22" s="5" t="n">
+      <c r="G22" s="6" t="n">
         <v>11.6</v>
       </c>
-      <c r="H22" s="5" t="n">
+      <c r="H22" s="6" t="n">
         <v>4.5</v>
       </c>
       <c r="I22" t="n">
         <v>11</v>
       </c>
-      <c r="J22" s="5" t="n">
+      <c r="J22" s="6" t="n">
         <v>13.9</v>
       </c>
       <c r="K22" t="n">
         <v>13</v>
       </c>
-      <c r="L22" s="5" t="n">
+      <c r="L22" s="6" t="n">
         <v>21</v>
       </c>
       <c r="M22" t="n">
         <v>7</v>
       </c>
-      <c r="N22" s="5" t="n">
+      <c r="N22" s="6" t="n">
         <v>17.9</v>
       </c>
       <c r="O22" t="n">
         <v>15</v>
       </c>
-      <c r="P22" s="5" t="n">
+      <c r="P22" s="6" t="n">
         <v>-5.9</v>
       </c>
       <c r="Q22" t="n">
         <v>13</v>
       </c>
-      <c r="R22" s="5" t="n">
+      <c r="R22" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="S22" t="n">
         <v>13</v>
       </c>
-      <c r="T22" s="5" t="n">
+      <c r="T22" s="6" t="n">
         <v>21.9</v>
       </c>
       <c r="U22" t="n">
@@ -4937,55 +4960,55 @@
           <t>금융(은행외)</t>
         </is>
       </c>
-      <c r="D23" s="5" t="n">
+      <c r="D23" s="6" t="n">
         <v>-2.4</v>
       </c>
-      <c r="E23" s="5" t="n">
+      <c r="E23" s="6" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="G23" s="5" t="n">
+      <c r="G23" s="6" t="n">
         <v>10.7</v>
       </c>
-      <c r="H23" s="5" t="n">
+      <c r="H23" s="6" t="n">
         <v>24.1</v>
       </c>
       <c r="I23" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="5" t="n">
+      <c r="J23" s="6" t="n">
         <v>21.4</v>
       </c>
       <c r="K23" t="n">
         <v>10</v>
       </c>
-      <c r="L23" s="5" t="n">
+      <c r="L23" s="6" t="n">
         <v>49</v>
       </c>
       <c r="M23" t="n">
         <v>2</v>
       </c>
-      <c r="N23" s="5" t="n">
+      <c r="N23" s="6" t="n">
         <v>27.2</v>
       </c>
       <c r="O23" t="n">
         <v>10</v>
       </c>
-      <c r="P23" s="5" t="n">
+      <c r="P23" s="6" t="n">
         <v>13.7</v>
       </c>
       <c r="Q23" t="n">
         <v>6</v>
       </c>
-      <c r="R23" s="5" t="n">
+      <c r="R23" s="6" t="n">
         <v>22.6</v>
       </c>
       <c r="S23" t="n">
         <v>6</v>
       </c>
-      <c r="T23" s="5" t="n">
+      <c r="T23" s="6" t="n">
         <v>-3.6</v>
       </c>
       <c r="U23" t="n">
@@ -5008,55 +5031,55 @@
           <t>전력·가스</t>
         </is>
       </c>
-      <c r="D24" s="5" t="n">
+      <c r="D24" s="6" t="n">
         <v>-2.6</v>
       </c>
-      <c r="E24" s="5" t="n">
+      <c r="E24" s="6" t="n">
         <v>-1.9</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="6" t="n">
         <v>-1.6</v>
       </c>
-      <c r="G24" s="5" t="n">
+      <c r="G24" s="6" t="n">
         <v>-11.1</v>
       </c>
-      <c r="H24" s="5" t="n">
+      <c r="H24" s="6" t="n">
         <v>-1.1</v>
       </c>
       <c r="I24" t="n">
         <v>15</v>
       </c>
-      <c r="J24" s="5" t="n">
+      <c r="J24" s="6" t="n">
         <v>37.4</v>
       </c>
       <c r="K24" t="n">
         <v>7</v>
       </c>
-      <c r="L24" s="5" t="n">
+      <c r="L24" s="6" t="n">
         <v>6.3</v>
       </c>
       <c r="M24" t="n">
         <v>15</v>
       </c>
-      <c r="N24" s="5" t="n">
+      <c r="N24" s="6" t="n">
         <v>35</v>
       </c>
       <c r="O24" t="n">
         <v>4</v>
       </c>
-      <c r="P24" s="5" t="n">
+      <c r="P24" s="6" t="n">
         <v>13.2</v>
       </c>
       <c r="Q24" t="n">
         <v>7</v>
       </c>
-      <c r="R24" s="5" t="n">
+      <c r="R24" s="6" t="n">
         <v>-8.300000000000001</v>
       </c>
       <c r="S24" t="n">
         <v>16</v>
       </c>
-      <c r="T24" s="5" t="n">
+      <c r="T24" s="6" t="n">
         <v>-10.7</v>
       </c>
       <c r="U24" t="n">
@@ -5079,55 +5102,55 @@
           <t>건설·자재</t>
         </is>
       </c>
-      <c r="D25" s="5" t="n">
+      <c r="D25" s="6" t="n">
         <v>-3.3</v>
       </c>
-      <c r="E25" s="5" t="n">
+      <c r="E25" s="6" t="n">
         <v>-5</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="6" t="n">
         <v>-7</v>
       </c>
-      <c r="G25" s="5" t="n">
+      <c r="G25" s="6" t="n">
         <v>-0.3</v>
       </c>
-      <c r="H25" s="5" t="n">
+      <c r="H25" s="6" t="n">
         <v>9.300000000000001</v>
       </c>
       <c r="I25" t="n">
         <v>9</v>
       </c>
-      <c r="J25" s="5" t="n">
+      <c r="J25" s="6" t="n">
         <v>42</v>
       </c>
       <c r="K25" t="n">
         <v>3</v>
       </c>
-      <c r="L25" s="5" t="n">
+      <c r="L25" s="6" t="n">
         <v>21.6</v>
       </c>
       <c r="M25" t="n">
         <v>6</v>
       </c>
-      <c r="N25" s="5" t="n">
+      <c r="N25" s="6" t="n">
         <v>32</v>
       </c>
       <c r="O25" t="n">
         <v>9</v>
       </c>
-      <c r="P25" s="5" t="n">
+      <c r="P25" s="6" t="n">
         <v>-2.4</v>
       </c>
       <c r="Q25" t="n">
         <v>12</v>
       </c>
-      <c r="R25" s="5" t="n">
+      <c r="R25" s="6" t="n">
         <v>12.6</v>
       </c>
       <c r="S25" t="n">
         <v>8</v>
       </c>
-      <c r="T25" s="5" t="n">
+      <c r="T25" s="6" t="n">
         <v>-6.1</v>
       </c>
       <c r="U25" t="n">
@@ -5150,55 +5173,55 @@
           <t>전기·정밀</t>
         </is>
       </c>
-      <c r="D26" s="5" t="n">
+      <c r="D26" s="6" t="n">
         <v>-3.7</v>
       </c>
-      <c r="E26" s="5" t="n">
+      <c r="E26" s="6" t="n">
         <v>-7.9</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="6" t="n">
         <v>-11.7</v>
       </c>
-      <c r="G26" s="5" t="n">
+      <c r="G26" s="6" t="n">
         <v>12.9</v>
       </c>
-      <c r="H26" s="5" t="n">
+      <c r="H26" s="6" t="n">
         <v>28</v>
       </c>
       <c r="I26" t="n">
         <v>3</v>
       </c>
-      <c r="J26" s="5" t="n">
+      <c r="J26" s="6" t="n">
         <v>27.5</v>
       </c>
       <c r="K26" t="n">
         <v>9</v>
       </c>
-      <c r="L26" s="5" t="n">
+      <c r="L26" s="6" t="n">
         <v>17.9</v>
       </c>
       <c r="M26" t="n">
         <v>10</v>
       </c>
-      <c r="N26" s="5" t="n">
+      <c r="N26" s="6" t="n">
         <v>33.7</v>
       </c>
       <c r="O26" t="n">
         <v>7</v>
       </c>
-      <c r="P26" s="5" t="n">
+      <c r="P26" s="6" t="n">
         <v>-23</v>
       </c>
       <c r="Q26" t="n">
         <v>17</v>
       </c>
-      <c r="R26" s="5" t="n">
+      <c r="R26" s="6" t="n">
         <v>25</v>
       </c>
       <c r="S26" t="n">
         <v>5</v>
       </c>
-      <c r="T26" s="5" t="n">
+      <c r="T26" s="6" t="n">
         <v>26.2</v>
       </c>
       <c r="U26" t="n">
@@ -5221,55 +5244,55 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D27" s="5" t="n">
+      <c r="D27" s="6" t="n">
         <v>-4.7</v>
       </c>
-      <c r="E27" s="5" t="n">
+      <c r="E27" s="6" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="6" t="n">
         <v>0.4</v>
       </c>
-      <c r="G27" s="5" t="n">
+      <c r="G27" s="6" t="n">
         <v>15.9</v>
       </c>
-      <c r="H27" s="5" t="n">
+      <c r="H27" s="6" t="n">
         <v>39.9</v>
       </c>
       <c r="I27" t="n">
         <v>1</v>
       </c>
-      <c r="J27" s="5" t="n">
+      <c r="J27" s="6" t="n">
         <v>44.8</v>
       </c>
       <c r="K27" t="n">
         <v>2</v>
       </c>
-      <c r="L27" s="5" t="n">
+      <c r="L27" s="6" t="n">
         <v>50.4</v>
       </c>
       <c r="M27" t="n">
         <v>1</v>
       </c>
-      <c r="N27" s="5" t="n">
+      <c r="N27" s="6" t="n">
         <v>33.2</v>
       </c>
       <c r="O27" t="n">
         <v>8</v>
       </c>
-      <c r="P27" s="5" t="n">
+      <c r="P27" s="6" t="n">
         <v>38.3</v>
       </c>
       <c r="Q27" t="n">
         <v>1</v>
       </c>
-      <c r="R27" s="5" t="n">
+      <c r="R27" s="6" t="n">
         <v>26.7</v>
       </c>
       <c r="S27" t="n">
         <v>4</v>
       </c>
-      <c r="T27" s="5" t="n">
+      <c r="T27" s="6" t="n">
         <v>-16.3</v>
       </c>
       <c r="U27" t="n">
@@ -5292,55 +5315,55 @@
           <t>철강·비철</t>
         </is>
       </c>
-      <c r="D28" s="5" t="n">
+      <c r="D28" s="6" t="n">
         <v>-4.9</v>
       </c>
-      <c r="E28" s="5" t="n">
+      <c r="E28" s="6" t="n">
         <v>-8.699999999999999</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="6" t="n">
         <v>-16</v>
       </c>
-      <c r="G28" s="5" t="n">
+      <c r="G28" s="6" t="n">
         <v>-16.9</v>
       </c>
-      <c r="H28" s="5" t="n">
+      <c r="H28" s="6" t="n">
         <v>32.2</v>
       </c>
       <c r="I28" t="n">
         <v>2</v>
       </c>
-      <c r="J28" s="5" t="n">
+      <c r="J28" s="6" t="n">
         <v>68.8</v>
       </c>
       <c r="K28" t="n">
         <v>1</v>
       </c>
-      <c r="L28" s="5" t="n">
+      <c r="L28" s="6" t="n">
         <v>20.6</v>
       </c>
       <c r="M28" t="n">
         <v>8</v>
       </c>
-      <c r="N28" s="5" t="n">
+      <c r="N28" s="6" t="n">
         <v>35</v>
       </c>
       <c r="O28" t="n">
         <v>4</v>
       </c>
-      <c r="P28" s="5" t="n">
+      <c r="P28" s="6" t="n">
         <v>16.1</v>
       </c>
       <c r="Q28" t="n">
         <v>5</v>
       </c>
-      <c r="R28" s="5" t="n">
+      <c r="R28" s="6" t="n">
         <v>20.8</v>
       </c>
       <c r="S28" t="n">
         <v>7</v>
       </c>
-      <c r="T28" s="5" t="n">
+      <c r="T28" s="6" t="n">
         <v>-8.6</v>
       </c>
       <c r="U28" t="n">
@@ -5363,55 +5386,55 @@
           <t>기계</t>
         </is>
       </c>
-      <c r="D29" s="5" t="n">
+      <c r="D29" s="6" t="n">
         <v>-5.9</v>
       </c>
-      <c r="E29" s="5" t="n">
+      <c r="E29" s="6" t="n">
         <v>-7.6</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="6" t="n">
         <v>-10.6</v>
       </c>
-      <c r="G29" s="5" t="n">
+      <c r="G29" s="6" t="n">
         <v>-7.8</v>
       </c>
-      <c r="H29" s="5" t="n">
+      <c r="H29" s="6" t="n">
         <v>13.7</v>
       </c>
       <c r="I29" t="n">
         <v>7</v>
       </c>
-      <c r="J29" s="5" t="n">
+      <c r="J29" s="6" t="n">
         <v>31.1</v>
       </c>
       <c r="K29" t="n">
         <v>8</v>
       </c>
-      <c r="L29" s="5" t="n">
+      <c r="L29" s="6" t="n">
         <v>22.3</v>
       </c>
       <c r="M29" t="n">
         <v>5</v>
       </c>
-      <c r="N29" s="5" t="n">
+      <c r="N29" s="6" t="n">
         <v>33.9</v>
       </c>
       <c r="O29" t="n">
         <v>6</v>
       </c>
-      <c r="P29" s="5" t="n">
+      <c r="P29" s="6" t="n">
         <v>-9.9</v>
       </c>
       <c r="Q29" t="n">
         <v>15</v>
       </c>
-      <c r="R29" s="5" t="n">
+      <c r="R29" s="6" t="n">
         <v>7.5</v>
       </c>
       <c r="S29" t="n">
         <v>9</v>
       </c>
-      <c r="T29" s="5" t="n">
+      <c r="T29" s="6" t="n">
         <v>17.7</v>
       </c>
       <c r="U29" t="n">
@@ -5434,55 +5457,55 @@
           <t>항셍지수</t>
         </is>
       </c>
-      <c r="D30" s="5" t="n">
+      <c r="D30" s="6" t="n">
         <v>-1.9</v>
       </c>
-      <c r="E30" s="5" t="n">
+      <c r="E30" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="G30" s="5" t="n">
+      <c r="G30" s="6" t="n">
         <v>-4.1</v>
       </c>
-      <c r="H30" s="5" t="n">
+      <c r="H30" s="6" t="n">
         <v>-2.5</v>
       </c>
       <c r="I30" t="n">
         <v>1</v>
       </c>
-      <c r="J30" s="5" t="n">
+      <c r="J30" s="6" t="n">
         <v>32.8</v>
       </c>
       <c r="K30" t="n">
         <v>1</v>
       </c>
-      <c r="L30" s="5" t="n">
+      <c r="L30" s="6" t="n">
         <v>24.8</v>
       </c>
       <c r="M30" t="n">
         <v>2</v>
       </c>
-      <c r="N30" s="5" t="n">
+      <c r="N30" s="6" t="n">
         <v>-11.9</v>
       </c>
       <c r="O30" t="n">
         <v>2</v>
       </c>
-      <c r="P30" s="5" t="n">
+      <c r="P30" s="6" t="n">
         <v>-14.4</v>
       </c>
       <c r="Q30" t="n">
         <v>1</v>
       </c>
-      <c r="R30" s="5" t="n">
+      <c r="R30" s="6" t="n">
         <v>-13.5</v>
       </c>
       <c r="S30" t="n">
         <v>1</v>
       </c>
-      <c r="T30" s="5" t="n">
+      <c r="T30" s="6" t="n">
         <v>-1.2</v>
       </c>
       <c r="U30" t="n">
@@ -5505,55 +5528,55 @@
           <t>H주(중국기업)</t>
         </is>
       </c>
-      <c r="D31" s="5" t="n">
+      <c r="D31" s="6" t="n">
         <v>-2.2</v>
       </c>
-      <c r="E31" s="5" t="n">
+      <c r="E31" s="6" t="n">
         <v>1.3</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="6" t="n">
         <v>-0.4</v>
       </c>
-      <c r="G31" s="5" t="n">
+      <c r="G31" s="6" t="n">
         <v>-5.5</v>
       </c>
-      <c r="H31" s="5" t="n">
+      <c r="H31" s="6" t="n">
         <v>-7.6</v>
       </c>
       <c r="I31" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="5" t="n">
+      <c r="J31" s="6" t="n">
         <v>26.2</v>
       </c>
       <c r="K31" t="n">
         <v>2</v>
       </c>
-      <c r="L31" s="5" t="n">
+      <c r="L31" s="6" t="n">
         <v>32.1</v>
       </c>
       <c r="M31" t="n">
         <v>1</v>
       </c>
-      <c r="N31" s="5" t="n">
+      <c r="N31" s="6" t="n">
         <v>-12.8</v>
       </c>
       <c r="O31" t="n">
         <v>3</v>
       </c>
-      <c r="P31" s="5" t="n">
+      <c r="P31" s="6" t="n">
         <v>-17.8</v>
       </c>
       <c r="Q31" t="n">
         <v>2</v>
       </c>
-      <c r="R31" s="5" t="n">
+      <c r="R31" s="6" t="n">
         <v>-23.6</v>
       </c>
       <c r="S31" t="n">
         <v>2</v>
       </c>
-      <c r="T31" s="5" t="n">
+      <c r="T31" s="6" t="n">
         <v>-2</v>
       </c>
       <c r="U31" t="n">
@@ -5576,55 +5599,55 @@
           <t>항셍테크</t>
         </is>
       </c>
-      <c r="D32" s="5" t="n">
+      <c r="D32" s="6" t="n">
         <v>-4.5</v>
       </c>
-      <c r="E32" s="5" t="n">
+      <c r="E32" s="6" t="n">
         <v>-2.2</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="6" t="n">
         <v>-0.6</v>
       </c>
-      <c r="G32" s="5" t="n">
+      <c r="G32" s="6" t="n">
         <v>-5.8</v>
       </c>
-      <c r="H32" s="5" t="n">
+      <c r="H32" s="6" t="n">
         <v>-15.9</v>
       </c>
       <c r="I32" t="n">
         <v>3</v>
       </c>
-      <c r="J32" s="5" t="n">
+      <c r="J32" s="6" t="n">
         <v>22.7</v>
       </c>
       <c r="K32" t="n">
         <v>3</v>
       </c>
-      <c r="L32" s="5" t="n">
+      <c r="L32" s="6" t="n">
         <v>18.9</v>
       </c>
       <c r="M32" t="n">
         <v>3</v>
       </c>
-      <c r="N32" s="5" t="n">
+      <c r="N32" s="6" t="n">
         <v>-9.300000000000001</v>
       </c>
       <c r="O32" t="n">
         <v>1</v>
       </c>
-      <c r="P32" s="5" t="n">
+      <c r="P32" s="6" t="n">
         <v>-27.4</v>
       </c>
       <c r="Q32" t="n">
         <v>3</v>
       </c>
-      <c r="R32" s="5" t="n">
+      <c r="R32" s="6" t="n">
         <v>-32.9</v>
       </c>
       <c r="S32" t="n">
         <v>3</v>
       </c>
-      <c r="T32" s="5" t="inlineStr"/>
+      <c r="T32" s="6" t="inlineStr"/>
       <c r="U32" t="inlineStr"/>
     </row>
     <row r="33">
@@ -5643,55 +5666,55 @@
           <t>은행</t>
         </is>
       </c>
-      <c r="D33" s="5" t="n">
+      <c r="D33" s="6" t="n">
         <v>0.9</v>
       </c>
-      <c r="E33" s="5" t="n">
+      <c r="E33" s="6" t="n">
         <v>2.9</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="6" t="n">
         <v>0.5</v>
       </c>
-      <c r="G33" s="5" t="n">
+      <c r="G33" s="6" t="n">
         <v>-1.6</v>
       </c>
-      <c r="H33" s="5" t="n">
+      <c r="H33" s="6" t="n">
         <v>-4.1</v>
       </c>
       <c r="I33" t="n">
         <v>5</v>
       </c>
-      <c r="J33" s="5" t="n">
+      <c r="J33" s="6" t="n">
         <v>10.8</v>
       </c>
       <c r="K33" t="n">
         <v>8</v>
       </c>
-      <c r="L33" s="5" t="n">
+      <c r="L33" s="6" t="n">
         <v>42.6</v>
       </c>
       <c r="M33" t="n">
         <v>1</v>
       </c>
-      <c r="N33" s="5" t="n">
+      <c r="N33" s="6" t="n">
         <v>-3.3</v>
       </c>
       <c r="O33" t="n">
         <v>5</v>
       </c>
-      <c r="P33" s="5" t="n">
+      <c r="P33" s="6" t="n">
         <v>-4.8</v>
       </c>
       <c r="Q33" t="n">
         <v>1</v>
       </c>
-      <c r="R33" s="5" t="n">
+      <c r="R33" s="6" t="n">
         <v>-1.2</v>
       </c>
       <c r="S33" t="n">
         <v>7</v>
       </c>
-      <c r="T33" s="5" t="n">
+      <c r="T33" s="6" t="n">
         <v>1.2</v>
       </c>
       <c r="U33" t="n">
@@ -5714,55 +5737,55 @@
           <t>증권</t>
         </is>
       </c>
-      <c r="D34" s="5" t="n">
+      <c r="D34" s="6" t="n">
         <v>-1.4</v>
       </c>
-      <c r="E34" s="5" t="n">
+      <c r="E34" s="6" t="n">
         <v>-1.2</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="6" t="n">
         <v>1.5</v>
       </c>
-      <c r="G34" s="5" t="n">
+      <c r="G34" s="6" t="n">
         <v>2.2</v>
       </c>
-      <c r="H34" s="5" t="n">
+      <c r="H34" s="6" t="n">
         <v>-9.4</v>
       </c>
       <c r="I34" t="n">
         <v>6</v>
       </c>
-      <c r="J34" s="5" t="n">
+      <c r="J34" s="6" t="n">
         <v>3.5</v>
       </c>
       <c r="K34" t="n">
         <v>10</v>
       </c>
-      <c r="L34" s="5" t="n">
+      <c r="L34" s="6" t="n">
         <v>29.7</v>
       </c>
       <c r="M34" t="n">
         <v>2</v>
       </c>
-      <c r="N34" s="5" t="n">
+      <c r="N34" s="6" t="n">
         <v>3.8</v>
       </c>
       <c r="O34" t="n">
         <v>2</v>
       </c>
-      <c r="P34" s="5" t="n">
+      <c r="P34" s="6" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q34" t="n">
         <v>8</v>
       </c>
-      <c r="R34" s="5" t="n">
+      <c r="R34" s="6" t="n">
         <v>-3.8</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
       </c>
-      <c r="T34" s="5" t="n">
+      <c r="T34" s="6" t="n">
         <v>17.5</v>
       </c>
       <c r="U34" t="n">
@@ -5785,55 +5808,55 @@
           <t>백주(주류)</t>
         </is>
       </c>
-      <c r="D35" s="5" t="n">
+      <c r="D35" s="6" t="n">
         <v>-1.7</v>
       </c>
-      <c r="E35" s="5" t="n">
+      <c r="E35" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="G35" s="5" t="n">
+      <c r="G35" s="6" t="n">
         <v>-16.1</v>
       </c>
-      <c r="H35" s="5" t="n">
+      <c r="H35" s="6" t="n">
         <v>-22.9</v>
       </c>
       <c r="I35" t="n">
         <v>13</v>
       </c>
-      <c r="J35" s="5" t="n">
+      <c r="J35" s="6" t="n">
         <v>-13</v>
       </c>
       <c r="K35" t="n">
         <v>13</v>
       </c>
-      <c r="L35" s="5" t="n">
+      <c r="L35" s="6" t="n">
         <v>-11</v>
       </c>
       <c r="M35" t="n">
         <v>11</v>
       </c>
-      <c r="N35" s="5" t="n">
+      <c r="N35" s="6" t="n">
         <v>-18.6</v>
       </c>
       <c r="O35" t="n">
         <v>10</v>
       </c>
-      <c r="P35" s="5" t="n">
+      <c r="P35" s="6" t="n">
         <v>-11.9</v>
       </c>
       <c r="Q35" t="n">
         <v>3</v>
       </c>
-      <c r="R35" s="5" t="n">
+      <c r="R35" s="6" t="n">
         <v>-3</v>
       </c>
       <c r="S35" t="n">
         <v>9</v>
       </c>
-      <c r="T35" s="5" t="n">
+      <c r="T35" s="6" t="n">
         <v>302.8</v>
       </c>
       <c r="U35" t="n">
@@ -5856,55 +5879,55 @@
           <t>소비(消费)</t>
         </is>
       </c>
-      <c r="D36" s="5" t="n">
+      <c r="D36" s="6" t="n">
         <v>-1.8</v>
       </c>
-      <c r="E36" s="5" t="n">
+      <c r="E36" s="6" t="n">
         <v>3.3</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="6" t="n">
         <v>2.8</v>
       </c>
-      <c r="G36" s="5" t="n">
+      <c r="G36" s="6" t="n">
         <v>-13.2</v>
       </c>
-      <c r="H36" s="5" t="n">
+      <c r="H36" s="6" t="n">
         <v>-17.7</v>
       </c>
       <c r="I36" t="n">
         <v>10</v>
       </c>
-      <c r="J36" s="5" t="n">
+      <c r="J36" s="6" t="n">
         <v>-2.9</v>
       </c>
       <c r="K36" t="n">
         <v>12</v>
       </c>
-      <c r="L36" s="5" t="n">
+      <c r="L36" s="6" t="n">
         <v>-4.2</v>
       </c>
       <c r="M36" t="n">
         <v>10</v>
       </c>
-      <c r="N36" s="5" t="n">
+      <c r="N36" s="6" t="n">
         <v>-18.3</v>
       </c>
       <c r="O36" t="n">
         <v>9</v>
       </c>
-      <c r="P36" s="5" t="n">
+      <c r="P36" s="6" t="n">
         <v>-13.4</v>
       </c>
       <c r="Q36" t="n">
         <v>4</v>
       </c>
-      <c r="R36" s="5" t="n">
+      <c r="R36" s="6" t="n">
         <v>-7.5</v>
       </c>
       <c r="S36" t="n">
         <v>12</v>
       </c>
-      <c r="T36" s="5" t="n">
+      <c r="T36" s="6" t="n">
         <v>72.7</v>
       </c>
       <c r="U36" t="n">
@@ -5927,55 +5950,55 @@
           <t>신에너지차</t>
         </is>
       </c>
-      <c r="D37" s="5" t="n">
+      <c r="D37" s="6" t="n">
         <v>-3</v>
       </c>
-      <c r="E37" s="5" t="n">
+      <c r="E37" s="6" t="n">
         <v>-7.1</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="6" t="n">
         <v>-20.1</v>
       </c>
-      <c r="G37" s="5" t="n">
+      <c r="G37" s="6" t="n">
         <v>-21</v>
       </c>
-      <c r="H37" s="5" t="n">
+      <c r="H37" s="6" t="n">
         <v>-17</v>
       </c>
       <c r="I37" t="n">
         <v>8</v>
       </c>
-      <c r="J37" s="5" t="n">
+      <c r="J37" s="6" t="n">
         <v>56.6</v>
       </c>
       <c r="K37" t="n">
         <v>3</v>
       </c>
-      <c r="L37" s="5" t="n">
+      <c r="L37" s="6" t="n">
         <v>0.3</v>
       </c>
       <c r="M37" t="n">
         <v>8</v>
       </c>
-      <c r="N37" s="5" t="n">
+      <c r="N37" s="6" t="n">
         <v>-29</v>
       </c>
       <c r="O37" t="n">
         <v>12</v>
       </c>
-      <c r="P37" s="5" t="n">
+      <c r="P37" s="6" t="n">
         <v>-28.9</v>
       </c>
       <c r="Q37" t="n">
         <v>10</v>
       </c>
-      <c r="R37" s="5" t="n">
+      <c r="R37" s="6" t="n">
         <v>41.9</v>
       </c>
       <c r="S37" t="n">
         <v>2</v>
       </c>
-      <c r="T37" s="5" t="inlineStr"/>
+      <c r="T37" s="6" t="inlineStr"/>
       <c r="U37" t="inlineStr"/>
     </row>
     <row r="38">
@@ -5994,55 +6017,55 @@
           <t>태양광</t>
         </is>
       </c>
-      <c r="D38" s="5" t="n">
+      <c r="D38" s="6" t="n">
         <v>-3.5</v>
       </c>
-      <c r="E38" s="5" t="n">
+      <c r="E38" s="6" t="n">
         <v>-11.1</v>
       </c>
-      <c r="F38" s="5" t="n">
+      <c r="F38" s="6" t="n">
         <v>-22.4</v>
       </c>
-      <c r="G38" s="5" t="n">
+      <c r="G38" s="6" t="n">
         <v>-24.7</v>
       </c>
-      <c r="H38" s="5" t="n">
+      <c r="H38" s="6" t="n">
         <v>-17.2</v>
       </c>
       <c r="I38" t="n">
         <v>9</v>
       </c>
-      <c r="J38" s="5" t="n">
+      <c r="J38" s="6" t="n">
         <v>27.1</v>
       </c>
       <c r="K38" t="n">
         <v>7</v>
       </c>
-      <c r="L38" s="5" t="n">
+      <c r="L38" s="6" t="n">
         <v>-14.9</v>
       </c>
       <c r="M38" t="n">
         <v>13</v>
       </c>
-      <c r="N38" s="5" t="n">
+      <c r="N38" s="6" t="n">
         <v>-35.2</v>
       </c>
       <c r="O38" t="n">
         <v>13</v>
       </c>
-      <c r="P38" s="5" t="n">
+      <c r="P38" s="6" t="n">
         <v>-19.7</v>
       </c>
       <c r="Q38" t="n">
         <v>5</v>
       </c>
-      <c r="R38" s="5" t="n">
+      <c r="R38" s="6" t="n">
         <v>50.7</v>
       </c>
       <c r="S38" t="n">
         <v>1</v>
       </c>
-      <c r="T38" s="5" t="inlineStr"/>
+      <c r="T38" s="6" t="inlineStr"/>
       <c r="U38" t="inlineStr"/>
     </row>
     <row r="39">
@@ -6061,55 +6084,55 @@
           <t>의약</t>
         </is>
       </c>
-      <c r="D39" s="5" t="n">
+      <c r="D39" s="6" t="n">
         <v>-3.7</v>
       </c>
-      <c r="E39" s="5" t="n">
+      <c r="E39" s="6" t="n">
         <v>0.3</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="6" t="n">
         <v>12.7</v>
       </c>
-      <c r="G39" s="5" t="n">
+      <c r="G39" s="6" t="n">
         <v>-3.4</v>
       </c>
-      <c r="H39" s="5" t="n">
+      <c r="H39" s="6" t="n">
         <v>-3.7</v>
       </c>
       <c r="I39" t="n">
         <v>4</v>
       </c>
-      <c r="J39" s="5" t="n">
+      <c r="J39" s="6" t="n">
         <v>4.7</v>
       </c>
       <c r="K39" t="n">
         <v>9</v>
       </c>
-      <c r="L39" s="5" t="n">
+      <c r="L39" s="6" t="n">
         <v>-12.2</v>
       </c>
       <c r="M39" t="n">
         <v>12</v>
       </c>
-      <c r="N39" s="5" t="n">
+      <c r="N39" s="6" t="n">
         <v>-14</v>
       </c>
       <c r="O39" t="n">
         <v>8</v>
       </c>
-      <c r="P39" s="5" t="n">
+      <c r="P39" s="6" t="n">
         <v>-24.5</v>
       </c>
       <c r="Q39" t="n">
         <v>7</v>
       </c>
-      <c r="R39" s="5" t="n">
+      <c r="R39" s="6" t="n">
         <v>-15.7</v>
       </c>
       <c r="S39" t="n">
         <v>13</v>
       </c>
-      <c r="T39" s="5" t="n">
+      <c r="T39" s="6" t="n">
         <v>58.4</v>
       </c>
       <c r="U39" t="n">
@@ -6132,55 +6155,55 @@
           <t>부동산</t>
         </is>
       </c>
-      <c r="D40" s="5" t="n">
+      <c r="D40" s="6" t="n">
         <v>-4.4</v>
       </c>
-      <c r="E40" s="5" t="n">
+      <c r="E40" s="6" t="n">
         <v>-4.9</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="6" t="n">
         <v>-8</v>
       </c>
-      <c r="G40" s="5" t="n">
+      <c r="G40" s="6" t="n">
         <v>-16</v>
       </c>
-      <c r="H40" s="5" t="n">
+      <c r="H40" s="6" t="n">
         <v>-22.8</v>
       </c>
       <c r="I40" t="n">
         <v>12</v>
       </c>
-      <c r="J40" s="5" t="n">
+      <c r="J40" s="6" t="n">
         <v>2.5</v>
       </c>
       <c r="K40" t="n">
         <v>11</v>
       </c>
-      <c r="L40" s="5" t="n">
+      <c r="L40" s="6" t="n">
         <v>-0.5</v>
       </c>
       <c r="M40" t="n">
         <v>9</v>
       </c>
-      <c r="N40" s="5" t="n">
+      <c r="N40" s="6" t="n">
         <v>-27</v>
       </c>
       <c r="O40" t="n">
         <v>11</v>
       </c>
-      <c r="P40" s="5" t="n">
+      <c r="P40" s="6" t="n">
         <v>-10.4</v>
       </c>
       <c r="Q40" t="n">
         <v>2</v>
       </c>
-      <c r="R40" s="5" t="n">
+      <c r="R40" s="6" t="n">
         <v>-6.4</v>
       </c>
       <c r="S40" t="n">
         <v>11</v>
       </c>
-      <c r="T40" s="5" t="n">
+      <c r="T40" s="6" t="n">
         <v>-6.6</v>
       </c>
       <c r="U40" t="n">
@@ -6203,55 +6226,55 @@
           <t>방산(军工)</t>
         </is>
       </c>
-      <c r="D41" s="5" t="n">
+      <c r="D41" s="6" t="n">
         <v>-5.2</v>
       </c>
-      <c r="E41" s="5" t="n">
+      <c r="E41" s="6" t="n">
         <v>-17.1</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="6" t="n">
         <v>-17.6</v>
       </c>
-      <c r="G41" s="5" t="n">
+      <c r="G41" s="6" t="n">
         <v>-22.3</v>
       </c>
-      <c r="H41" s="5" t="n">
+      <c r="H41" s="6" t="n">
         <v>-22.7</v>
       </c>
       <c r="I41" t="n">
         <v>11</v>
       </c>
-      <c r="J41" s="5" t="n">
+      <c r="J41" s="6" t="n">
         <v>31.8</v>
       </c>
       <c r="K41" t="n">
         <v>6</v>
       </c>
-      <c r="L41" s="5" t="n">
+      <c r="L41" s="6" t="n">
         <v>8.5</v>
       </c>
       <c r="M41" t="n">
         <v>6</v>
       </c>
-      <c r="N41" s="5" t="n">
+      <c r="N41" s="6" t="n">
         <v>-10.8</v>
       </c>
       <c r="O41" t="n">
         <v>6</v>
       </c>
-      <c r="P41" s="5" t="n">
+      <c r="P41" s="6" t="n">
         <v>-26.1</v>
       </c>
       <c r="Q41" t="n">
         <v>8</v>
       </c>
-      <c r="R41" s="5" t="n">
+      <c r="R41" s="6" t="n">
         <v>13.1</v>
       </c>
       <c r="S41" t="n">
         <v>5</v>
       </c>
-      <c r="T41" s="5" t="n">
+      <c r="T41" s="6" t="n">
         <v>69.90000000000001</v>
       </c>
       <c r="U41" t="n">
@@ -6274,55 +6297,55 @@
           <t>유색금속</t>
         </is>
       </c>
-      <c r="D42" s="5" t="n">
+      <c r="D42" s="6" t="n">
         <v>-5.2</v>
       </c>
-      <c r="E42" s="5" t="n">
+      <c r="E42" s="6" t="n">
         <v>-6.8</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="6" t="n">
         <v>-20</v>
       </c>
-      <c r="G42" s="5" t="n">
+      <c r="G42" s="6" t="n">
         <v>-22.2</v>
       </c>
-      <c r="H42" s="5" t="n">
+      <c r="H42" s="6" t="n">
         <v>-15.1</v>
       </c>
       <c r="I42" t="n">
         <v>7</v>
       </c>
-      <c r="J42" s="5" t="n">
+      <c r="J42" s="6" t="n">
         <v>101.1</v>
       </c>
       <c r="K42" t="n">
         <v>1</v>
       </c>
-      <c r="L42" s="5" t="n">
+      <c r="L42" s="6" t="n">
         <v>4.1</v>
       </c>
       <c r="M42" t="n">
         <v>7</v>
       </c>
-      <c r="N42" s="5" t="n">
+      <c r="N42" s="6" t="n">
         <v>-11.4</v>
       </c>
       <c r="O42" t="n">
         <v>7</v>
       </c>
-      <c r="P42" s="5" t="n">
+      <c r="P42" s="6" t="n">
         <v>-21.6</v>
       </c>
       <c r="Q42" t="n">
         <v>6</v>
       </c>
-      <c r="R42" s="5" t="n">
+      <c r="R42" s="6" t="n">
         <v>33.2</v>
       </c>
       <c r="S42" t="n">
         <v>3</v>
       </c>
-      <c r="T42" s="5" t="n">
+      <c r="T42" s="6" t="n">
         <v>41.8</v>
       </c>
       <c r="U42" t="n">
@@ -6345,55 +6368,55 @@
           <t>반도체</t>
         </is>
       </c>
-      <c r="D43" s="5" t="n">
+      <c r="D43" s="6" t="n">
         <v>-7.7</v>
       </c>
-      <c r="E43" s="5" t="n">
+      <c r="E43" s="6" t="n">
         <v>-21.8</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="6" t="n">
         <v>-10.4</v>
       </c>
-      <c r="G43" s="5" t="n">
+      <c r="G43" s="6" t="n">
         <v>33.9</v>
       </c>
-      <c r="H43" s="5" t="n">
+      <c r="H43" s="6" t="n">
         <v>46.2</v>
       </c>
       <c r="I43" t="n">
         <v>1</v>
       </c>
-      <c r="J43" s="5" t="n">
+      <c r="J43" s="6" t="n">
         <v>45</v>
       </c>
       <c r="K43" t="n">
         <v>5</v>
       </c>
-      <c r="L43" s="5" t="n">
+      <c r="L43" s="6" t="n">
         <v>25.6</v>
       </c>
       <c r="M43" t="n">
         <v>3</v>
       </c>
-      <c r="N43" s="5" t="n">
+      <c r="N43" s="6" t="n">
         <v>-2.4</v>
       </c>
       <c r="O43" t="n">
         <v>4</v>
       </c>
-      <c r="P43" s="5" t="n">
+      <c r="P43" s="6" t="n">
         <v>-36.6</v>
       </c>
       <c r="Q43" t="n">
         <v>12</v>
       </c>
-      <c r="R43" s="5" t="n">
+      <c r="R43" s="6" t="n">
         <v>23.8</v>
       </c>
       <c r="S43" t="n">
         <v>4</v>
       </c>
-      <c r="T43" s="5" t="n">
+      <c r="T43" s="6" t="n">
         <v>46.2</v>
       </c>
       <c r="U43" t="n">
@@ -6416,55 +6439,55 @@
           <t>테크(科技)</t>
         </is>
       </c>
-      <c r="D44" s="5" t="n">
+      <c r="D44" s="6" t="n">
         <v>-8.199999999999999</v>
       </c>
-      <c r="E44" s="5" t="n">
+      <c r="E44" s="6" t="n">
         <v>-16.8</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="F44" s="6" t="n">
         <v>-14.4</v>
       </c>
-      <c r="G44" s="5" t="n">
+      <c r="G44" s="6" t="n">
         <v>18.5</v>
       </c>
-      <c r="H44" s="5" t="n">
+      <c r="H44" s="6" t="n">
         <v>29.1</v>
       </c>
       <c r="I44" t="n">
         <v>3</v>
       </c>
-      <c r="J44" s="5" t="n">
+      <c r="J44" s="6" t="n">
         <v>52.1</v>
       </c>
       <c r="K44" t="n">
         <v>4</v>
       </c>
-      <c r="L44" s="5" t="n">
+      <c r="L44" s="6" t="n">
         <v>12</v>
       </c>
       <c r="M44" t="n">
         <v>5</v>
       </c>
-      <c r="N44" s="5" t="n">
+      <c r="N44" s="6" t="n">
         <v>0.5</v>
       </c>
       <c r="O44" t="n">
         <v>3</v>
       </c>
-      <c r="P44" s="5" t="n">
+      <c r="P44" s="6" t="n">
         <v>-34</v>
       </c>
       <c r="Q44" t="n">
         <v>11</v>
       </c>
-      <c r="R44" s="5" t="n">
+      <c r="R44" s="6" t="n">
         <v>-2.8</v>
       </c>
       <c r="S44" t="n">
         <v>8</v>
       </c>
-      <c r="T44" s="5" t="n">
+      <c r="T44" s="6" t="n">
         <v>44</v>
       </c>
       <c r="U44" t="n">
@@ -6487,55 +6510,55 @@
           <t>5G통신</t>
         </is>
       </c>
-      <c r="D45" s="5" t="n">
+      <c r="D45" s="6" t="n">
         <v>-10</v>
       </c>
-      <c r="E45" s="5" t="n">
+      <c r="E45" s="6" t="n">
         <v>-13.8</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="6" t="n">
         <v>-20.9</v>
       </c>
-      <c r="G45" s="5" t="n">
+      <c r="G45" s="6" t="n">
         <v>17.6</v>
       </c>
-      <c r="H45" s="5" t="n">
+      <c r="H45" s="6" t="n">
         <v>38.9</v>
       </c>
       <c r="I45" t="n">
         <v>2</v>
       </c>
-      <c r="J45" s="5" t="n">
+      <c r="J45" s="6" t="n">
         <v>99.7</v>
       </c>
       <c r="K45" t="n">
         <v>2</v>
       </c>
-      <c r="L45" s="5" t="n">
+      <c r="L45" s="6" t="n">
         <v>24.2</v>
       </c>
       <c r="M45" t="n">
         <v>4</v>
       </c>
-      <c r="N45" s="5" t="n">
+      <c r="N45" s="6" t="n">
         <v>16.3</v>
       </c>
       <c r="O45" t="n">
         <v>1</v>
       </c>
-      <c r="P45" s="5" t="n">
+      <c r="P45" s="6" t="n">
         <v>-37.8</v>
       </c>
       <c r="Q45" t="n">
         <v>13</v>
       </c>
-      <c r="R45" s="5" t="n">
+      <c r="R45" s="6" t="n">
         <v>6.8</v>
       </c>
       <c r="S45" t="n">
         <v>6</v>
       </c>
-      <c r="T45" s="5" t="n">
+      <c r="T45" s="6" t="n">
         <v>19.3</v>
       </c>
       <c r="U45" t="n">
@@ -6778,7 +6801,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6826,14 +6849,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>3Q 매출 가이던스 컨센 하회+참여도 공시 축소에 -7%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6877,14 +6900,14 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>2Q 실적 미스+호주 제련소 사고로 알루미나 가이던스 하향</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6934,14 +6957,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>개별 촉매 없이 바이오 섹터 매도세 속 52주 신저가</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -6987,14 +7010,14 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>AI데이터센터·비트코인 채굴주 동반 급락, 6일 연속 하락</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7040,14 +7063,14 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>$1.65B Superior 인수 후 레버리지 우려·차익실현</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7093,10 +7116,10 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7142,10 +7165,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7191,10 +7214,10 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7240,10 +7263,10 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7289,10 +7312,10 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7338,10 +7361,10 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7387,10 +7410,10 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7436,10 +7459,10 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7485,10 +7508,10 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7534,10 +7557,10 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="6" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7583,10 +7606,10 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="6" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7632,10 +7655,10 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="6" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7681,10 +7704,10 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7730,10 +7753,10 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="6" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7777,10 +7800,10 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7826,10 +7849,10 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7875,10 +7898,10 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7924,10 +7947,10 @@
         </is>
       </c>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" s="6" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -7973,10 +7996,10 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="6" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8022,10 +8045,10 @@
         </is>
       </c>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" s="6" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8071,10 +8094,10 @@
         </is>
       </c>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" s="6" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8120,10 +8143,10 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="6" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8169,10 +8192,10 @@
         </is>
       </c>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" s="6" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8216,10 +8239,10 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="6" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8265,10 +8288,10 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="6" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8314,10 +8337,10 @@
         </is>
       </c>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" s="6" t="inlineStr"/>
+      <c r="M32" s="7" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8363,10 +8386,10 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="6" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8412,10 +8435,10 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="6" t="inlineStr"/>
+      <c r="M34" s="7" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8461,10 +8484,10 @@
         </is>
       </c>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" s="6" t="inlineStr"/>
+      <c r="M35" s="7" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8510,10 +8533,10 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="6" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8559,10 +8582,10 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="6" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8608,10 +8631,10 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="6" t="inlineStr"/>
+      <c r="M38" s="7" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8655,10 +8678,10 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="6" t="inlineStr"/>
+      <c r="M39" s="7" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8704,10 +8727,10 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="6" t="inlineStr"/>
+      <c r="M40" s="7" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8751,10 +8774,10 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="6" t="inlineStr"/>
+      <c r="M41" s="7" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8800,10 +8823,10 @@
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" s="6" t="inlineStr"/>
+      <c r="M42" s="7" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="4" t="inlineStr">
+      <c r="A43" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8849,10 +8872,10 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="6" t="inlineStr"/>
+      <c r="M43" s="7" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="4" t="inlineStr">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8898,10 +8921,10 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="6" t="inlineStr"/>
+      <c r="M44" s="7" t="inlineStr"/>
     </row>
     <row r="45">
-      <c r="A45" s="4" t="inlineStr">
+      <c r="A45" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8947,10 +8970,10 @@
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" s="6" t="inlineStr"/>
+      <c r="M45" s="7" t="inlineStr"/>
     </row>
     <row r="46">
-      <c r="A46" s="4" t="inlineStr">
+      <c r="A46" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -8996,10 +9019,10 @@
         </is>
       </c>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" s="6" t="inlineStr"/>
+      <c r="M46" s="7" t="inlineStr"/>
     </row>
     <row r="47">
-      <c r="A47" s="4" t="inlineStr">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9049,10 +9072,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M47" s="6" t="inlineStr"/>
+      <c r="M47" s="7" t="inlineStr"/>
     </row>
     <row r="48">
-      <c r="A48" s="4" t="inlineStr">
+      <c r="A48" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9098,10 +9121,10 @@
         </is>
       </c>
       <c r="L48" t="inlineStr"/>
-      <c r="M48" s="6" t="inlineStr"/>
+      <c r="M48" s="7" t="inlineStr"/>
     </row>
     <row r="49">
-      <c r="A49" s="4" t="inlineStr">
+      <c r="A49" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9147,10 +9170,10 @@
         </is>
       </c>
       <c r="L49" t="inlineStr"/>
-      <c r="M49" s="6" t="inlineStr"/>
+      <c r="M49" s="7" t="inlineStr"/>
     </row>
     <row r="50">
-      <c r="A50" s="4" t="inlineStr">
+      <c r="A50" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9194,10 +9217,10 @@
         </is>
       </c>
       <c r="L50" t="inlineStr"/>
-      <c r="M50" s="6" t="inlineStr"/>
+      <c r="M50" s="7" t="inlineStr"/>
     </row>
     <row r="51">
-      <c r="A51" s="4" t="inlineStr">
+      <c r="A51" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9245,14 +9268,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M51" s="6" t="inlineStr">
+      <c r="M51" s="7" t="inlineStr">
         <is>
           <t>(전일) HCA發 수술량 둔화 우려·목표가 인하($585→$520), 7/16 실적 앞 매도</t>
         </is>
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9302,10 +9325,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M52" s="6" t="inlineStr"/>
+      <c r="M52" s="7" t="inlineStr"/>
     </row>
     <row r="53">
-      <c r="A53" s="4" t="inlineStr">
+      <c r="A53" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9353,10 +9376,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M53" s="6" t="inlineStr"/>
+      <c r="M53" s="7" t="inlineStr"/>
     </row>
     <row r="54">
-      <c r="A54" s="4" t="inlineStr">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9402,14 +9425,14 @@
         </is>
       </c>
       <c r="L54" t="inlineStr"/>
-      <c r="M54" s="6" t="inlineStr">
+      <c r="M54" s="7" t="inlineStr">
         <is>
           <t>(전일) 클라우드 광통신 투자 둔화·서비스업체 재고소화 지연 우려</t>
         </is>
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="4" t="inlineStr">
+      <c r="A55" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9455,10 +9478,10 @@
         </is>
       </c>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" s="6" t="inlineStr"/>
+      <c r="M55" s="7" t="inlineStr"/>
     </row>
     <row r="56">
-      <c r="A56" s="4" t="inlineStr">
+      <c r="A56" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9506,10 +9529,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M56" s="6" t="inlineStr"/>
+      <c r="M56" s="7" t="inlineStr"/>
     </row>
     <row r="57">
-      <c r="A57" s="4" t="inlineStr">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9553,14 +9576,14 @@
         </is>
       </c>
       <c r="L57" t="inlineStr"/>
-      <c r="M57" s="6" t="inlineStr">
+      <c r="M57" s="7" t="inlineStr">
         <is>
           <t>(전일) 양자컴 섹터 리스크오프+공매도 리포트의 국방부 계약 우려</t>
         </is>
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="4" t="inlineStr">
+      <c r="A58" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9606,10 +9629,10 @@
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" s="6" t="inlineStr"/>
+      <c r="M58" s="7" t="inlineStr"/>
     </row>
     <row r="59">
-      <c r="A59" s="4" t="inlineStr">
+      <c r="A59" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9655,10 +9678,10 @@
         </is>
       </c>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" s="6" t="inlineStr"/>
+      <c r="M59" s="7" t="inlineStr"/>
     </row>
     <row r="60">
-      <c r="A60" s="4" t="inlineStr">
+      <c r="A60" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9704,14 +9727,14 @@
         </is>
       </c>
       <c r="L60" t="inlineStr"/>
-      <c r="M60" s="6" t="inlineStr">
+      <c r="M60" s="7" t="inlineStr">
         <is>
           <t>(전일) AI 광학주 랠리 후 차익실현·밸류에이션 부담</t>
         </is>
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="4" t="inlineStr">
+      <c r="A61" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9755,14 +9778,14 @@
         </is>
       </c>
       <c r="L61" t="inlineStr"/>
-      <c r="M61" s="6" t="inlineStr">
+      <c r="M61" s="7" t="inlineStr">
         <is>
           <t>(전일) 메타 자체 클라우드 진출 경쟁 우려 지속, AI 컴퓨트주 약세 연장</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="4" t="inlineStr">
+      <c r="A62" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9808,10 +9831,10 @@
         </is>
       </c>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" s="6" t="inlineStr"/>
+      <c r="M62" s="7" t="inlineStr"/>
     </row>
     <row r="63">
-      <c r="A63" s="4" t="inlineStr">
+      <c r="A63" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -9855,10 +9878,10 @@
         </is>
       </c>
       <c r="L63" t="inlineStr"/>
-      <c r="M63" s="6" t="inlineStr"/>
+      <c r="M63" s="7" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="3" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9908,14 +9931,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M64" s="6" t="inlineStr">
+      <c r="M64" s="7" t="inlineStr">
         <is>
           <t>2Q EPS $10.04(예상 $5.34) 대폭 서프라이즈, 재해손실 감소 +8%</t>
         </is>
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="3" t="inlineStr">
+      <c r="A65" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -9965,14 +9988,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M65" s="6" t="inlineStr">
+      <c r="M65" s="7" t="inlineStr">
         <is>
           <t>General Mills·월마트 재생농업 제휴 발표+BMO 목표가 상향</t>
         </is>
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="3" t="inlineStr">
+      <c r="A66" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10022,14 +10045,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M66" s="6" t="inlineStr">
+      <c r="M66" s="7" t="inlineStr">
         <is>
           <t>정제마진 강세 지속, 애널리스트 목표가 상향 랠리</t>
         </is>
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="3" t="inlineStr">
+      <c r="A67" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10079,14 +10102,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M67" s="6" t="inlineStr">
+      <c r="M67" s="7" t="inlineStr">
         <is>
           <t>정제 업황 호조, Raymond James TP $235 상향·정유 동반 강세</t>
         </is>
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="3" t="inlineStr">
+      <c r="A68" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10136,14 +10159,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M68" s="6" t="inlineStr">
+      <c r="M68" s="7" t="inlineStr">
         <is>
           <t>정유·에너지 섹터 강세 동반(개별 뉴스 미확인)</t>
         </is>
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="3" t="inlineStr">
+      <c r="A69" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10189,10 +10212,10 @@
         </is>
       </c>
       <c r="L69" t="inlineStr"/>
-      <c r="M69" s="6" t="inlineStr"/>
+      <c r="M69" s="7" t="inlineStr"/>
     </row>
     <row r="70">
-      <c r="A70" s="3" t="inlineStr">
+      <c r="A70" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10242,10 +10265,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M70" s="6" t="inlineStr"/>
+      <c r="M70" s="7" t="inlineStr"/>
     </row>
     <row r="71">
-      <c r="A71" s="3" t="inlineStr">
+      <c r="A71" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10291,10 +10314,10 @@
         </is>
       </c>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" s="6" t="inlineStr"/>
+      <c r="M71" s="7" t="inlineStr"/>
     </row>
     <row r="72">
-      <c r="A72" s="3" t="inlineStr">
+      <c r="A72" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10344,10 +10367,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M72" s="6" t="inlineStr"/>
+      <c r="M72" s="7" t="inlineStr"/>
     </row>
     <row r="73">
-      <c r="A73" s="3" t="inlineStr">
+      <c r="A73" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10391,10 +10414,10 @@
         </is>
       </c>
       <c r="L73" t="inlineStr"/>
-      <c r="M73" s="6" t="inlineStr"/>
+      <c r="M73" s="7" t="inlineStr"/>
     </row>
     <row r="74">
-      <c r="A74" s="3" t="inlineStr">
+      <c r="A74" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10442,10 +10465,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M74" s="6" t="inlineStr"/>
+      <c r="M74" s="7" t="inlineStr"/>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
+      <c r="A75" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10495,10 +10518,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M75" s="6" t="inlineStr"/>
+      <c r="M75" s="7" t="inlineStr"/>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
+      <c r="A76" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10546,10 +10569,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M76" s="6" t="inlineStr"/>
+      <c r="M76" s="7" t="inlineStr"/>
     </row>
     <row r="77">
-      <c r="A77" s="3" t="inlineStr">
+      <c r="A77" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10599,10 +10622,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M77" s="6" t="inlineStr"/>
+      <c r="M77" s="7" t="inlineStr"/>
     </row>
     <row r="78">
-      <c r="A78" s="3" t="inlineStr">
+      <c r="A78" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10652,10 +10675,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M78" s="6" t="inlineStr"/>
+      <c r="M78" s="7" t="inlineStr"/>
     </row>
     <row r="79">
-      <c r="A79" s="3" t="inlineStr">
+      <c r="A79" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10705,10 +10728,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M79" s="6" t="inlineStr"/>
+      <c r="M79" s="7" t="inlineStr"/>
     </row>
     <row r="80">
-      <c r="A80" s="3" t="inlineStr">
+      <c r="A80" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10758,10 +10781,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M80" s="6" t="inlineStr"/>
+      <c r="M80" s="7" t="inlineStr"/>
     </row>
     <row r="81">
-      <c r="A81" s="3" t="inlineStr">
+      <c r="A81" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10811,10 +10834,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M81" s="6" t="inlineStr"/>
+      <c r="M81" s="7" t="inlineStr"/>
     </row>
     <row r="82">
-      <c r="A82" s="3" t="inlineStr">
+      <c r="A82" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10864,10 +10887,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M82" s="6" t="inlineStr"/>
+      <c r="M82" s="7" t="inlineStr"/>
     </row>
     <row r="83">
-      <c r="A83" s="3" t="inlineStr">
+      <c r="A83" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10917,10 +10940,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M83" s="6" t="inlineStr"/>
+      <c r="M83" s="7" t="inlineStr"/>
     </row>
     <row r="84">
-      <c r="A84" s="3" t="inlineStr">
+      <c r="A84" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -10970,10 +10993,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M84" s="6" t="inlineStr"/>
+      <c r="M84" s="7" t="inlineStr"/>
     </row>
     <row r="85">
-      <c r="A85" s="3" t="inlineStr">
+      <c r="A85" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11023,10 +11046,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M85" s="6" t="inlineStr"/>
+      <c r="M85" s="7" t="inlineStr"/>
     </row>
     <row r="86">
-      <c r="A86" s="3" t="inlineStr">
+      <c r="A86" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11074,10 +11097,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M86" s="6" t="inlineStr"/>
+      <c r="M86" s="7" t="inlineStr"/>
     </row>
     <row r="87">
-      <c r="A87" s="3" t="inlineStr">
+      <c r="A87" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11127,10 +11150,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M87" s="6" t="inlineStr"/>
+      <c r="M87" s="7" t="inlineStr"/>
     </row>
     <row r="88">
-      <c r="A88" s="3" t="inlineStr">
+      <c r="A88" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11180,10 +11203,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M88" s="6" t="inlineStr"/>
+      <c r="M88" s="7" t="inlineStr"/>
     </row>
     <row r="89">
-      <c r="A89" s="3" t="inlineStr">
+      <c r="A89" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11233,10 +11256,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M89" s="6" t="inlineStr"/>
+      <c r="M89" s="7" t="inlineStr"/>
     </row>
     <row r="90">
-      <c r="A90" s="3" t="inlineStr">
+      <c r="A90" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11286,10 +11309,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M90" s="6" t="inlineStr"/>
+      <c r="M90" s="7" t="inlineStr"/>
     </row>
     <row r="91">
-      <c r="A91" s="3" t="inlineStr">
+      <c r="A91" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11339,10 +11362,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M91" s="6" t="inlineStr"/>
+      <c r="M91" s="7" t="inlineStr"/>
     </row>
     <row r="92">
-      <c r="A92" s="3" t="inlineStr">
+      <c r="A92" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11392,10 +11415,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M92" s="6" t="inlineStr"/>
+      <c r="M92" s="7" t="inlineStr"/>
     </row>
     <row r="93">
-      <c r="A93" s="3" t="inlineStr">
+      <c r="A93" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11441,10 +11464,10 @@
         </is>
       </c>
       <c r="L93" t="inlineStr"/>
-      <c r="M93" s="6" t="inlineStr"/>
+      <c r="M93" s="7" t="inlineStr"/>
     </row>
     <row r="94">
-      <c r="A94" s="3" t="inlineStr">
+      <c r="A94" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11494,10 +11517,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M94" s="6" t="inlineStr"/>
+      <c r="M94" s="7" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" s="3" t="inlineStr">
+      <c r="A95" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11547,10 +11570,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M95" s="6" t="inlineStr"/>
+      <c r="M95" s="7" t="inlineStr"/>
     </row>
     <row r="96">
-      <c r="A96" s="3" t="inlineStr">
+      <c r="A96" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11600,10 +11623,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M96" s="6" t="inlineStr"/>
+      <c r="M96" s="7" t="inlineStr"/>
     </row>
     <row r="97">
-      <c r="A97" s="3" t="inlineStr">
+      <c r="A97" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11653,10 +11676,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M97" s="6" t="inlineStr"/>
+      <c r="M97" s="7" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+      <c r="A98" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11706,10 +11729,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M98" s="6" t="inlineStr"/>
+      <c r="M98" s="7" t="inlineStr"/>
     </row>
     <row r="99">
-      <c r="A99" s="3" t="inlineStr">
+      <c r="A99" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11759,10 +11782,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M99" s="6" t="inlineStr"/>
+      <c r="M99" s="7" t="inlineStr"/>
     </row>
     <row r="100">
-      <c r="A100" s="3" t="inlineStr">
+      <c r="A100" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11812,10 +11835,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M100" s="6" t="inlineStr"/>
+      <c r="M100" s="7" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" s="3" t="inlineStr">
+      <c r="A101" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11865,10 +11888,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M101" s="6" t="inlineStr"/>
+      <c r="M101" s="7" t="inlineStr"/>
     </row>
     <row r="102">
-      <c r="A102" s="3" t="inlineStr">
+      <c r="A102" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11914,10 +11937,10 @@
         </is>
       </c>
       <c r="L102" t="inlineStr"/>
-      <c r="M102" s="6" t="inlineStr"/>
+      <c r="M102" s="7" t="inlineStr"/>
     </row>
     <row r="103">
-      <c r="A103" s="3" t="inlineStr">
+      <c r="A103" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -11967,10 +11990,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M103" s="6" t="inlineStr"/>
+      <c r="M103" s="7" t="inlineStr"/>
     </row>
     <row r="104">
-      <c r="A104" s="3" t="inlineStr">
+      <c r="A104" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12016,10 +12039,10 @@
         </is>
       </c>
       <c r="L104" t="inlineStr"/>
-      <c r="M104" s="6" t="inlineStr"/>
+      <c r="M104" s="7" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" s="3" t="inlineStr">
+      <c r="A105" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12069,10 +12092,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M105" s="6" t="inlineStr"/>
+      <c r="M105" s="7" t="inlineStr"/>
     </row>
     <row r="106">
-      <c r="A106" s="3" t="inlineStr">
+      <c r="A106" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12118,10 +12141,10 @@
         </is>
       </c>
       <c r="L106" t="inlineStr"/>
-      <c r="M106" s="6" t="inlineStr"/>
+      <c r="M106" s="7" t="inlineStr"/>
     </row>
     <row r="107">
-      <c r="A107" s="3" t="inlineStr">
+      <c r="A107" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12167,10 +12190,10 @@
         </is>
       </c>
       <c r="L107" t="inlineStr"/>
-      <c r="M107" s="6" t="inlineStr"/>
+      <c r="M107" s="7" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" s="3" t="inlineStr">
+      <c r="A108" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12218,10 +12241,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M108" s="6" t="inlineStr"/>
+      <c r="M108" s="7" t="inlineStr"/>
     </row>
     <row r="109">
-      <c r="A109" s="3" t="inlineStr">
+      <c r="A109" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12269,10 +12292,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M109" s="6" t="inlineStr"/>
+      <c r="M109" s="7" t="inlineStr"/>
     </row>
     <row r="110">
-      <c r="A110" s="3" t="inlineStr">
+      <c r="A110" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12318,10 +12341,10 @@
         </is>
       </c>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" s="6" t="inlineStr"/>
+      <c r="M110" s="7" t="inlineStr"/>
     </row>
     <row r="111">
-      <c r="A111" s="3" t="inlineStr">
+      <c r="A111" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12371,10 +12394,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M111" s="6" t="inlineStr"/>
+      <c r="M111" s="7" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" s="3" t="inlineStr">
+      <c r="A112" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12424,10 +12447,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M112" s="6" t="inlineStr"/>
+      <c r="M112" s="7" t="inlineStr"/>
     </row>
     <row r="113">
-      <c r="A113" s="3" t="inlineStr">
+      <c r="A113" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12473,10 +12496,10 @@
         </is>
       </c>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" s="6" t="inlineStr"/>
+      <c r="M113" s="7" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" s="3" t="inlineStr">
+      <c r="A114" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12522,10 +12545,10 @@
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
-      <c r="M114" s="6" t="inlineStr"/>
+      <c r="M114" s="7" t="inlineStr"/>
     </row>
     <row r="115">
-      <c r="A115" s="3" t="inlineStr">
+      <c r="A115" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12571,10 +12594,10 @@
         </is>
       </c>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" s="6" t="inlineStr"/>
+      <c r="M115" s="7" t="inlineStr"/>
     </row>
     <row r="116">
-      <c r="A116" s="3" t="inlineStr">
+      <c r="A116" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12620,10 +12643,10 @@
         </is>
       </c>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" s="6" t="inlineStr"/>
+      <c r="M116" s="7" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" s="3" t="inlineStr">
+      <c r="A117" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12673,10 +12696,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M117" s="6" t="inlineStr"/>
+      <c r="M117" s="7" t="inlineStr"/>
     </row>
     <row r="118">
-      <c r="A118" s="3" t="inlineStr">
+      <c r="A118" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12720,10 +12743,10 @@
         </is>
       </c>
       <c r="L118" t="inlineStr"/>
-      <c r="M118" s="6" t="inlineStr"/>
+      <c r="M118" s="7" t="inlineStr"/>
     </row>
     <row r="119">
-      <c r="A119" s="3" t="inlineStr">
+      <c r="A119" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12769,10 +12792,10 @@
         </is>
       </c>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" s="6" t="inlineStr"/>
+      <c r="M119" s="7" t="inlineStr"/>
     </row>
     <row r="120">
-      <c r="A120" s="3" t="inlineStr">
+      <c r="A120" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12822,10 +12845,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M120" s="6" t="inlineStr"/>
+      <c r="M120" s="7" t="inlineStr"/>
     </row>
     <row r="121">
-      <c r="A121" s="3" t="inlineStr">
+      <c r="A121" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12875,10 +12898,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M121" s="6" t="inlineStr"/>
+      <c r="M121" s="7" t="inlineStr"/>
     </row>
     <row r="122">
-      <c r="A122" s="3" t="inlineStr">
+      <c r="A122" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12928,10 +12951,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M122" s="6" t="inlineStr"/>
+      <c r="M122" s="7" t="inlineStr"/>
     </row>
     <row r="123">
-      <c r="A123" s="3" t="inlineStr">
+      <c r="A123" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -12977,10 +13000,10 @@
         </is>
       </c>
       <c r="L123" t="inlineStr"/>
-      <c r="M123" s="6" t="inlineStr"/>
+      <c r="M123" s="7" t="inlineStr"/>
     </row>
     <row r="124">
-      <c r="A124" s="3" t="inlineStr">
+      <c r="A124" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13030,10 +13053,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M124" s="6" t="inlineStr"/>
+      <c r="M124" s="7" t="inlineStr"/>
     </row>
     <row r="125">
-      <c r="A125" s="3" t="inlineStr">
+      <c r="A125" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13079,10 +13102,10 @@
         </is>
       </c>
       <c r="L125" t="inlineStr"/>
-      <c r="M125" s="6" t="inlineStr"/>
+      <c r="M125" s="7" t="inlineStr"/>
     </row>
     <row r="126">
-      <c r="A126" s="3" t="inlineStr">
+      <c r="A126" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13128,10 +13151,10 @@
         </is>
       </c>
       <c r="L126" t="inlineStr"/>
-      <c r="M126" s="6" t="inlineStr"/>
+      <c r="M126" s="7" t="inlineStr"/>
     </row>
     <row r="127">
-      <c r="A127" s="3" t="inlineStr">
+      <c r="A127" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13177,10 +13200,10 @@
         </is>
       </c>
       <c r="L127" t="inlineStr"/>
-      <c r="M127" s="6" t="inlineStr"/>
+      <c r="M127" s="7" t="inlineStr"/>
     </row>
     <row r="128">
-      <c r="A128" s="3" t="inlineStr">
+      <c r="A128" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13226,10 +13249,10 @@
         </is>
       </c>
       <c r="L128" t="inlineStr"/>
-      <c r="M128" s="6" t="inlineStr"/>
+      <c r="M128" s="7" t="inlineStr"/>
     </row>
     <row r="129">
-      <c r="A129" s="3" t="inlineStr">
+      <c r="A129" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13279,10 +13302,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M129" s="6" t="inlineStr"/>
+      <c r="M129" s="7" t="inlineStr"/>
     </row>
     <row r="130">
-      <c r="A130" s="3" t="inlineStr">
+      <c r="A130" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13332,10 +13355,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M130" s="6" t="inlineStr"/>
+      <c r="M130" s="7" t="inlineStr"/>
     </row>
     <row r="131">
-      <c r="A131" s="3" t="inlineStr">
+      <c r="A131" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13385,10 +13408,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M131" s="6" t="inlineStr"/>
+      <c r="M131" s="7" t="inlineStr"/>
     </row>
     <row r="132">
-      <c r="A132" s="3" t="inlineStr">
+      <c r="A132" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13434,10 +13457,10 @@
         </is>
       </c>
       <c r="L132" t="inlineStr"/>
-      <c r="M132" s="6" t="inlineStr"/>
+      <c r="M132" s="7" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" s="3" t="inlineStr">
+      <c r="A133" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13483,10 +13506,10 @@
         </is>
       </c>
       <c r="L133" t="inlineStr"/>
-      <c r="M133" s="6" t="inlineStr"/>
+      <c r="M133" s="7" t="inlineStr"/>
     </row>
     <row r="134">
-      <c r="A134" s="3" t="inlineStr">
+      <c r="A134" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13532,10 +13555,10 @@
         </is>
       </c>
       <c r="L134" t="inlineStr"/>
-      <c r="M134" s="6" t="inlineStr"/>
+      <c r="M134" s="7" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" s="3" t="inlineStr">
+      <c r="A135" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13581,10 +13604,10 @@
         </is>
       </c>
       <c r="L135" t="inlineStr"/>
-      <c r="M135" s="6" t="inlineStr"/>
+      <c r="M135" s="7" t="inlineStr"/>
     </row>
     <row r="136">
-      <c r="A136" s="3" t="inlineStr">
+      <c r="A136" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13630,10 +13653,10 @@
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
-      <c r="M136" s="6" t="inlineStr"/>
+      <c r="M136" s="7" t="inlineStr"/>
     </row>
     <row r="137">
-      <c r="A137" s="3" t="inlineStr">
+      <c r="A137" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13679,10 +13702,10 @@
         </is>
       </c>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" s="6" t="inlineStr"/>
+      <c r="M137" s="7" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" s="3" t="inlineStr">
+      <c r="A138" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13728,10 +13751,10 @@
         </is>
       </c>
       <c r="L138" t="inlineStr"/>
-      <c r="M138" s="6" t="inlineStr"/>
+      <c r="M138" s="7" t="inlineStr"/>
     </row>
     <row r="139">
-      <c r="A139" s="3" t="inlineStr">
+      <c r="A139" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13777,10 +13800,10 @@
         </is>
       </c>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" s="6" t="inlineStr"/>
+      <c r="M139" s="7" t="inlineStr"/>
     </row>
     <row r="140">
-      <c r="A140" s="3" t="inlineStr">
+      <c r="A140" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13826,10 +13849,10 @@
         </is>
       </c>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" s="6" t="inlineStr"/>
+      <c r="M140" s="7" t="inlineStr"/>
     </row>
     <row r="141">
-      <c r="A141" s="3" t="inlineStr">
+      <c r="A141" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13875,10 +13898,10 @@
         </is>
       </c>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" s="6" t="inlineStr"/>
+      <c r="M141" s="7" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" s="3" t="inlineStr">
+      <c r="A142" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13928,10 +13951,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M142" s="6" t="inlineStr"/>
+      <c r="M142" s="7" t="inlineStr"/>
     </row>
     <row r="143">
-      <c r="A143" s="3" t="inlineStr">
+      <c r="A143" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -13979,10 +14002,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M143" s="6" t="inlineStr"/>
+      <c r="M143" s="7" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" s="3" t="inlineStr">
+      <c r="A144" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14032,10 +14055,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M144" s="6" t="inlineStr"/>
+      <c r="M144" s="7" t="inlineStr"/>
     </row>
     <row r="145">
-      <c r="A145" s="3" t="inlineStr">
+      <c r="A145" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14081,10 +14104,10 @@
         </is>
       </c>
       <c r="L145" t="inlineStr"/>
-      <c r="M145" s="6" t="inlineStr"/>
+      <c r="M145" s="7" t="inlineStr"/>
     </row>
     <row r="146">
-      <c r="A146" s="3" t="inlineStr">
+      <c r="A146" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14130,10 +14153,10 @@
         </is>
       </c>
       <c r="L146" t="inlineStr"/>
-      <c r="M146" s="6" t="inlineStr"/>
+      <c r="M146" s="7" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" s="3" t="inlineStr">
+      <c r="A147" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14183,10 +14206,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M147" s="6" t="inlineStr"/>
+      <c r="M147" s="7" t="inlineStr"/>
     </row>
     <row r="148">
-      <c r="A148" s="3" t="inlineStr">
+      <c r="A148" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14232,10 +14255,10 @@
         </is>
       </c>
       <c r="L148" t="inlineStr"/>
-      <c r="M148" s="6" t="inlineStr"/>
+      <c r="M148" s="7" t="inlineStr"/>
     </row>
     <row r="149">
-      <c r="A149" s="3" t="inlineStr">
+      <c r="A149" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14281,10 +14304,10 @@
         </is>
       </c>
       <c r="L149" t="inlineStr"/>
-      <c r="M149" s="6" t="inlineStr"/>
+      <c r="M149" s="7" t="inlineStr"/>
     </row>
     <row r="150">
-      <c r="A150" s="3" t="inlineStr">
+      <c r="A150" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14330,10 +14353,10 @@
         </is>
       </c>
       <c r="L150" t="inlineStr"/>
-      <c r="M150" s="6" t="inlineStr"/>
+      <c r="M150" s="7" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" s="3" t="inlineStr">
+      <c r="A151" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14383,10 +14406,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M151" s="6" t="inlineStr"/>
+      <c r="M151" s="7" t="inlineStr"/>
     </row>
     <row r="152">
-      <c r="A152" s="3" t="inlineStr">
+      <c r="A152" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14436,10 +14459,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M152" s="6" t="inlineStr"/>
+      <c r="M152" s="7" t="inlineStr"/>
     </row>
     <row r="153">
-      <c r="A153" s="3" t="inlineStr">
+      <c r="A153" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14483,10 +14506,10 @@
         </is>
       </c>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" s="6" t="inlineStr"/>
+      <c r="M153" s="7" t="inlineStr"/>
     </row>
     <row r="154">
-      <c r="A154" s="3" t="inlineStr">
+      <c r="A154" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14532,10 +14555,10 @@
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" s="6" t="inlineStr"/>
+      <c r="M154" s="7" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" s="3" t="inlineStr">
+      <c r="A155" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14581,10 +14604,10 @@
         </is>
       </c>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" s="6" t="inlineStr"/>
+      <c r="M155" s="7" t="inlineStr"/>
     </row>
     <row r="156">
-      <c r="A156" s="3" t="inlineStr">
+      <c r="A156" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14630,10 +14653,10 @@
         </is>
       </c>
       <c r="L156" t="inlineStr"/>
-      <c r="M156" s="6" t="inlineStr"/>
+      <c r="M156" s="7" t="inlineStr"/>
     </row>
     <row r="157">
-      <c r="A157" s="3" t="inlineStr">
+      <c r="A157" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14683,10 +14706,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M157" s="6" t="inlineStr"/>
+      <c r="M157" s="7" t="inlineStr"/>
     </row>
     <row r="158">
-      <c r="A158" s="3" t="inlineStr">
+      <c r="A158" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14732,10 +14755,10 @@
         </is>
       </c>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" s="6" t="inlineStr"/>
+      <c r="M158" s="7" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" s="3" t="inlineStr">
+      <c r="A159" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14783,10 +14806,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M159" s="6" t="inlineStr"/>
+      <c r="M159" s="7" t="inlineStr"/>
     </row>
     <row r="160">
-      <c r="A160" s="3" t="inlineStr">
+      <c r="A160" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14832,10 +14855,10 @@
         </is>
       </c>
       <c r="L160" t="inlineStr"/>
-      <c r="M160" s="6" t="inlineStr"/>
+      <c r="M160" s="7" t="inlineStr"/>
     </row>
     <row r="161">
-      <c r="A161" s="3" t="inlineStr">
+      <c r="A161" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14885,10 +14908,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M161" s="6" t="inlineStr"/>
+      <c r="M161" s="7" t="inlineStr"/>
     </row>
     <row r="162">
-      <c r="A162" s="3" t="inlineStr">
+      <c r="A162" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14932,10 +14955,10 @@
         </is>
       </c>
       <c r="L162" t="inlineStr"/>
-      <c r="M162" s="6" t="inlineStr"/>
+      <c r="M162" s="7" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" s="3" t="inlineStr">
+      <c r="A163" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -14985,10 +15008,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M163" s="6" t="inlineStr"/>
+      <c r="M163" s="7" t="inlineStr"/>
     </row>
     <row r="164">
-      <c r="A164" s="3" t="inlineStr">
+      <c r="A164" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15038,10 +15061,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M164" s="6" t="inlineStr"/>
+      <c r="M164" s="7" t="inlineStr"/>
     </row>
     <row r="165">
-      <c r="A165" s="3" t="inlineStr">
+      <c r="A165" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15091,10 +15114,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M165" s="6" t="inlineStr"/>
+      <c r="M165" s="7" t="inlineStr"/>
     </row>
     <row r="166">
-      <c r="A166" s="3" t="inlineStr">
+      <c r="A166" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15144,10 +15167,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M166" s="6" t="inlineStr"/>
+      <c r="M166" s="7" t="inlineStr"/>
     </row>
     <row r="167">
-      <c r="A167" s="3" t="inlineStr">
+      <c r="A167" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15197,10 +15220,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M167" s="6" t="inlineStr"/>
+      <c r="M167" s="7" t="inlineStr"/>
     </row>
     <row r="168">
-      <c r="A168" s="3" t="inlineStr">
+      <c r="A168" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15250,10 +15273,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M168" s="6" t="inlineStr"/>
+      <c r="M168" s="7" t="inlineStr"/>
     </row>
     <row r="169">
-      <c r="A169" s="3" t="inlineStr">
+      <c r="A169" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15303,10 +15326,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M169" s="6" t="inlineStr"/>
+      <c r="M169" s="7" t="inlineStr"/>
     </row>
     <row r="170">
-      <c r="A170" s="3" t="inlineStr">
+      <c r="A170" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15356,10 +15379,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M170" s="6" t="inlineStr"/>
+      <c r="M170" s="7" t="inlineStr"/>
     </row>
     <row r="171">
-      <c r="A171" s="3" t="inlineStr">
+      <c r="A171" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15405,10 +15428,10 @@
         </is>
       </c>
       <c r="L171" t="inlineStr"/>
-      <c r="M171" s="6" t="inlineStr"/>
+      <c r="M171" s="7" t="inlineStr"/>
     </row>
     <row r="172">
-      <c r="A172" s="3" t="inlineStr">
+      <c r="A172" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15454,10 +15477,10 @@
         </is>
       </c>
       <c r="L172" t="inlineStr"/>
-      <c r="M172" s="6" t="inlineStr"/>
+      <c r="M172" s="7" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" s="3" t="inlineStr">
+      <c r="A173" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15507,10 +15530,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M173" s="6" t="inlineStr"/>
+      <c r="M173" s="7" t="inlineStr"/>
     </row>
     <row r="174">
-      <c r="A174" s="3" t="inlineStr">
+      <c r="A174" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15560,10 +15583,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M174" s="6" t="inlineStr"/>
+      <c r="M174" s="7" t="inlineStr"/>
     </row>
     <row r="175">
-      <c r="A175" s="3" t="inlineStr">
+      <c r="A175" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15613,10 +15636,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M175" s="6" t="inlineStr"/>
+      <c r="M175" s="7" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" s="3" t="inlineStr">
+      <c r="A176" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15666,14 +15689,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M176" s="6" t="inlineStr">
+      <c r="M176" s="7" t="inlineStr">
         <is>
           <t>(전일) 중국 당국, 알리바바 Qwen 연동 Apple Intelligence 정식 승인 — 중국 불확실성 해소</t>
         </is>
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="3" t="inlineStr">
+      <c r="A177" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15719,14 +15742,14 @@
         </is>
       </c>
       <c r="L177" t="inlineStr"/>
-      <c r="M177" s="6" t="inlineStr">
+      <c r="M177" s="7" t="inlineStr">
         <is>
           <t>(전일) Piper Sandler 목표가 $31→$36 상향(Overweight 유지)</t>
         </is>
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="3" t="inlineStr">
+      <c r="A178" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15776,10 +15799,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M178" s="6" t="inlineStr"/>
+      <c r="M178" s="7" t="inlineStr"/>
     </row>
     <row r="179">
-      <c r="A179" s="3" t="inlineStr">
+      <c r="A179" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15825,10 +15848,10 @@
         </is>
       </c>
       <c r="L179" t="inlineStr"/>
-      <c r="M179" s="6" t="inlineStr"/>
+      <c r="M179" s="7" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" s="3" t="inlineStr">
+      <c r="A180" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15878,10 +15901,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M180" s="6" t="inlineStr"/>
+      <c r="M180" s="7" t="inlineStr"/>
     </row>
     <row r="181">
-      <c r="A181" s="3" t="inlineStr">
+      <c r="A181" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15931,10 +15954,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M181" s="6" t="inlineStr"/>
+      <c r="M181" s="7" t="inlineStr"/>
     </row>
     <row r="182">
-      <c r="A182" s="3" t="inlineStr">
+      <c r="A182" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -15980,10 +16003,10 @@
         </is>
       </c>
       <c r="L182" t="inlineStr"/>
-      <c r="M182" s="6" t="inlineStr"/>
+      <c r="M182" s="7" t="inlineStr"/>
     </row>
     <row r="183">
-      <c r="A183" s="3" t="inlineStr">
+      <c r="A183" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16027,10 +16050,10 @@
         </is>
       </c>
       <c r="L183" t="inlineStr"/>
-      <c r="M183" s="6" t="inlineStr"/>
+      <c r="M183" s="7" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" s="3" t="inlineStr">
+      <c r="A184" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16076,10 +16099,10 @@
         </is>
       </c>
       <c r="L184" t="inlineStr"/>
-      <c r="M184" s="6" t="inlineStr"/>
+      <c r="M184" s="7" t="inlineStr"/>
     </row>
     <row r="185">
-      <c r="A185" s="3" t="inlineStr">
+      <c r="A185" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16125,10 +16148,10 @@
         </is>
       </c>
       <c r="L185" t="inlineStr"/>
-      <c r="M185" s="6" t="inlineStr"/>
+      <c r="M185" s="7" t="inlineStr"/>
     </row>
     <row r="186">
-      <c r="A186" s="3" t="inlineStr">
+      <c r="A186" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16174,10 +16197,10 @@
         </is>
       </c>
       <c r="L186" t="inlineStr"/>
-      <c r="M186" s="6" t="inlineStr"/>
+      <c r="M186" s="7" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" s="3" t="inlineStr">
+      <c r="A187" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16223,10 +16246,10 @@
         </is>
       </c>
       <c r="L187" t="inlineStr"/>
-      <c r="M187" s="6" t="inlineStr"/>
+      <c r="M187" s="7" t="inlineStr"/>
     </row>
     <row r="188">
-      <c r="A188" s="3" t="inlineStr">
+      <c r="A188" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16276,10 +16299,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M188" s="6" t="inlineStr"/>
+      <c r="M188" s="7" t="inlineStr"/>
     </row>
     <row r="189">
-      <c r="A189" s="3" t="inlineStr">
+      <c r="A189" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16323,10 +16346,10 @@
         </is>
       </c>
       <c r="L189" t="inlineStr"/>
-      <c r="M189" s="6" t="inlineStr"/>
+      <c r="M189" s="7" t="inlineStr"/>
     </row>
     <row r="190">
-      <c r="A190" s="3" t="inlineStr">
+      <c r="A190" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16376,10 +16399,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M190" s="6" t="inlineStr"/>
+      <c r="M190" s="7" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" s="3" t="inlineStr">
+      <c r="A191" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16425,10 +16448,10 @@
         </is>
       </c>
       <c r="L191" t="inlineStr"/>
-      <c r="M191" s="6" t="inlineStr"/>
+      <c r="M191" s="7" t="inlineStr"/>
     </row>
     <row r="192">
-      <c r="A192" s="3" t="inlineStr">
+      <c r="A192" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16474,10 +16497,10 @@
         </is>
       </c>
       <c r="L192" t="inlineStr"/>
-      <c r="M192" s="6" t="inlineStr"/>
+      <c r="M192" s="7" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" s="3" t="inlineStr">
+      <c r="A193" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16523,10 +16546,10 @@
         </is>
       </c>
       <c r="L193" t="inlineStr"/>
-      <c r="M193" s="6" t="inlineStr"/>
+      <c r="M193" s="7" t="inlineStr"/>
     </row>
     <row r="194">
-      <c r="A194" s="3" t="inlineStr">
+      <c r="A194" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16576,10 +16599,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M194" s="6" t="inlineStr"/>
+      <c r="M194" s="7" t="inlineStr"/>
     </row>
     <row r="195">
-      <c r="A195" s="3" t="inlineStr">
+      <c r="A195" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16629,10 +16652,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M195" s="6" t="inlineStr"/>
+      <c r="M195" s="7" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" s="3" t="inlineStr">
+      <c r="A196" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16678,10 +16701,10 @@
         </is>
       </c>
       <c r="L196" t="inlineStr"/>
-      <c r="M196" s="6" t="inlineStr"/>
+      <c r="M196" s="7" t="inlineStr"/>
     </row>
     <row r="197">
-      <c r="A197" s="3" t="inlineStr">
+      <c r="A197" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16731,10 +16754,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M197" s="6" t="inlineStr"/>
+      <c r="M197" s="7" t="inlineStr"/>
     </row>
     <row r="198">
-      <c r="A198" s="3" t="inlineStr">
+      <c r="A198" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16780,10 +16803,10 @@
         </is>
       </c>
       <c r="L198" t="inlineStr"/>
-      <c r="M198" s="6" t="inlineStr"/>
+      <c r="M198" s="7" t="inlineStr"/>
     </row>
     <row r="199">
-      <c r="A199" s="3" t="inlineStr">
+      <c r="A199" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16833,10 +16856,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M199" s="6" t="inlineStr"/>
+      <c r="M199" s="7" t="inlineStr"/>
     </row>
     <row r="200">
-      <c r="A200" s="3" t="inlineStr">
+      <c r="A200" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -16882,7 +16905,7 @@
         </is>
       </c>
       <c r="L200" t="inlineStr"/>
-      <c r="M200" s="6" t="inlineStr"/>
+      <c r="M200" s="7" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:M200"/>
@@ -16982,7 +17005,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17028,14 +17051,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>비철 섹터 급락 — 구리·아연 가격 하락 우려로 -7%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17081,14 +17104,14 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>금 가격 하락·FY27 감익 전망 경계, 비철 매도 동반</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17134,14 +17157,14 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>구리·비철 급락 연동+AI전선 수요 기대 되돌림</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17187,14 +17210,14 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>AI전선 테마 과열 경계 속 외국인 매도 가속 -6%</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17240,14 +17263,14 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>반도체 관련 조정 동반 급락(수주 사상최고나 선반영 해소)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17293,10 +17316,10 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17342,10 +17365,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="inlineStr">
+      <c r="A9" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17391,14 +17414,14 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr">
+      <c r="M9" s="7" t="inlineStr">
         <is>
           <t>폴란드 편의점 1위 자브카 대규모 출자 검토 보도(7/16), 유럽 확장 기대</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="inlineStr">
+      <c r="A10" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17444,14 +17467,14 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr">
+      <c r="M10" s="7" t="inlineStr">
         <is>
           <t>FY3/26 사상 최고익 경신 전망, 토이하비 호조 상승추세 지속</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="inlineStr">
+      <c r="A11" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17501,14 +17524,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M11" s="6" t="inlineStr">
+      <c r="M11" s="7" t="inlineStr">
         <is>
           <t>기계·비철 급락장서 고배당 디펜시브로 상대 자금 유입</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="inlineStr">
+      <c r="A12" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17554,14 +17577,14 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr">
+      <c r="M12" s="7" t="inlineStr">
         <is>
           <t>디펜시브 소비재로 급락장서 상대적 견조, 60일 신고가</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="inlineStr">
+      <c r="A13" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -17607,7 +17630,7 @@
         </is>
       </c>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" s="6" t="inlineStr">
+      <c r="M13" s="7" t="inlineStr">
         <is>
           <t>미국 주택사업 확대 기대·고배당(당일 보합, 장중 신고가 터치)</t>
         </is>
@@ -17711,7 +17734,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17753,14 +17776,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>10% 할인 신주배정 발표 희석 우려+반도체 급락 -15%</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17806,14 +17829,14 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>노무라 경쟁심화 경고·광섬유 가격 둔화 우려, 고점 차익실현</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17861,14 +17884,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>IPO 공모가 하회 지속, 항셍테크 -4.4% 급락 속 매도 압력</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17916,14 +17939,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>PCB·전자부품 섹터 급락(A주 동종 다수 하한가) 동반 하락</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -17971,14 +17994,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>7/10 상장 직후 고점 대비 신규상장주 조정+섹터 약세</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18024,10 +18047,10 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18071,10 +18094,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18120,10 +18143,10 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18169,10 +18192,10 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18218,10 +18241,10 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18271,10 +18294,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M12" s="6" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18324,10 +18347,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18377,10 +18400,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M14" s="6" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18426,10 +18449,10 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18475,14 +18498,14 @@
         </is>
       </c>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" s="6" t="inlineStr">
+      <c r="M16" s="7" t="inlineStr">
         <is>
           <t>(전일) 탄산리튬 가격 3월래 최저(칠레 수출증가·CATL 광산 재가동 공급과잉 우려)</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18532,14 +18555,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M17" s="6" t="inlineStr">
+      <c r="M17" s="7" t="inlineStr">
         <is>
           <t>(전일) 골드만 하반기 리튬 20%+ 공급과잉 전망 등 공급증가 우려</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="3" t="inlineStr">
+      <c r="A18" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18589,10 +18612,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M18" s="6" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -18642,7 +18665,7 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M19" s="6" t="inlineStr">
+      <c r="M19" s="7" t="inlineStr">
         <is>
           <t>(전일) 항셍지수 랠리 속 사상최고가, 매매단위 축소·30억달러 채권상환 호재</t>
         </is>
@@ -18746,7 +18769,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="4" t="inlineStr">
+      <c r="A2" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18792,14 +18815,14 @@
         </is>
       </c>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" s="6" t="inlineStr">
+      <c r="M2" s="7" t="inlineStr">
         <is>
           <t>반기 순익 +3200% 예고에도 대주주 감자 계획·고밸류 차익실현</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="4" t="inlineStr">
+      <c r="A3" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18845,14 +18868,14 @@
         </is>
       </c>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" s="6" t="inlineStr">
+      <c r="M3" s="7" t="inlineStr">
         <is>
           <t>반기 가이던스(+25~45%)가 기관 예상(68%) 하회, PE 106배 해소</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="4" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18896,14 +18919,14 @@
         </is>
       </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" s="6" t="inlineStr">
+      <c r="M4" s="7" t="inlineStr">
         <is>
           <t>로봇 섹터 차익실현+1Q 순익 -48%, 시장 전반 약세</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="4" t="inlineStr">
+      <c r="A5" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -18949,14 +18972,14 @@
         </is>
       </c>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" s="6" t="inlineStr">
+      <c r="M5" s="7" t="inlineStr">
         <is>
           <t>위성통신·AI 테마 과열 후 PE 87배 고평가 해소 연속 하락</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19002,14 +19025,14 @@
         </is>
       </c>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" s="6" t="inlineStr">
+      <c r="M6" s="7" t="inlineStr">
         <is>
           <t>1Q 순익 -30.7%·환차손 확대, 주력자금 순매도</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="4" t="inlineStr">
+      <c r="A7" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19055,10 +19078,10 @@
         </is>
       </c>
       <c r="L7" t="inlineStr"/>
-      <c r="M7" s="6" t="inlineStr"/>
+      <c r="M7" s="7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="4" t="inlineStr">
+      <c r="A8" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19104,10 +19127,10 @@
         </is>
       </c>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" s="6" t="inlineStr"/>
+      <c r="M8" s="7" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="4" t="inlineStr">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19151,10 +19174,10 @@
         </is>
       </c>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" s="6" t="inlineStr"/>
+      <c r="M9" s="7" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="inlineStr">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19200,10 +19223,10 @@
         </is>
       </c>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" s="6" t="inlineStr"/>
+      <c r="M10" s="7" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="inlineStr">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19249,10 +19272,10 @@
         </is>
       </c>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" s="6" t="inlineStr"/>
+      <c r="M11" s="7" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="4" t="inlineStr">
+      <c r="A12" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19296,10 +19319,10 @@
         </is>
       </c>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" s="6" t="inlineStr"/>
+      <c r="M12" s="7" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="4" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19347,10 +19370,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M13" s="6" t="inlineStr"/>
+      <c r="M13" s="7" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+      <c r="A14" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19396,10 +19419,10 @@
         </is>
       </c>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" s="6" t="inlineStr"/>
+      <c r="M14" s="7" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="4" t="inlineStr">
+      <c r="A15" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19445,10 +19468,10 @@
         </is>
       </c>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" s="6" t="inlineStr"/>
+      <c r="M15" s="7" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="4" t="inlineStr">
+      <c r="A16" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19498,10 +19521,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M16" s="6" t="inlineStr"/>
+      <c r="M16" s="7" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="4" t="inlineStr">
+      <c r="A17" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19547,10 +19570,10 @@
         </is>
       </c>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" s="6" t="inlineStr"/>
+      <c r="M17" s="7" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="4" t="inlineStr">
+      <c r="A18" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19596,10 +19619,10 @@
         </is>
       </c>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" s="6" t="inlineStr"/>
+      <c r="M18" s="7" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="4" t="inlineStr">
+      <c r="A19" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19645,10 +19668,10 @@
         </is>
       </c>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" s="6" t="inlineStr"/>
+      <c r="M19" s="7" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="4" t="inlineStr">
+      <c r="A20" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19694,10 +19717,10 @@
         </is>
       </c>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" s="6" t="inlineStr"/>
+      <c r="M20" s="7" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
+      <c r="A21" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19743,10 +19766,10 @@
         </is>
       </c>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" s="6" t="inlineStr"/>
+      <c r="M21" s="7" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="4" t="inlineStr">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19788,10 +19811,10 @@
         </is>
       </c>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" s="6" t="inlineStr"/>
+      <c r="M22" s="7" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="4" t="inlineStr">
+      <c r="A23" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19837,10 +19860,10 @@
         </is>
       </c>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" s="6" t="inlineStr"/>
+      <c r="M23" s="7" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="4" t="inlineStr">
+      <c r="A24" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19888,10 +19911,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M24" s="6" t="inlineStr"/>
+      <c r="M24" s="7" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="4" t="inlineStr">
+      <c r="A25" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19937,10 +19960,10 @@
         </is>
       </c>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" s="6" t="inlineStr"/>
+      <c r="M25" s="7" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="4" t="inlineStr">
+      <c r="A26" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -19990,10 +20013,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M26" s="6" t="inlineStr"/>
+      <c r="M26" s="7" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="4" t="inlineStr">
+      <c r="A27" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20043,10 +20066,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M27" s="6" t="inlineStr"/>
+      <c r="M27" s="7" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="4" t="inlineStr">
+      <c r="A28" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20092,10 +20115,10 @@
         </is>
       </c>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" s="6" t="inlineStr"/>
+      <c r="M28" s="7" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="4" t="inlineStr">
+      <c r="A29" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20145,10 +20168,10 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M29" s="6" t="inlineStr"/>
+      <c r="M29" s="7" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="4" t="inlineStr">
+      <c r="A30" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20194,10 +20217,10 @@
         </is>
       </c>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" s="6" t="inlineStr"/>
+      <c r="M30" s="7" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="4" t="inlineStr">
+      <c r="A31" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20243,10 +20266,10 @@
         </is>
       </c>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" s="6" t="inlineStr"/>
+      <c r="M31" s="7" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="4" t="inlineStr">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20294,14 +20317,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M32" s="6" t="inlineStr">
+      <c r="M32" s="7" t="inlineStr">
         <is>
           <t>(전일) 7/13 급락(-13%) 후 차익실현·주력자금 순유출 지속</t>
         </is>
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
+      <c r="A33" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20347,10 +20370,10 @@
         </is>
       </c>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" s="6" t="inlineStr"/>
+      <c r="M33" s="7" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
+      <c r="A34" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20396,14 +20419,14 @@
         </is>
       </c>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" s="6" t="inlineStr">
+      <c r="M34" s="7" t="inlineStr">
         <is>
           <t>(전일) 1Q 순손실 확대(-77% YoY), 상업우주 테마 고점 차익실현</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
+      <c r="A35" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20451,14 +20474,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M35" s="6" t="inlineStr">
+      <c r="M35" s="7" t="inlineStr">
         <is>
           <t>(전일) IPO 직후 급락 지속: 패널 업황·370억위안 부채·해금 부담(7/3~7 이상변동)</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
+      <c r="A36" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20504,10 +20527,10 @@
         </is>
       </c>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" s="6" t="inlineStr"/>
+      <c r="M36" s="7" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
+      <c r="A37" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20553,10 +20576,10 @@
         </is>
       </c>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" s="6" t="inlineStr"/>
+      <c r="M37" s="7" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
+      <c r="A38" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20602,14 +20625,14 @@
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" s="6" t="inlineStr">
+      <c r="M38" s="7" t="inlineStr">
         <is>
           <t>(전일) 1Q26 순이익 -62% 급감·주력자금 순유출, 고평가(PE 300배+) 부담 조정</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
+      <c r="A39" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20655,14 +20678,14 @@
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" s="6" t="inlineStr">
+      <c r="M39" s="7" t="inlineStr">
         <is>
           <t>(전일) 특별한 뉴스 없음(섹터/수급 흐름 추정)</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
+      <c r="A40" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20706,14 +20729,14 @@
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
-      <c r="M40" s="6" t="inlineStr">
+      <c r="M40" s="7" t="inlineStr">
         <is>
           <t>(전일) 특별한 뉴스 없음(신규상장주 수급/해금 부담 추정)</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20759,14 +20782,14 @@
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
-      <c r="M41" s="6" t="inlineStr">
+      <c r="M41" s="7" t="inlineStr">
         <is>
           <t>(전일) 탄산리튬 가격 약세 지속·리튬 섹터 수급 부진</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
+      <c r="A42" s="5" t="inlineStr">
         <is>
           <t>신저가</t>
         </is>
@@ -20814,14 +20837,14 @@
           <t>O</t>
         </is>
       </c>
-      <c r="M42" s="6" t="inlineStr">
+      <c r="M42" s="7" t="inlineStr">
         <is>
           <t>(전일) 상장 1년 해금 도래 수급 부담+순익 역성장·자회사 제재 악재</t>
         </is>
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
+      <c r="A43" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -20867,14 +20890,14 @@
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" s="6" t="inlineStr">
+      <c r="M43" s="7" t="inlineStr">
         <is>
           <t>국무원 중의약 15·5규획 발표로 중약 섹터 급등, 연속 강세</t>
         </is>
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="3" t="inlineStr">
+      <c r="A44" s="4" t="inlineStr">
         <is>
           <t>신고가</t>
         </is>
@@ -20920,7 +20943,7 @@
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" s="6" t="inlineStr">
+      <c r="M44" s="7" t="inlineStr">
         <is>
           <t>야룽장 유역 강수 증가로 수력 발전량 상승 기대</t>
         </is>

--- a/신고신저가_20260720.xlsx
+++ b/신고신저가_20260720.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -611,33 +611,40 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 [B·해석형] AI 하드웨어 밸류 되돌림이 아시아 전역으로 확산된 하루 — 일본 AI전선(스미토모전공 -6.2%)·중국 광모듈(天孚通信 -13%, PE 106배)·PCB(다수 하한가)·메모리까지 같은 체인이 같은 이유(고밸류+기대치 하회)로 무너진 반면, 미국은 TRV 어닝서프라이즈 +8%·정제마진 강세로 신고가 137개 — 조정이 아직 실적 팩터가 받치는 미국으로 전이되지 않은 국면. 일본 은행 -4.7%는 YTD +40% 고점권 차익실현 성격. 예외는 중국 중약 — 15·5규획 발표에 역행 강세.</t>
+          <t>💬 ■ 결론: 금요일(7/17)은 AI 하드웨어 고밸류 되돌림의 전면 확산 — 지수 조정(나스닥 -1.4%, 닛케이 -4.0%) 속 미국만 금융·디펜시브 로테이션으로 방어.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>[C·구조형] [결론] AI 하드웨어 고밸류 되돌림, 아시아부터 — 미국은 실적주가 방어. [강세] 미국 정유(정제마진)·보험(TRV +8%), 일본 디펜시브(의약·운수·식품), 중국 중약(15·5규획). [약세] AI 체인 일제 조정: 일본 전선·기계(철강비철 ETF 1M -16%), 중국 광모듈 天孚 -13%(기관 기대 하회·PE 106배), PCB 하한가 다수, 항셍테크 -4.4%. 일본 은행 -4.7%는 YTD +40% 후 차익실현.</t>
+          <t>■ 좋은 섹터: 美 금융(신고 순증 +55, PER 19배·밸류 부담無)·유틸·헬스케어 / 日 의약·운수·식품(급락장 유일 플러스) / 中 중약(15·5규획 발표).</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>[D·시장별] 미국: 신고 137 — 보험(TRV +8%)·정유(정제마진) 주도, NFLX만 가이던스 실망 -7% / 일본: 기계·비철 급락(철강비철 1M -16%)·AI전선 되돌림, 의약·운수 디펜시브로 피난 / 홍콩: 테크 -4.4%, IPO 신주(루시쉐어 등) 매도 압력 / 중국A: 신저 41개 — 광모듈·PCB·메모리 고밸류 해소, 중약만 15·5규획에 역행 강세.</t>
+          <t>■ 나쁜 섹터: AI 하드웨어 체인 일괄 — 美 전자기술(신저 순증 -26)·비철(-13), 日 기계 -5.9%·철강비철 -4.9%(ETF 1M -16%)·AI전선, 中 광모듈(天孚 -13%, PE 106배)·PCB(하한가 다수)·메모리, 항셍테크 -4.4%. 日 은행 -4.7%는 YTD +40% 후 차익실현(성격 상이).</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>[A·요약형] 금요일(7/17)은 미국-아시아 온도차 뚜렷 — 미국 신고가 137개(정유·보험 강세) vs 아시아는 AI·반도체 고밸류 되돌림(일본 기계·비철 급락, 중국A 신저 41개, 항셍테크 -4.4%). 이벤트: NFLX 가이던스 실망 -7%, 세븐&amp;아이 자브카 출자 검토 보도 신고가, 중약 15·5규획 강세.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+          <t>■ 이벤트: TRV 어닝서프라이즈 +8%, NFLX 3Q 가이던스 실망 -7%, 세븐&amp;아이 자브카 출자 검토 보도 신고가.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>■ 체크: ①화요일 도쿄(금 -4%를 월 휴장으로 미소화) ②월요일 밤 미국 ③미·이란(유가·금리). ※월요일 장중 중화권 +2~3% 반등했으나 신저가 확산은 지속(중국A 41개).</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
         <is>
           <t>※ 60일 컬럼은 TradingView 3개월(약 63거래일) 고저가 기준. 신고/신저 판정: 당일 고가(저가)가 해당 기간 최고(최저)가 도달.</t>
         </is>

--- a/신고신저가_20260720.xlsx
+++ b/신고신저가_20260720.xlsx
@@ -611,35 +611,35 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>💬 ■ 결론: 금요일(7/17)은 AI 하드웨어 고밸류 되돌림의 전면 확산 — 지수 조정(나스닥 -1.4%, 닛케이 -4.0%) 속 미국만 금융·디펜시브 로테이션으로 방어.</t>
+          <t>💬 ■ 결론: 금요일(7/17)은 AI 하드웨어 고밸류 되돌림의 전면 확산 — 지수 조정 속 미국만 금융·디펜시브 로테이션으로 방어.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="inlineStr">
         <is>
-          <t>■ 좋은 섹터: 美 금융(신고 순증 +55, PER 19배·밸류 부담無)·유틸·헬스케어 / 日 의약·운수·식품(급락장 유일 플러스) / 中 중약(15·5규획 발표).</t>
+          <t>■ 美: 나스닥 -1.4%·S&amp;P -1.0% — 강세: 금융(신고 순증 +55, PER 19배)·유틸·헬스케어·에너지(1주 +4.7%, YTD +31% 1위). 약세: 전자기술(신저 -26)·커뮤니케이션 -1.8%. TRV 어닝서프라이즈 +8%, NFLX 가이던스 실망 -7%.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="inlineStr">
         <is>
-          <t>■ 나쁜 섹터: AI 하드웨어 체인 일괄 — 美 전자기술(신저 순증 -26)·비철(-13), 日 기계 -5.9%·철강비철 -4.9%(ETF 1M -16%)·AI전선, 中 광모듈(天孚 -13%, PE 106배)·PCB(하한가 다수)·메모리, 항셍테크 -4.4%. 日 은행 -4.7%는 YTD +40% 후 차익실현(성격 상이).</t>
+          <t>■ 日: 닛케이 -4.0% 급락 — 기계 -5.9%·철강비철 -4.9%(1M -16%)·AI전선 동반 붕괴, 은행 -4.7%는 YTD +40% 후 차익실현(성격 상이). 플러스는 의약·운수·식품 디펜시브뿐. 세븐&amp;아이 자브카 출자 검토 보도 신고가.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="inlineStr">
         <is>
-          <t>■ 이벤트: TRV 어닝서프라이즈 +8%, NFLX 3Q 가이던스 실망 -7%, 세븐&amp;아이 자브카 출자 검토 보도 신고가.</t>
+          <t>■ 中·홍콩: 항셍테크 -4.4%, A주 신저 41개 — 광모듈(天孚 -13%, PE 106배)·PCB(하한가 다수)·메모리 고밸류 해소. 중약만 15·5규획 발표에 역행 강세.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>■ 체크: ①화요일 도쿄(금 -4%를 월 휴장으로 미소화) ②월요일 밤 미국 ③미·이란(유가·금리). ※월요일 장중 중화권 +2~3% 반등했으나 신저가 확산은 지속(중국A 41개).</t>
+          <t>■ 체크: ①화요일 도쿄(월 휴장으로 금 -4% 미소화) ②월요일 밤 미국 ③미·이란(유가·금리).</t>
         </is>
       </c>
     </row>

--- a/신고신저가_20260720.xlsx
+++ b/신고신저가_20260720.xlsx
@@ -6583,9 +6583,9 @@
   <conditionalFormatting sqref="D2:D45">
     <cfRule type="colorScale" priority="1">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-10"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="1.2"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6595,9 +6595,9 @@
   <conditionalFormatting sqref="E2:E45">
     <cfRule type="colorScale" priority="2">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-21.8"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="4.7"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6607,9 +6607,9 @@
   <conditionalFormatting sqref="F2:F45">
     <cfRule type="colorScale" priority="3">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-22.4"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="12.7"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6619,9 +6619,9 @@
   <conditionalFormatting sqref="G2:G45">
     <cfRule type="colorScale" priority="4">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-24.7"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="33.9"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6631,9 +6631,9 @@
   <conditionalFormatting sqref="H2:H45">
     <cfRule type="colorScale" priority="5">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-22.9"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="46.2"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6643,9 +6643,9 @@
   <conditionalFormatting sqref="J2:J45">
     <cfRule type="colorScale" priority="6">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-13"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="101.1"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6655,9 +6655,9 @@
   <conditionalFormatting sqref="L2:L45">
     <cfRule type="colorScale" priority="7">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-14.9"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="50.4"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6667,9 +6667,9 @@
   <conditionalFormatting sqref="N2:N45">
     <cfRule type="colorScale" priority="8">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-35.2"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="56"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6679,9 +6679,9 @@
   <conditionalFormatting sqref="P2:P45">
     <cfRule type="colorScale" priority="9">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-37.8"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="64.3"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6691,9 +6691,9 @@
   <conditionalFormatting sqref="R2:R45">
     <cfRule type="colorScale" priority="10">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-32.9"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="53.3"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
@@ -6703,9 +6703,9 @@
   <conditionalFormatting sqref="T2:T45">
     <cfRule type="colorScale" priority="11">
       <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
+        <cfvo type="num" val="-32.7"/>
+        <cfvo type="num" val="0"/>
+        <cfvo type="num" val="302.8"/>
         <color rgb="007A9BFF"/>
         <color rgb="00FFFFFF"/>
         <color rgb="00FF7B7B"/>
